--- a/Products Price table Web.xlsx
+++ b/Products Price table Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3C9C01-ECAA-4C3E-95F1-B5D511D148E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C68133D-CA5A-494A-98A5-28641BE69488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="ITEM_DDOWN">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Item Classification 7.14.26'!$A$1:$P$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Item Classification 7.14.26'!$A$1:$P$60</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Item Classification 7.14.26'!$1:$1</definedName>
     <definedName name="TOFU">#REF!</definedName>
     <definedName name="VENDOR_DDOWN">#REF!</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="124">
   <si>
     <t>Items</t>
   </si>
@@ -418,6 +418,9 @@
   </si>
   <si>
     <t>9 Star</t>
+  </si>
+  <si>
+    <t>Wang-TX</t>
   </si>
 </sst>
 </file>
@@ -746,7 +749,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -923,9 +926,6 @@
     <xf numFmtId="20" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1029,6 +1029,30 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1349,12 +1373,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.140625" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" style="1" customWidth="1"/>
     <col min="4" max="5" width="11.5703125" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="1"/>
     <col min="7" max="7" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1370,10 +1394,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="18.75">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="77" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -1394,13 +1418,13 @@
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="73" t="s">
+      <c r="I1" s="72" t="s">
         <v>120</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="74" t="s">
+      <c r="K1" s="73" t="s">
         <v>121</v>
       </c>
       <c r="L1" s="6" t="s">
@@ -1420,10 +1444,10 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="75" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1452,7 +1476,7 @@
         <f>N2/F2</f>
         <v>8</v>
       </c>
-      <c r="K2" s="75">
+      <c r="K2" s="74">
         <f>J2/I2-1</f>
         <v>1.7118644067796609</v>
       </c>
@@ -1472,10 +1496,10 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="75" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -1504,7 +1528,7 @@
         <f>N3/F2</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="K3" s="75">
+      <c r="K3" s="74">
         <f>J3/I2-1</f>
         <v>2.1186440677966099</v>
       </c>
@@ -1524,10 +1548,10 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="75" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -1556,7 +1580,7 @@
         <f>N4/F4</f>
         <v>3.9</v>
       </c>
-      <c r="K4" s="75">
+      <c r="K4" s="74">
         <f>J4/I4-1</f>
         <v>0.28712871287128716</v>
       </c>
@@ -1578,10 +1602,10 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="75" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -1610,7 +1634,7 @@
         <f>N5/F5</f>
         <v>8</v>
       </c>
-      <c r="K5" s="75">
+      <c r="K5" s="74">
         <f>J5/I5-1</f>
         <v>1.7972027972027975</v>
       </c>
@@ -1630,10 +1654,10 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="75" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -1662,7 +1686,7 @@
         <f>N6/F5</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="K6" s="75">
+      <c r="K6" s="74">
         <f>J6/I5-1</f>
         <v>2.2167832167832167</v>
       </c>
@@ -1682,10 +1706,10 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="75" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1714,8 +1738,8 @@
         <f>N7/F7</f>
         <v>3.9</v>
       </c>
-      <c r="K7" s="75">
-        <f t="shared" ref="K7:K58" si="1">J7/I7-1</f>
+      <c r="K7" s="74">
+        <f t="shared" ref="K7:K59" si="1">J7/I7-1</f>
         <v>0.28712871287128716</v>
       </c>
       <c r="L7" s="9">
@@ -1736,10 +1760,10 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="79" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -1792,7 +1816,7 @@
       <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="80" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -1820,7 +1844,7 @@
       <c r="J9" s="21">
         <v>4.8</v>
       </c>
-      <c r="K9" s="75">
+      <c r="K9" s="74">
         <f t="shared" si="1"/>
         <v>0.71428571428571441</v>
       </c>
@@ -1842,10 +1866,10 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="76" t="s">
         <v>112</v>
       </c>
       <c r="C10" s="23" t="s">
@@ -1875,7 +1899,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="46"/>
-      <c r="M10" s="91"/>
+      <c r="M10" s="90"/>
       <c r="N10" s="27">
         <v>95.4</v>
       </c>
@@ -1886,10 +1910,10 @@
       <c r="R10" s="29"/>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="76" t="s">
         <v>113</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -1914,15 +1938,15 @@
       <c r="I11" s="20">
         <v>3.18</v>
       </c>
-      <c r="J11" s="95">
+      <c r="J11" s="94">
         <v>4.875</v>
       </c>
-      <c r="K11" s="75">
+      <c r="K11" s="74">
         <f t="shared" si="1"/>
         <v>0.53301886792452824</v>
       </c>
       <c r="L11" s="46"/>
-      <c r="M11" s="91"/>
+      <c r="M11" s="90"/>
       <c r="N11" s="21">
         <v>97.5</v>
       </c>
@@ -1933,10 +1957,10 @@
       <c r="R11" s="29"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="76" t="s">
         <v>114</v>
       </c>
       <c r="C12" s="30" t="s">
@@ -1965,13 +1989,13 @@
         <f>N12/F12</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="K12" s="75">
+      <c r="K12" s="74">
         <f t="shared" si="1"/>
         <v>0.60278745644599274</v>
       </c>
       <c r="L12" s="32"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="82">
+      <c r="M12" s="91"/>
+      <c r="N12" s="81">
         <v>92</v>
       </c>
       <c r="O12" s="32"/>
@@ -1980,10 +2004,10 @@
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="76" t="s">
         <v>114</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -1999,7 +2023,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="7">
-        <f t="shared" ref="G13" si="3">F13*42</f>
+        <f>F13*42</f>
         <v>840</v>
       </c>
       <c r="H13" s="13">
@@ -2012,13 +2036,13 @@
         <f>N13/F13</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="K13" s="75">
+      <c r="K13" s="74">
         <f>J12/I12-1</f>
         <v>0.60278745644599274</v>
       </c>
       <c r="L13" s="35"/>
-      <c r="M13" s="93"/>
-      <c r="N13" s="82">
+      <c r="M13" s="92"/>
+      <c r="N13" s="81">
         <v>92</v>
       </c>
       <c r="O13" s="35"/>
@@ -2027,10 +2051,10 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="76" t="s">
         <v>115</v>
       </c>
       <c r="C14" s="10" t="s">
@@ -2059,12 +2083,12 @@
         <f>N14/F14</f>
         <v>4.5</v>
       </c>
-      <c r="K14" s="75">
+      <c r="K14" s="74">
         <f t="shared" si="1"/>
         <v>0.56794425087108014</v>
       </c>
       <c r="L14" s="11"/>
-      <c r="M14" s="94"/>
+      <c r="M14" s="93"/>
       <c r="N14" s="9">
         <v>90</v>
       </c>
@@ -2074,10 +2098,10 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="76" t="s">
         <v>115</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -2093,7 +2117,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" ref="G15" si="4">F15*42</f>
+        <f t="shared" ref="G15:G23" si="3">F15*42</f>
         <v>840</v>
       </c>
       <c r="H15" s="7">
@@ -2106,12 +2130,12 @@
         <f>N15/F14</f>
         <v>5.4</v>
       </c>
-      <c r="K15" s="75">
+      <c r="K15" s="74">
         <f>J15/I14-1</f>
         <v>0.88153310104529625</v>
       </c>
       <c r="L15" s="11"/>
-      <c r="M15" s="94"/>
+      <c r="M15" s="93"/>
       <c r="N15" s="9">
         <v>108</v>
       </c>
@@ -2121,10 +2145,10 @@
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="77" t="s">
+      <c r="B16" s="76" t="s">
         <v>116</v>
       </c>
       <c r="C16" s="30" t="s">
@@ -2140,7 +2164,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="7">
-        <f>F16*42</f>
+        <f t="shared" si="3"/>
         <v>630</v>
       </c>
       <c r="H16" s="10">
@@ -2153,12 +2177,12 @@
         <f>N16/F16</f>
         <v>5.3</v>
       </c>
-      <c r="K16" s="75">
+      <c r="K16" s="74">
         <f t="shared" si="1"/>
         <v>0.70967741935483852</v>
       </c>
       <c r="L16" s="11"/>
-      <c r="M16" s="94"/>
+      <c r="M16" s="93"/>
       <c r="N16" s="9">
         <v>79.5</v>
       </c>
@@ -2168,10 +2192,10 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A17" s="77" t="s">
+      <c r="A17" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="77" t="s">
+      <c r="B17" s="76" t="s">
         <v>116</v>
       </c>
       <c r="C17" s="30" t="s">
@@ -2187,7 +2211,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="7">
-        <f t="shared" ref="G17:G18" si="5">F17*42</f>
+        <f t="shared" si="3"/>
         <v>630</v>
       </c>
       <c r="H17" s="10">
@@ -2200,13 +2224,13 @@
         <f>N17/F16</f>
         <v>4.6500000000000004</v>
       </c>
-      <c r="K17" s="75">
+      <c r="K17" s="74">
         <f>J17/I16-1</f>
         <v>0.5</v>
       </c>
       <c r="L17" s="32"/>
-      <c r="M17" s="92"/>
-      <c r="N17" s="82">
+      <c r="M17" s="91"/>
+      <c r="N17" s="81">
         <v>69.75</v>
       </c>
       <c r="O17" s="11"/>
@@ -2215,10 +2239,10 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A18" s="77" t="s">
+      <c r="A18" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="77" t="s">
+      <c r="B18" s="76" t="s">
         <v>116</v>
       </c>
       <c r="C18" s="30" t="s">
@@ -2234,7 +2258,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>630</v>
       </c>
       <c r="H18" s="10">
@@ -2247,13 +2271,13 @@
         <f>N18/F17</f>
         <v>4.6500000000000004</v>
       </c>
-      <c r="K18" s="75">
+      <c r="K18" s="74">
         <f>J17/I16-1</f>
         <v>0.5</v>
       </c>
       <c r="L18" s="35"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="82">
+      <c r="M18" s="92"/>
+      <c r="N18" s="81">
         <v>69.75</v>
       </c>
       <c r="O18" s="11"/>
@@ -2262,10 +2286,10 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="76" t="s">
         <v>116</v>
       </c>
       <c r="C19" s="30" t="s">
@@ -2281,7 +2305,7 @@
         <v>14</v>
       </c>
       <c r="G19" s="13">
-        <f>F19*42</f>
+        <f t="shared" si="3"/>
         <v>588</v>
       </c>
       <c r="H19" s="10">
@@ -2294,7 +2318,7 @@
         <f>N19/14</f>
         <v>4.7</v>
       </c>
-      <c r="K19" s="75">
+      <c r="K19" s="74">
         <f>J19/I16-1</f>
         <v>0.5161290322580645</v>
       </c>
@@ -2313,10 +2337,10 @@
       <c r="R19" s="29"/>
     </row>
     <row r="20" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B20" s="80" t="s">
         <v>117</v>
       </c>
       <c r="C20" s="30" t="s">
@@ -2332,7 +2356,7 @@
         <v>20</v>
       </c>
       <c r="G20" s="7">
-        <f>F20*42</f>
+        <f t="shared" si="3"/>
         <v>840</v>
       </c>
       <c r="H20" s="10">
@@ -2345,7 +2369,7 @@
         <f>N20/F$20</f>
         <v>5</v>
       </c>
-      <c r="K20" s="75">
+      <c r="K20" s="74">
         <f t="shared" si="1"/>
         <v>0.27551020408163263</v>
       </c>
@@ -2360,10 +2384,10 @@
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="B21" s="80" t="s">
         <v>117</v>
       </c>
       <c r="C21" s="30" t="s">
@@ -2379,7 +2403,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="7">
-        <f t="shared" ref="G21:G23" si="6">F21*42</f>
+        <f t="shared" si="3"/>
         <v>840</v>
       </c>
       <c r="H21" s="10">
@@ -2392,13 +2416,13 @@
         <f>N21/F$20</f>
         <v>5.6</v>
       </c>
-      <c r="K21" s="75">
+      <c r="K21" s="74">
         <f>J21/I20-1</f>
         <v>0.4285714285714286</v>
       </c>
       <c r="L21" s="31"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="82">
+      <c r="N21" s="81">
         <v>112</v>
       </c>
       <c r="O21" s="11"/>
@@ -2407,10 +2431,10 @@
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="80" t="s">
         <v>117</v>
       </c>
       <c r="C22" s="30" t="s">
@@ -2426,7 +2450,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>840</v>
       </c>
       <c r="H22" s="13">
@@ -2439,13 +2463,13 @@
         <f>N22/F$20</f>
         <v>5.6</v>
       </c>
-      <c r="K22" s="75">
+      <c r="K22" s="74">
         <f>J21/I20-1</f>
         <v>0.4285714285714286</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="14"/>
-      <c r="N22" s="82">
+      <c r="N22" s="81">
         <v>112</v>
       </c>
       <c r="O22" s="11"/>
@@ -2454,10 +2478,10 @@
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A23" s="77" t="s">
+      <c r="A23" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="81" t="s">
+      <c r="B23" s="80" t="s">
         <v>117</v>
       </c>
       <c r="C23" s="30" t="s">
@@ -2473,7 +2497,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>840</v>
       </c>
       <c r="H23" s="13">
@@ -2486,7 +2510,7 @@
         <f>N23/F$20</f>
         <v>5.95</v>
       </c>
-      <c r="K23" s="75">
+      <c r="K23" s="74">
         <f>J23/I20-1</f>
         <v>0.51785714285714302</v>
       </c>
@@ -2501,10 +2525,10 @@
       </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A24" s="77" t="s">
+      <c r="A24" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="80" t="s">
         <v>117</v>
       </c>
       <c r="C24" s="30" t="s">
@@ -2533,7 +2557,7 @@
         <f>N24/F24</f>
         <v>5.83</v>
       </c>
-      <c r="K24" s="75">
+      <c r="K24" s="74">
         <f>J24/I20-1</f>
         <v>0.48724489795918369</v>
       </c>
@@ -2554,10 +2578,10 @@
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A25" s="77" t="s">
+      <c r="A25" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="80" t="s">
+      <c r="B25" s="79" t="s">
         <v>45</v>
       </c>
       <c r="C25" s="37" t="s">
@@ -2585,7 +2609,7 @@
       <c r="J25" s="9">
         <v>4.8499999999999996</v>
       </c>
-      <c r="K25" s="75">
+      <c r="K25" s="74">
         <f>J25/I25-1</f>
         <v>0.49230769230769211</v>
       </c>
@@ -2601,10 +2625,10 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A26" s="77" t="s">
+      <c r="A26" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="75" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -2620,7 +2644,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="7">
-        <f>F26*42</f>
+        <f t="shared" ref="G26:G39" si="4">F26*42</f>
         <v>840</v>
       </c>
       <c r="H26" s="10">
@@ -2633,7 +2657,7 @@
         <f>N26/F26</f>
         <v>5.0999999999999996</v>
       </c>
-      <c r="K26" s="75">
+      <c r="K26" s="74">
         <f t="shared" si="1"/>
         <v>0.3563829787234043</v>
       </c>
@@ -2648,10 +2672,10 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A27" s="77" t="s">
+      <c r="A27" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="75" t="s">
         <v>47</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -2667,7 +2691,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" ref="G27:G29" si="7">F27*42</f>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H27" s="10">
@@ -2680,7 +2704,7 @@
         <f>N27/F$26</f>
         <v>5.5</v>
       </c>
-      <c r="K27" s="75">
+      <c r="K27" s="74">
         <f>J27/I26-1</f>
         <v>0.4627659574468086</v>
       </c>
@@ -2695,10 +2719,10 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="76" t="s">
+      <c r="B28" s="75" t="s">
         <v>47</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -2714,7 +2738,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H28" s="10">
@@ -2727,7 +2751,7 @@
         <f>N28/F$26</f>
         <v>6.45</v>
       </c>
-      <c r="K28" s="75">
+      <c r="K28" s="74">
         <f>J28/I26-1</f>
         <v>0.71542553191489366</v>
       </c>
@@ -2742,10 +2766,10 @@
       </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A29" s="77" t="s">
+      <c r="A29" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="76" t="s">
+      <c r="B29" s="75" t="s">
         <v>47</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -2761,7 +2785,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H29" s="10">
@@ -2774,7 +2798,7 @@
         <f>N29/F$26</f>
         <v>6</v>
       </c>
-      <c r="K29" s="75">
+      <c r="K29" s="74">
         <f>J29/I26-1</f>
         <v>0.59574468085106402</v>
       </c>
@@ -2789,10 +2813,10 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A30" s="77" t="s">
+      <c r="A30" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="86" t="s">
+      <c r="B30" s="85" t="s">
         <v>49</v>
       </c>
       <c r="C30" s="30" t="s">
@@ -2808,7 +2832,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="7">
-        <f>F30*42</f>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H30" s="14">
@@ -2821,7 +2845,7 @@
         <f>N30/F30</f>
         <v>5.75</v>
       </c>
-      <c r="K30" s="75">
+      <c r="K30" s="74">
         <f t="shared" si="1"/>
         <v>0.47058823529411753</v>
       </c>
@@ -2836,10 +2860,10 @@
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A31" s="77" t="s">
+      <c r="A31" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="86" t="s">
+      <c r="B31" s="85" t="s">
         <v>49</v>
       </c>
       <c r="C31" s="30" t="s">
@@ -2855,7 +2879,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" ref="G31:G32" si="8">F31*42</f>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H31" s="14">
@@ -2868,7 +2892,7 @@
         <f>N31/F$30</f>
         <v>6.75</v>
       </c>
-      <c r="K31" s="75">
+      <c r="K31" s="74">
         <f>J31/I30-1</f>
         <v>0.7263427109974423</v>
       </c>
@@ -2883,10 +2907,10 @@
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A32" s="77" t="s">
+      <c r="A32" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="86" t="s">
+      <c r="B32" s="85" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="30" t="s">
@@ -2902,7 +2926,7 @@
         <v>20</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H32" s="14">
@@ -2915,7 +2939,7 @@
         <f>N32/F$30</f>
         <v>6.25</v>
       </c>
-      <c r="K32" s="75">
+      <c r="K32" s="74">
         <f>J32/I30-1</f>
         <v>0.59846547314577991</v>
       </c>
@@ -2930,10 +2954,10 @@
       </c>
     </row>
     <row r="33" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A33" s="77" t="s">
+      <c r="A33" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="86" t="s">
+      <c r="B33" s="85" t="s">
         <v>51</v>
       </c>
       <c r="C33" s="30" t="s">
@@ -2949,7 +2973,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="7">
-        <f>F33*42</f>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H33" s="14">
@@ -2962,7 +2986,7 @@
         <f>N33/F$33</f>
         <v>5.75</v>
       </c>
-      <c r="K33" s="75">
+      <c r="K33" s="74">
         <f t="shared" si="1"/>
         <v>0.2979683972911964</v>
       </c>
@@ -2977,10 +3001,10 @@
       </c>
     </row>
     <row r="34" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A34" s="77" t="s">
+      <c r="A34" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="85" t="s">
         <v>51</v>
       </c>
       <c r="C34" s="30" t="s">
@@ -2996,7 +3020,7 @@
         <v>20</v>
       </c>
       <c r="G34" s="7">
-        <f t="shared" ref="G34:G35" si="9">F34*42</f>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H34" s="14">
@@ -3009,7 +3033,7 @@
         <f>N34/F$33</f>
         <v>6.75</v>
       </c>
-      <c r="K34" s="75">
+      <c r="K34" s="74">
         <f>J34/I33-1</f>
         <v>0.52370203160270901</v>
       </c>
@@ -3024,10 +3048,10 @@
       </c>
     </row>
     <row r="35" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A35" s="77" t="s">
+      <c r="A35" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="86" t="s">
+      <c r="B35" s="85" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="30" t="s">
@@ -3043,7 +3067,7 @@
         <v>20</v>
       </c>
       <c r="G35" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H35" s="14">
@@ -3056,7 +3080,7 @@
         <f>N35/F$33</f>
         <v>6.25</v>
       </c>
-      <c r="K35" s="75">
+      <c r="K35" s="74">
         <f>J35/I33-1</f>
         <v>0.4108352144469527</v>
       </c>
@@ -3071,10 +3095,10 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A36" s="81" t="s">
+      <c r="A36" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="83" t="s">
+      <c r="B36" s="82" t="s">
         <v>54</v>
       </c>
       <c r="C36" s="10" t="s">
@@ -3090,7 +3114,7 @@
         <v>40</v>
       </c>
       <c r="G36" s="10">
-        <f>F36*42</f>
+        <f t="shared" si="4"/>
         <v>1680</v>
       </c>
       <c r="H36" s="10">
@@ -3102,7 +3126,7 @@
       <c r="J36" s="9">
         <v>6.5</v>
       </c>
-      <c r="K36" s="75">
+      <c r="K36" s="74">
         <f t="shared" si="1"/>
         <v>0.32113821138211374</v>
       </c>
@@ -3121,10 +3145,10 @@
       </c>
     </row>
     <row r="37" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A37" s="81" t="s">
+      <c r="A37" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="83" t="s">
+      <c r="B37" s="82" t="s">
         <v>57</v>
       </c>
       <c r="C37" s="10" t="s">
@@ -3140,7 +3164,7 @@
         <v>40</v>
       </c>
       <c r="G37" s="10">
-        <f>F37*42</f>
+        <f t="shared" si="4"/>
         <v>1680</v>
       </c>
       <c r="H37" s="10">
@@ -3152,7 +3176,7 @@
       <c r="J37" s="9">
         <v>6.5</v>
       </c>
-      <c r="K37" s="75">
+      <c r="K37" s="74">
         <f t="shared" si="1"/>
         <v>0.37420718816067633</v>
       </c>
@@ -3171,10 +3195,10 @@
       </c>
     </row>
     <row r="38" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A38" s="77" t="s">
+      <c r="A38" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="84" t="s">
+      <c r="B38" s="83" t="s">
         <v>60</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -3190,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="G38" s="7">
-        <f>F38*42</f>
+        <f t="shared" si="4"/>
         <v>1260</v>
       </c>
       <c r="H38" s="10">
@@ -3201,16 +3225,16 @@
       </c>
       <c r="J38" s="9">
         <f>N38/F38</f>
-        <v>6</v>
-      </c>
-      <c r="K38" s="75">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="K38" s="74">
         <f t="shared" si="1"/>
-        <v>0.2396694214876034</v>
+        <v>0.30853994490358128</v>
       </c>
       <c r="L38" s="9"/>
       <c r="M38" s="10"/>
       <c r="N38" s="9">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="O38" s="43"/>
       <c r="P38" s="44" t="s">
@@ -3218,10 +3242,10 @@
       </c>
     </row>
     <row r="39" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A39" s="77" t="s">
+      <c r="A39" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="84" t="s">
+      <c r="B39" s="83" t="s">
         <v>60</v>
       </c>
       <c r="C39" s="7" t="s">
@@ -3237,7 +3261,7 @@
         <v>30</v>
       </c>
       <c r="G39" s="7">
-        <f>F39*42</f>
+        <f t="shared" si="4"/>
         <v>1260</v>
       </c>
       <c r="H39" s="10">
@@ -3250,7 +3274,7 @@
         <f>N39/F38</f>
         <v>5.75</v>
       </c>
-      <c r="K39" s="75">
+      <c r="K39" s="74">
         <f>J39/I38-1</f>
         <v>0.18801652892561993</v>
       </c>
@@ -3265,10 +3289,10 @@
       </c>
     </row>
     <row r="40" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A40" s="77" t="s">
+      <c r="A40" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="84" t="s">
+      <c r="B40" s="83" t="s">
         <v>63</v>
       </c>
       <c r="C40" s="7" t="s">
@@ -3285,7 +3309,7 @@
         <v>19.8</v>
       </c>
       <c r="G40" s="7">
-        <f t="shared" ref="G40:G46" si="10">F40*42</f>
+        <f t="shared" ref="G40:G47" si="5">F40*42</f>
         <v>831.6</v>
       </c>
       <c r="H40" s="7">
@@ -3298,7 +3322,7 @@
         <f>N40/F40</f>
         <v>5.954545454545455</v>
       </c>
-      <c r="K40" s="75">
+      <c r="K40" s="74">
         <f t="shared" si="1"/>
         <v>0.11508341845420511</v>
       </c>
@@ -3318,243 +3342,236 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:16" s="45" customFormat="1" ht="15.6" customHeight="1">
-      <c r="A41" s="77" t="s">
+    <row r="41" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A41" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B41" s="88" t="s">
+      <c r="B41" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="96" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="97" t="s">
+        <v>34</v>
+      </c>
+      <c r="F41" s="98">
+        <v>30</v>
+      </c>
+      <c r="G41" s="98">
+        <f t="shared" ref="G41" si="6">F41*42</f>
+        <v>1260</v>
+      </c>
+      <c r="H41" s="98">
+        <v>42</v>
+      </c>
+      <c r="I41" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="J41" s="100">
+        <v>6.35</v>
+      </c>
+      <c r="K41" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41" s="100"/>
+      <c r="M41" s="98"/>
+      <c r="N41" s="9">
+        <f>J41*F41</f>
+        <v>190.5</v>
+      </c>
+      <c r="O41" s="101"/>
+      <c r="P41" s="103" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="45" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A42" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="48" t="s">
+      <c r="C42" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="49" t="s">
+      <c r="D42" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="50">
+      <c r="E42" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="F42" s="50">
         <v>30</v>
       </c>
-      <c r="G41" s="50">
-        <f t="shared" si="10"/>
+      <c r="G42" s="50">
+        <f t="shared" si="5"/>
         <v>1260</v>
       </c>
-      <c r="H41" s="50">
-        <v>42</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J41" s="51">
+      <c r="H42" s="50">
+        <v>42</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J42" s="51">
         <v>5.15</v>
       </c>
-      <c r="K41" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L41" s="51"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="52">
+      <c r="K42" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42" s="51"/>
+      <c r="M42" s="50"/>
+      <c r="N42" s="52">
         <v>117.9</v>
       </c>
-      <c r="O41" s="51"/>
-      <c r="P41" s="53"/>
-    </row>
-    <row r="42" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A42" s="77" t="s">
+      <c r="O42" s="51"/>
+      <c r="P42" s="53"/>
+    </row>
+    <row r="43" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A43" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="85" t="s">
+      <c r="B43" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="54" t="s">
+      <c r="C43" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="D42" s="55" t="s">
+      <c r="D43" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="E42" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="F42" s="54">
+      <c r="E43" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="54">
         <v>30</v>
       </c>
-      <c r="G42" s="50">
-        <f t="shared" si="10"/>
+      <c r="G43" s="50">
+        <f t="shared" si="5"/>
         <v>1260</v>
       </c>
-      <c r="H42" s="54">
-        <v>42</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J42" s="57"/>
-      <c r="K42" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L42" s="57"/>
-      <c r="M42" s="54"/>
-      <c r="N42" s="57"/>
-      <c r="O42" s="57"/>
-      <c r="P42" s="58"/>
-    </row>
-    <row r="43" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A43" s="77" t="s">
+      <c r="H43" s="54">
+        <v>42</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J43" s="57"/>
+      <c r="K43" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43" s="57"/>
+      <c r="M43" s="54"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="57"/>
+      <c r="P43" s="58"/>
+    </row>
+    <row r="44" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A44" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="80" t="s">
+      <c r="B44" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="C44" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D44" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E44" s="10">
         <v>5</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F44" s="10">
         <v>30</v>
       </c>
-      <c r="G43" s="7">
-        <f t="shared" si="10"/>
+      <c r="G44" s="7">
+        <f t="shared" si="5"/>
         <v>1260</v>
       </c>
-      <c r="H43" s="10">
-        <v>42</v>
-      </c>
-      <c r="I43" s="10">
+      <c r="H44" s="10">
+        <v>42</v>
+      </c>
+      <c r="I44" s="10">
         <v>0.94</v>
       </c>
-      <c r="J43" s="9">
-        <f>N43/F43</f>
+      <c r="J44" s="9">
+        <f>N44/F44</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="K43" s="75">
+      <c r="K44" s="74">
         <f t="shared" si="1"/>
         <v>0.22340425531914887</v>
       </c>
-      <c r="L43" s="9">
-        <f>N43/6</f>
+      <c r="L44" s="9">
+        <f>N44/6</f>
         <v>5.75</v>
       </c>
-      <c r="M43" s="10"/>
-      <c r="N43" s="9">
+      <c r="M44" s="10"/>
+      <c r="N44" s="9">
         <v>34.5</v>
       </c>
-      <c r="O43" s="11">
+      <c r="O44" s="11">
         <v>30</v>
       </c>
-      <c r="P43" s="59" t="s">
+      <c r="P44" s="59" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="31.5">
-      <c r="A44" s="77" t="s">
+    <row r="45" spans="1:16" ht="15.75">
+      <c r="A45" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="80" t="s">
+      <c r="B45" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C45" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D45" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E44" s="60">
+      <c r="E45" s="102">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F45" s="10">
         <f>25*1.1</f>
         <v>27.500000000000004</v>
       </c>
-      <c r="G44" s="10">
-        <f t="shared" si="10"/>
+      <c r="G45" s="10">
+        <f t="shared" si="5"/>
         <v>1155.0000000000002</v>
       </c>
-      <c r="H44" s="10">
-        <v>42</v>
-      </c>
-      <c r="I44" s="10">
+      <c r="H45" s="10">
+        <v>42</v>
+      </c>
+      <c r="I45" s="10">
         <v>1.42</v>
       </c>
-      <c r="J44" s="9">
-        <f>N44/F44</f>
+      <c r="J45" s="9">
+        <f>N45/F45</f>
         <v>1.6363636363636362</v>
       </c>
-      <c r="K44" s="75">
+      <c r="K45" s="74">
         <f t="shared" si="1"/>
         <v>0.15236875800256078</v>
       </c>
-      <c r="L44" s="9">
-        <f>N44/25</f>
+      <c r="L45" s="9">
+        <f>N45/25</f>
         <v>1.8</v>
-      </c>
-      <c r="M44" s="10"/>
-      <c r="N44" s="9">
-        <v>45</v>
-      </c>
-      <c r="O44" s="9">
-        <v>45</v>
-      </c>
-      <c r="P44" s="61" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
-      <c r="A45" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B45" s="87" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E45" s="17">
-        <v>0.875</v>
-      </c>
-      <c r="F45" s="62">
-        <f>E45*24</f>
-        <v>21</v>
-      </c>
-      <c r="G45" s="10">
-        <f t="shared" si="10"/>
-        <v>882</v>
-      </c>
-      <c r="H45" s="10">
-        <v>42</v>
-      </c>
-      <c r="I45" s="10">
-        <v>9.1199999999999992</v>
-      </c>
-      <c r="J45" s="9">
-        <f>N45/F45</f>
-        <v>10.8</v>
-      </c>
-      <c r="K45" s="75">
-        <f t="shared" si="1"/>
-        <v>0.1842105263157896</v>
-      </c>
-      <c r="L45" s="9">
-        <f>N45/24</f>
-        <v>9.4500000000000011</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="9">
-        <v>226.8</v>
+        <v>45</v>
       </c>
       <c r="O45" s="9">
-        <v>226.8</v>
-      </c>
-      <c r="P45" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="P45" s="60" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3562,680 +3579,733 @@
       <c r="A46" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B46" s="87" t="s">
-        <v>79</v>
+      <c r="B46" s="86" t="s">
+        <v>77</v>
       </c>
       <c r="C46" s="30" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E46" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="F46" s="61">
+        <f>E46*24</f>
+        <v>21</v>
+      </c>
+      <c r="G46" s="10">
+        <f t="shared" si="5"/>
+        <v>882</v>
+      </c>
+      <c r="H46" s="10">
+        <v>42</v>
+      </c>
+      <c r="I46" s="10">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="J46" s="9">
+        <f>N46/F46</f>
+        <v>10.8</v>
+      </c>
+      <c r="K46" s="74">
+        <f t="shared" si="1"/>
+        <v>0.1842105263157896</v>
+      </c>
+      <c r="L46" s="9">
+        <f>N46/24</f>
+        <v>9.4500000000000011</v>
+      </c>
+      <c r="M46" s="10"/>
+      <c r="N46" s="9">
+        <v>226.8</v>
+      </c>
+      <c r="O46" s="9">
+        <v>226.8</v>
+      </c>
+      <c r="P46" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
+      <c r="A47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E47" s="17">
         <v>0.75</v>
       </c>
-      <c r="F46" s="62">
+      <c r="F47" s="61">
         <v>19.5</v>
       </c>
-      <c r="G46" s="10">
-        <f t="shared" si="10"/>
+      <c r="G47" s="10">
+        <f t="shared" si="5"/>
         <v>819</v>
       </c>
-      <c r="H46" s="10">
-        <v>42</v>
-      </c>
-      <c r="I46" s="10">
+      <c r="H47" s="10">
+        <v>42</v>
+      </c>
+      <c r="I47" s="10">
         <v>5.21</v>
       </c>
-      <c r="J46" s="9">
-        <f>O46/F46</f>
+      <c r="J47" s="9">
+        <f>O47/F47</f>
         <v>7.5066666666666668</v>
       </c>
-      <c r="K46" s="75">
+      <c r="K47" s="74">
         <f t="shared" si="1"/>
         <v>0.44081893793985927</v>
       </c>
-      <c r="L46" s="9">
-        <f>N46/26</f>
+      <c r="L47" s="9">
+        <f>N47/26</f>
         <v>5.63</v>
       </c>
-      <c r="M46" s="10"/>
-      <c r="N46" s="9">
+      <c r="M47" s="10"/>
+      <c r="N47" s="9">
         <v>146.38</v>
       </c>
-      <c r="O46" s="9">
+      <c r="O47" s="9">
         <v>146.38</v>
       </c>
-      <c r="P46" s="18" t="s">
+      <c r="P47" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:16" s="64" customFormat="1" ht="18" customHeight="1">
-      <c r="A47" s="10" t="s">
+    <row r="48" spans="1:16" s="63" customFormat="1" ht="18" customHeight="1">
+      <c r="A48" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B47" s="87" t="s">
+      <c r="B48" s="86" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C48" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D48" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E47" s="66"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="67"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L47" s="68"/>
-      <c r="M47" s="69"/>
-      <c r="N47" s="68"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="63"/>
-    </row>
-    <row r="48" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A48" s="77" t="s">
+      <c r="E48" s="65"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="67"/>
+      <c r="K48" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48" s="67"/>
+      <c r="M48" s="68"/>
+      <c r="N48" s="67"/>
+      <c r="O48" s="64"/>
+      <c r="P48" s="62"/>
+    </row>
+    <row r="49" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A49" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B48" s="89" t="s">
+      <c r="B49" s="88" t="s">
         <v>85</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C49" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D48" s="70" t="s">
+      <c r="D49" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="E48" s="70">
+      <c r="E49" s="69">
         <v>5</v>
       </c>
-      <c r="F48" s="62">
+      <c r="F49" s="61">
         <v>40</v>
       </c>
-      <c r="G48" s="10">
-        <f>F48*42</f>
+      <c r="G49" s="10">
+        <f>F49*42</f>
         <v>1680</v>
       </c>
-      <c r="H48" s="10">
-        <v>42</v>
-      </c>
-      <c r="I48" s="10">
+      <c r="H49" s="10">
+        <v>42</v>
+      </c>
+      <c r="I49" s="10">
         <v>1.26</v>
       </c>
-      <c r="J48" s="9">
+      <c r="J49" s="9">
         <v>1.95</v>
       </c>
-      <c r="K48" s="75">
+      <c r="K49" s="74">
         <f t="shared" si="1"/>
         <v>0.54761904761904767</v>
       </c>
-      <c r="L48" s="9">
-        <f>N48/8</f>
+      <c r="L49" s="9">
+        <f>N49/8</f>
         <v>9.75</v>
       </c>
-      <c r="M48" s="10"/>
-      <c r="N48" s="9">
-        <f>J48*F48</f>
+      <c r="M49" s="10"/>
+      <c r="N49" s="9">
+        <f>J49*F49</f>
         <v>78</v>
       </c>
-      <c r="O48" s="11"/>
-      <c r="P48" s="71" t="s">
+      <c r="O49" s="11"/>
+      <c r="P49" s="70" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:16" s="64" customFormat="1" ht="21" customHeight="1">
-      <c r="A49" s="77" t="s">
+    <row r="50" spans="1:16" s="63" customFormat="1" ht="21" customHeight="1">
+      <c r="A50" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B49" s="89" t="s">
+      <c r="B50" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C50" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="70" t="s">
+      <c r="D50" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="E49" s="70">
+      <c r="E50" s="69">
         <v>5</v>
       </c>
-      <c r="F49" s="62">
+      <c r="F50" s="61">
         <v>40</v>
       </c>
-      <c r="G49" s="10">
-        <f t="shared" ref="G49:G59" si="11">F49*42</f>
+      <c r="G50" s="10">
+        <f t="shared" ref="G50:G60" si="7">F50*42</f>
         <v>1680</v>
       </c>
-      <c r="H49" s="10">
-        <v>42</v>
-      </c>
-      <c r="I49" s="10">
+      <c r="H50" s="10">
+        <v>42</v>
+      </c>
+      <c r="I50" s="10">
         <v>1.53</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J50" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K49" s="75">
+      <c r="K50" s="74">
         <f t="shared" si="1"/>
         <v>0.50326797385620892</v>
       </c>
-      <c r="L49" s="9">
-        <f t="shared" ref="L49:L59" si="12">N49/8</f>
+      <c r="L50" s="9">
+        <f t="shared" ref="L50:L60" si="8">N50/8</f>
         <v>11.5</v>
       </c>
-      <c r="M49" s="10"/>
-      <c r="N49" s="9">
-        <f t="shared" ref="N49:N59" si="13">J49*F49</f>
+      <c r="M50" s="10"/>
+      <c r="N50" s="9">
+        <f t="shared" ref="N50:N60" si="9">J50*F50</f>
         <v>92</v>
       </c>
-      <c r="O49" s="11"/>
-      <c r="P49" s="71" t="s">
+      <c r="O50" s="11"/>
+      <c r="P50" s="70" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:16" s="64" customFormat="1" ht="21" customHeight="1">
-      <c r="A50" s="77" t="s">
+    <row r="51" spans="1:16" s="63" customFormat="1" ht="21" customHeight="1">
+      <c r="A51" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B50" s="89" t="s">
+      <c r="B51" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C51" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="70" t="s">
+      <c r="D51" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="E50" s="70">
+      <c r="E51" s="69">
         <v>5</v>
       </c>
-      <c r="F50" s="62">
+      <c r="F51" s="61">
         <v>40</v>
       </c>
-      <c r="G50" s="10">
-        <f t="shared" si="11"/>
+      <c r="G51" s="10">
+        <f t="shared" si="7"/>
         <v>1680</v>
       </c>
-      <c r="H50" s="10">
-        <v>42</v>
-      </c>
-      <c r="I50" s="10">
+      <c r="H51" s="10">
+        <v>42</v>
+      </c>
+      <c r="I51" s="10">
         <v>1.76</v>
       </c>
-      <c r="J50" s="9">
+      <c r="J51" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K50" s="75">
+      <c r="K51" s="74">
         <f t="shared" si="1"/>
         <v>0.30681818181818166</v>
       </c>
-      <c r="L50" s="9">
-        <f t="shared" si="12"/>
+      <c r="L51" s="9">
+        <f t="shared" si="8"/>
         <v>11.5</v>
-      </c>
-      <c r="M50" s="10"/>
-      <c r="N50" s="9">
-        <f t="shared" si="13"/>
-        <v>92</v>
-      </c>
-      <c r="O50" s="11"/>
-      <c r="P50" s="71" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" s="64" customFormat="1" ht="18" customHeight="1">
-      <c r="A51" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="B51" s="89" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D51" s="70" t="s">
-        <v>94</v>
-      </c>
-      <c r="E51" s="70">
-        <v>5</v>
-      </c>
-      <c r="F51" s="62">
-        <v>40</v>
-      </c>
-      <c r="G51" s="10">
-        <f t="shared" si="11"/>
-        <v>1680</v>
-      </c>
-      <c r="H51" s="10">
-        <v>42</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J51" s="9">
-        <v>5.2</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L51" s="9">
-        <f t="shared" si="12"/>
-        <v>26</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="9">
-        <f t="shared" si="13"/>
-        <v>208</v>
+        <f t="shared" si="9"/>
+        <v>92</v>
       </c>
       <c r="O51" s="11"/>
-      <c r="P51" s="71" t="s">
+      <c r="P51" s="70" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="52" spans="1:16" s="64" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A52" s="77" t="s">
+    <row r="52" spans="1:16" s="63" customFormat="1" ht="18" customHeight="1">
+      <c r="A52" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B52" s="89" t="s">
-        <v>95</v>
+      <c r="B52" s="88" t="s">
+        <v>93</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="70" t="s">
+      <c r="D52" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="E52" s="69">
+        <v>5</v>
+      </c>
+      <c r="F52" s="61">
+        <v>40</v>
+      </c>
+      <c r="G52" s="10">
+        <f t="shared" si="7"/>
+        <v>1680</v>
+      </c>
+      <c r="H52" s="10">
+        <v>42</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J52" s="9">
+        <v>5.2</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52" s="9">
+        <f t="shared" si="8"/>
+        <v>26</v>
+      </c>
+      <c r="M52" s="10"/>
+      <c r="N52" s="9">
+        <f t="shared" si="9"/>
+        <v>208</v>
+      </c>
+      <c r="O52" s="11"/>
+      <c r="P52" s="70" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" s="63" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A53" s="76" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="E52" s="70">
+      <c r="E53" s="69">
         <v>5</v>
       </c>
-      <c r="F52" s="62">
+      <c r="F53" s="61">
         <v>40</v>
       </c>
-      <c r="G52" s="10">
-        <f t="shared" si="11"/>
+      <c r="G53" s="10">
+        <f t="shared" si="7"/>
         <v>1680</v>
       </c>
-      <c r="H52" s="10">
-        <v>42</v>
-      </c>
-      <c r="I52" s="10">
+      <c r="H53" s="10">
+        <v>42</v>
+      </c>
+      <c r="I53" s="10">
         <v>2.75</v>
       </c>
-      <c r="J52" s="9">
+      <c r="J53" s="9">
         <v>3.38</v>
       </c>
-      <c r="K52" s="75">
+      <c r="K53" s="74">
         <f t="shared" si="1"/>
         <v>0.22909090909090901</v>
       </c>
-      <c r="L52" s="9">
-        <f t="shared" si="12"/>
+      <c r="L53" s="9">
+        <f t="shared" si="8"/>
         <v>16.899999999999999</v>
       </c>
-      <c r="M52" s="10"/>
-      <c r="N52" s="9">
-        <f t="shared" si="13"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="9">
+        <f t="shared" si="9"/>
         <v>135.19999999999999</v>
       </c>
-      <c r="O52" s="11"/>
-      <c r="P52" s="71" t="s">
+      <c r="O53" s="11"/>
+      <c r="P53" s="70" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="64" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A53" s="77" t="s">
+    <row r="54" spans="1:16" s="63" customFormat="1" ht="20.25" customHeight="1">
+      <c r="A54" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B53" s="89" t="s">
+      <c r="B54" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C54" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="70" t="s">
+      <c r="D54" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="E53" s="70">
+      <c r="E54" s="69">
         <v>5</v>
       </c>
-      <c r="F53" s="62">
+      <c r="F54" s="61">
         <v>40</v>
       </c>
-      <c r="G53" s="10">
-        <f t="shared" si="11"/>
+      <c r="G54" s="10">
+        <f t="shared" si="7"/>
         <v>1680</v>
       </c>
-      <c r="H53" s="10">
-        <v>42</v>
-      </c>
-      <c r="I53" s="10">
+      <c r="H54" s="10">
+        <v>42</v>
+      </c>
+      <c r="I54" s="10">
         <v>2.7</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J54" s="9">
         <v>3.78</v>
       </c>
-      <c r="K53" s="75">
+      <c r="K54" s="74">
         <f t="shared" si="1"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="L53" s="9">
-        <f t="shared" si="12"/>
+      <c r="L54" s="9">
+        <f t="shared" si="8"/>
         <v>18.899999999999999</v>
       </c>
-      <c r="M53" s="10"/>
-      <c r="N53" s="9">
-        <f t="shared" si="13"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="9">
+        <f t="shared" si="9"/>
         <v>151.19999999999999</v>
       </c>
-      <c r="O53" s="11"/>
-      <c r="P53" s="71" t="s">
+      <c r="O54" s="11"/>
+      <c r="P54" s="70" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="64" customFormat="1" ht="18" customHeight="1">
-      <c r="A54" s="77" t="s">
+    <row r="55" spans="1:16" s="63" customFormat="1" ht="18" customHeight="1">
+      <c r="A55" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B54" s="89" t="s">
+      <c r="B55" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C55" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D54" s="70" t="s">
+      <c r="D55" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="E54" s="70">
+      <c r="E55" s="69">
         <v>5</v>
       </c>
-      <c r="F54" s="62">
+      <c r="F55" s="61">
         <v>40</v>
       </c>
-      <c r="G54" s="10">
-        <f t="shared" si="11"/>
+      <c r="G55" s="10">
+        <f t="shared" si="7"/>
         <v>1680</v>
       </c>
-      <c r="H54" s="10">
-        <v>42</v>
-      </c>
-      <c r="I54" s="10">
+      <c r="H55" s="10">
+        <v>42</v>
+      </c>
+      <c r="I55" s="10">
         <v>2.58</v>
       </c>
-      <c r="J54" s="9">
+      <c r="J55" s="9">
         <v>3.65</v>
       </c>
-      <c r="K54" s="75">
+      <c r="K55" s="74">
         <f t="shared" si="1"/>
         <v>0.41472868217054248</v>
       </c>
-      <c r="L54" s="9">
-        <f t="shared" si="12"/>
+      <c r="L55" s="9">
+        <f t="shared" si="8"/>
         <v>18.25</v>
       </c>
-      <c r="M54" s="10"/>
-      <c r="N54" s="9">
-        <f t="shared" si="13"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="9">
+        <f>J55*F55</f>
         <v>146</v>
       </c>
-      <c r="O54" s="11"/>
-      <c r="P54" s="71" t="s">
+      <c r="O55" s="11"/>
+      <c r="P55" s="70" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A55" s="77" t="s">
+    <row r="56" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A56" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B55" s="89" t="s">
+      <c r="B56" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="C55" s="30" t="s">
+      <c r="C56" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D55" s="70" t="s">
+      <c r="D56" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="70">
+      <c r="E56" s="69">
         <v>5</v>
       </c>
-      <c r="F55" s="62">
+      <c r="F56" s="61">
         <v>40</v>
       </c>
-      <c r="G55" s="10">
-        <f t="shared" si="11"/>
+      <c r="G56" s="10">
+        <f t="shared" si="7"/>
         <v>1680</v>
       </c>
-      <c r="H55" s="10">
-        <v>42</v>
-      </c>
-      <c r="I55" s="10">
+      <c r="H56" s="10">
+        <v>42</v>
+      </c>
+      <c r="I56" s="10">
         <v>1.7</v>
       </c>
-      <c r="J55" s="9">
+      <c r="J56" s="9">
         <v>2.7</v>
       </c>
-      <c r="K55" s="75">
+      <c r="K56" s="74">
         <f t="shared" si="1"/>
         <v>0.58823529411764719</v>
       </c>
-      <c r="L55" s="9">
-        <f t="shared" si="12"/>
+      <c r="L56" s="9">
+        <f t="shared" si="8"/>
         <v>13.5</v>
       </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="9">
-        <f t="shared" si="13"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="9">
+        <f t="shared" si="9"/>
         <v>108</v>
       </c>
-      <c r="O55" s="11"/>
-      <c r="P55" s="71" t="s">
+      <c r="O56" s="11"/>
+      <c r="P56" s="70" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A56" s="77" t="s">
+    <row r="57" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A57" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B56" s="89" t="s">
+      <c r="B57" s="88" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="30" t="s">
+      <c r="C57" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="70" t="s">
+      <c r="D57" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="E56" s="70">
+      <c r="E57" s="69">
         <v>5</v>
       </c>
-      <c r="F56" s="62">
+      <c r="F57" s="61">
         <v>40</v>
       </c>
-      <c r="G56" s="10">
-        <f t="shared" si="11"/>
+      <c r="G57" s="10">
+        <f t="shared" si="7"/>
         <v>1680</v>
       </c>
-      <c r="H56" s="10">
-        <v>42</v>
-      </c>
-      <c r="I56" s="10">
+      <c r="H57" s="10">
+        <v>42</v>
+      </c>
+      <c r="I57" s="10">
         <v>2.6</v>
       </c>
-      <c r="J56" s="9">
+      <c r="J57" s="9">
         <v>4</v>
       </c>
-      <c r="K56" s="75">
+      <c r="K57" s="74">
         <f t="shared" si="1"/>
         <v>0.53846153846153832</v>
       </c>
-      <c r="L56" s="9">
-        <f t="shared" si="12"/>
+      <c r="L57" s="9">
+        <f t="shared" si="8"/>
         <v>20</v>
-      </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="9">
-        <f t="shared" si="13"/>
-        <v>160</v>
-      </c>
-      <c r="O56" s="11"/>
-      <c r="P56" s="71" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A57" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="B57" s="90" t="s">
-        <v>105</v>
-      </c>
-      <c r="C57" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D57" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="E57" s="70">
-        <v>5</v>
-      </c>
-      <c r="F57" s="62">
-        <v>40</v>
-      </c>
-      <c r="G57" s="10">
-        <f t="shared" si="11"/>
-        <v>1680</v>
-      </c>
-      <c r="H57" s="10">
-        <v>42</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J57" s="9">
-        <f>N57/40</f>
-        <v>7.5</v>
-      </c>
-      <c r="K57" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L57" s="9">
-        <f t="shared" si="12"/>
-        <v>37.5</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="9">
+        <f t="shared" si="9"/>
+        <v>160</v>
+      </c>
+      <c r="O57" s="11"/>
+      <c r="P57" s="70" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A58" s="76" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" s="89" t="s">
+        <v>105</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="E58" s="69">
+        <v>5</v>
+      </c>
+      <c r="F58" s="61">
+        <v>40</v>
+      </c>
+      <c r="G58" s="10">
+        <f t="shared" si="7"/>
+        <v>1680</v>
+      </c>
+      <c r="H58" s="10">
+        <v>42</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J58" s="9">
+        <f>N58/40</f>
+        <v>7.5</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L58" s="9">
+        <f t="shared" si="8"/>
+        <v>37.5</v>
+      </c>
+      <c r="M58" s="10"/>
+      <c r="N58" s="9">
         <v>300</v>
       </c>
-      <c r="O57" s="11"/>
-      <c r="P57" s="44" t="s">
+      <c r="O58" s="11"/>
+      <c r="P58" s="44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:16" s="72" customFormat="1" ht="21">
-      <c r="A58" s="77" t="s">
+    <row r="59" spans="1:16" s="71" customFormat="1" ht="21">
+      <c r="A59" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B58" s="89" t="s">
+      <c r="B59" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="C58" s="30" t="s">
+      <c r="C59" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="D58" s="70" t="s">
+      <c r="D59" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="E58" s="70">
+      <c r="E59" s="69">
         <v>5</v>
       </c>
-      <c r="F58" s="62">
+      <c r="F59" s="61">
         <v>40</v>
       </c>
-      <c r="G58" s="10">
-        <f t="shared" si="11"/>
+      <c r="G59" s="10">
+        <f t="shared" si="7"/>
         <v>1680</v>
       </c>
-      <c r="H58" s="10">
-        <v>42</v>
-      </c>
-      <c r="I58" s="10">
+      <c r="H59" s="10">
+        <v>42</v>
+      </c>
+      <c r="I59" s="10">
         <v>1.58</v>
       </c>
-      <c r="J58" s="9">
+      <c r="J59" s="9">
         <v>3.1</v>
       </c>
-      <c r="K58" s="75">
+      <c r="K59" s="74">
         <f t="shared" si="1"/>
         <v>0.96202531645569622</v>
       </c>
-      <c r="L58" s="9">
-        <f>N58/8</f>
+      <c r="L59" s="9">
+        <f>N59/8</f>
         <v>15.5</v>
-      </c>
-      <c r="M58" s="10"/>
-      <c r="N58" s="9">
-        <f t="shared" si="13"/>
-        <v>124</v>
-      </c>
-      <c r="O58" s="11"/>
-      <c r="P58" s="71" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" s="64" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A59" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="B59" s="89" t="s">
-        <v>110</v>
-      </c>
-      <c r="C59" s="96"/>
-      <c r="D59" s="70" t="s">
-        <v>111</v>
-      </c>
-      <c r="E59" s="70">
-        <v>5</v>
-      </c>
-      <c r="F59" s="62">
-        <v>40</v>
-      </c>
-      <c r="G59" s="10">
-        <f t="shared" si="11"/>
-        <v>1680</v>
-      </c>
-      <c r="H59" s="10">
-        <v>42</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J59" s="9">
-        <v>4</v>
-      </c>
-      <c r="K59" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L59" s="9">
-        <f t="shared" si="12"/>
-        <v>20</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
+        <v>124</v>
+      </c>
+      <c r="O59" s="11"/>
+      <c r="P59" s="70" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A60" s="76" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" s="88" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" s="95"/>
+      <c r="D60" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="E60" s="69">
+        <v>5</v>
+      </c>
+      <c r="F60" s="61">
+        <v>40</v>
+      </c>
+      <c r="G60" s="10">
+        <f t="shared" si="7"/>
+        <v>1680</v>
+      </c>
+      <c r="H60" s="10">
+        <v>42</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J60" s="9">
+        <v>4</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L60" s="9">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="M60" s="10"/>
+      <c r="N60" s="9">
+        <f t="shared" si="9"/>
         <v>160</v>
       </c>
-      <c r="O59" s="11"/>
-      <c r="P59" s="71" t="s">
+      <c r="O60" s="11"/>
+      <c r="P60" s="70" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.36" right="0.36" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="48" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup scale="47" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Products Price table Web.xlsx
+++ b/Products Price table Web.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C68133D-CA5A-494A-98A5-28641BE69488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F81E8CD-6FDB-413A-9282-DA17A2AB6530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
   </bookViews>
   <sheets>
     <sheet name="Item Classification 7.14.26" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item Classification 7.14.26'!$A$1:$R$67</definedName>
     <definedName name="ITEM_DDOWN">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Item Classification 7.14.26'!$A$1:$P$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Item Classification 7.14.26'!$A$1:$P$67</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Item Classification 7.14.26'!$1:$1</definedName>
     <definedName name="TOFU">#REF!</definedName>
     <definedName name="VENDOR_DDOWN">#REF!</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="126">
   <si>
     <t>Items</t>
   </si>
@@ -421,6 +422,12 @@
   </si>
   <si>
     <t>Wang-TX</t>
+  </si>
+  <si>
+    <t>Pork Fritter XXL</t>
+  </si>
+  <si>
+    <t>PFR0020</t>
   </si>
 </sst>
 </file>
@@ -749,7 +756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -902,9 +909,6 @@
     <xf numFmtId="164" fontId="7" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1030,29 +1034,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1373,31 +1401,31 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.140625" customWidth="1"/>
     <col min="3" max="3" width="44.140625" style="1" customWidth="1"/>
     <col min="4" max="5" width="11.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="6" max="6" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" style="2" customWidth="1"/>
     <col min="9" max="9" width="25.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" style="3" customWidth="1"/>
     <col min="11" max="11" width="20.140625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" style="110" customWidth="1"/>
     <col min="15" max="15" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="18.75">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="76" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -1418,13 +1446,13 @@
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="72" t="s">
+      <c r="I1" s="71" t="s">
         <v>120</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="73" t="s">
+      <c r="K1" s="72" t="s">
         <v>121</v>
       </c>
       <c r="L1" s="6" t="s">
@@ -1433,7 +1461,7 @@
       <c r="M1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="102" t="s">
         <v>10</v>
       </c>
       <c r="O1" s="6" t="s">
@@ -1444,10 +1472,10 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="74" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1476,7 +1504,7 @@
         <f>N2/F2</f>
         <v>8</v>
       </c>
-      <c r="K2" s="74">
+      <c r="K2" s="73">
         <f>J2/I2-1</f>
         <v>1.7118644067796609</v>
       </c>
@@ -1487,7 +1515,7 @@
       <c r="M2" s="10">
         <v>65</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="103">
         <v>200</v>
       </c>
       <c r="O2" s="11"/>
@@ -1496,10 +1524,10 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="74" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -1528,7 +1556,7 @@
         <f>N3/F2</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="K3" s="74">
+      <c r="K3" s="73">
         <f>J3/I2-1</f>
         <v>2.1186440677966099</v>
       </c>
@@ -1539,7 +1567,7 @@
       <c r="M3" s="10">
         <v>65</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="103">
         <v>230</v>
       </c>
       <c r="O3" s="11"/>
@@ -1548,10 +1576,10 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="74" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -1580,7 +1608,7 @@
         <f>N4/F4</f>
         <v>3.9</v>
       </c>
-      <c r="K4" s="74">
+      <c r="K4" s="73">
         <f>J4/I4-1</f>
         <v>0.28712871287128716</v>
       </c>
@@ -1591,7 +1619,7 @@
       <c r="M4" s="10">
         <v>26</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="103">
         <v>93.6</v>
       </c>
       <c r="O4" s="9">
@@ -1602,10 +1630,10 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="74" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -1634,7 +1662,7 @@
         <f>N5/F5</f>
         <v>8</v>
       </c>
-      <c r="K5" s="74">
+      <c r="K5" s="73">
         <f>J5/I5-1</f>
         <v>1.7972027972027975</v>
       </c>
@@ -1645,7 +1673,7 @@
       <c r="M5" s="10">
         <v>65</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="103">
         <v>200</v>
       </c>
       <c r="O5" s="11"/>
@@ -1654,10 +1682,10 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="74" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -1686,7 +1714,7 @@
         <f>N6/F5</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="K6" s="74">
+      <c r="K6" s="73">
         <f>J6/I5-1</f>
         <v>2.2167832167832167</v>
       </c>
@@ -1697,7 +1725,7 @@
       <c r="M6" s="10">
         <v>65</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="103">
         <v>230</v>
       </c>
       <c r="O6" s="11"/>
@@ -1706,10 +1734,10 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="74" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1738,8 +1766,8 @@
         <f>N7/F7</f>
         <v>3.9</v>
       </c>
-      <c r="K7" s="74">
-        <f t="shared" ref="K7:K59" si="1">J7/I7-1</f>
+      <c r="K7" s="73">
+        <f t="shared" ref="K7:K66" si="1">J7/I7-1</f>
         <v>0.28712871287128716</v>
       </c>
       <c r="L7" s="9">
@@ -1749,7 +1777,7 @@
       <c r="M7" s="10">
         <v>26</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="103">
         <v>93.6</v>
       </c>
       <c r="O7" s="9">
@@ -1760,10 +1788,10 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="79" t="s">
+      <c r="B8" s="78" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -1779,7 +1807,7 @@
         <v>24</v>
       </c>
       <c r="G8" s="10">
-        <f t="shared" ref="G8:G14" si="2">F8*42</f>
+        <f t="shared" ref="G8:G15" si="2">F8*42</f>
         <v>1008</v>
       </c>
       <c r="H8" s="10">
@@ -1802,7 +1830,7 @@
       <c r="M8" s="10">
         <v>26</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="103">
         <v>124.8</v>
       </c>
       <c r="O8" s="9">
@@ -1816,7 +1844,7 @@
       <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="79" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -1844,7 +1872,7 @@
       <c r="J9" s="21">
         <v>4.8</v>
       </c>
-      <c r="K9" s="74">
+      <c r="K9" s="73">
         <f t="shared" si="1"/>
         <v>0.71428571428571441</v>
       </c>
@@ -1853,7 +1881,7 @@
         <v>4.8</v>
       </c>
       <c r="M9" s="20"/>
-      <c r="N9" s="21">
+      <c r="N9" s="104">
         <f>J9*30</f>
         <v>144</v>
       </c>
@@ -1866,10 +1894,10 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="76" t="s">
+      <c r="B10" s="75" t="s">
         <v>112</v>
       </c>
       <c r="C10" s="23" t="s">
@@ -1899,8 +1927,8 @@
         <v>34</v>
       </c>
       <c r="L10" s="46"/>
-      <c r="M10" s="90"/>
-      <c r="N10" s="27">
+      <c r="M10" s="89"/>
+      <c r="N10" s="105">
         <v>95.4</v>
       </c>
       <c r="O10" s="27"/>
@@ -1910,10 +1938,10 @@
       <c r="R10" s="29"/>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="75" t="s">
         <v>113</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -1938,16 +1966,16 @@
       <c r="I11" s="20">
         <v>3.18</v>
       </c>
-      <c r="J11" s="94">
+      <c r="J11" s="93">
         <v>4.875</v>
       </c>
-      <c r="K11" s="74">
+      <c r="K11" s="73">
         <f t="shared" si="1"/>
         <v>0.53301886792452824</v>
       </c>
       <c r="L11" s="46"/>
-      <c r="M11" s="90"/>
-      <c r="N11" s="21">
+      <c r="M11" s="89"/>
+      <c r="N11" s="104">
         <v>97.5</v>
       </c>
       <c r="O11" s="21"/>
@@ -1957,10 +1985,10 @@
       <c r="R11" s="29"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="75" t="s">
         <v>114</v>
       </c>
       <c r="C12" s="30" t="s">
@@ -1989,13 +2017,13 @@
         <f>N12/F12</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="K12" s="74">
+      <c r="K12" s="73">
         <f t="shared" si="1"/>
         <v>0.60278745644599274</v>
       </c>
       <c r="L12" s="32"/>
-      <c r="M12" s="91"/>
-      <c r="N12" s="81">
+      <c r="M12" s="90"/>
+      <c r="N12" s="80">
         <v>92</v>
       </c>
       <c r="O12" s="32"/>
@@ -2004,10 +2032,10 @@
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="75" t="s">
         <v>114</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -2036,13 +2064,13 @@
         <f>N13/F13</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="K13" s="74">
+      <c r="K13" s="73">
         <f>J12/I12-1</f>
         <v>0.60278745644599274</v>
       </c>
       <c r="L13" s="35"/>
-      <c r="M13" s="92"/>
-      <c r="N13" s="81">
+      <c r="M13" s="91"/>
+      <c r="N13" s="80">
         <v>92</v>
       </c>
       <c r="O13" s="35"/>
@@ -2051,17 +2079,17 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="76" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="75" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>34</v>
@@ -2070,132 +2098,131 @@
         <v>20</v>
       </c>
       <c r="G14" s="7">
+        <f>F14*42</f>
+        <v>840</v>
+      </c>
+      <c r="H14" s="13">
+        <v>42</v>
+      </c>
+      <c r="I14" s="7">
+        <v>2.87</v>
+      </c>
+      <c r="J14" s="31">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K14" s="73">
+        <f>J13/I13-1</f>
+        <v>0.60278745644599274</v>
+      </c>
+      <c r="L14" s="35"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="80">
+        <v>92</v>
+      </c>
+      <c r="O14" s="35"/>
+      <c r="P14" s="101" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A15" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="75" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="7">
+        <v>20</v>
+      </c>
+      <c r="G15" s="7">
         <f t="shared" si="2"/>
         <v>840</v>
       </c>
-      <c r="H14" s="7">
-        <v>42</v>
-      </c>
-      <c r="I14" s="7">
+      <c r="H15" s="7">
+        <v>42</v>
+      </c>
+      <c r="I15" s="7">
         <v>2.87</v>
       </c>
-      <c r="J14" s="9">
-        <f>N14/F14</f>
+      <c r="J15" s="9">
+        <f>N15/F15</f>
         <v>4.5</v>
       </c>
-      <c r="K14" s="74">
+      <c r="K15" s="73">
         <f t="shared" si="1"/>
         <v>0.56794425087108014</v>
       </c>
-      <c r="L14" s="11"/>
-      <c r="M14" s="93"/>
-      <c r="N14" s="9">
+      <c r="L15" s="11"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="103">
         <v>90</v>
       </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="36" t="s">
+      <c r="O15" s="11"/>
+      <c r="P15" s="36" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A15" s="76" t="s">
+    <row r="16" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A16" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="76" t="s">
+      <c r="B16" s="75" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="7">
         <v>20</v>
       </c>
-      <c r="G15" s="7">
-        <f t="shared" ref="G15:G23" si="3">F15*42</f>
+      <c r="G16" s="7">
+        <f t="shared" ref="G16:G27" si="3">F16*42</f>
         <v>840</v>
       </c>
-      <c r="H15" s="7">
-        <v>42</v>
-      </c>
-      <c r="I15" s="7">
+      <c r="H16" s="7">
+        <v>42</v>
+      </c>
+      <c r="I16" s="7">
         <v>2.87</v>
       </c>
-      <c r="J15" s="9">
-        <f>N15/F14</f>
+      <c r="J16" s="9">
+        <f>N16/F15</f>
         <v>5.4</v>
       </c>
-      <c r="K15" s="74">
-        <f>J15/I14-1</f>
+      <c r="K16" s="73">
+        <f>J16/I15-1</f>
         <v>0.88153310104529625</v>
       </c>
-      <c r="L15" s="11"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="9">
+      <c r="L16" s="11"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="103">
         <v>108</v>
       </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="15" t="s">
+      <c r="O16" s="11"/>
+      <c r="P16" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A16" s="76" t="s">
+    <row r="17" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A17" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="76" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="7">
-        <v>15</v>
-      </c>
-      <c r="G16" s="7">
-        <f t="shared" si="3"/>
-        <v>630</v>
-      </c>
-      <c r="H16" s="10">
-        <v>42</v>
-      </c>
-      <c r="I16" s="7">
-        <v>3.1</v>
-      </c>
-      <c r="J16" s="9">
-        <f>N16/F16</f>
-        <v>5.3</v>
-      </c>
-      <c r="K16" s="74">
-        <f t="shared" si="1"/>
-        <v>0.70967741935483852</v>
-      </c>
-      <c r="L16" s="11"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="9">
-        <v>79.5</v>
-      </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A17" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="76" t="s">
+      <c r="B17" s="75" t="s">
         <v>116</v>
       </c>
       <c r="C17" s="30" t="s">
@@ -2220,29 +2247,29 @@
       <c r="I17" s="7">
         <v>3.1</v>
       </c>
-      <c r="J17" s="31">
-        <f>N17/F16</f>
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="K17" s="74">
-        <f>J17/I16-1</f>
-        <v>0.5</v>
-      </c>
-      <c r="L17" s="32"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="81">
-        <v>69.75</v>
+      <c r="J17" s="9">
+        <f>N17/F17</f>
+        <v>5.3</v>
+      </c>
+      <c r="K17" s="73">
+        <f t="shared" si="1"/>
+        <v>0.70967741935483852</v>
+      </c>
+      <c r="L17" s="11"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="103">
+        <v>79.5</v>
       </c>
       <c r="O17" s="11"/>
-      <c r="P17" s="12" t="s">
-        <v>17</v>
+      <c r="P17" s="33" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A18" s="76" t="s">
+      <c r="A18" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="75" t="s">
         <v>116</v>
       </c>
       <c r="C18" s="30" t="s">
@@ -2271,512 +2298,511 @@
         <f>N18/F17</f>
         <v>4.6500000000000004</v>
       </c>
-      <c r="K18" s="74">
-        <f>J17/I16-1</f>
+      <c r="K18" s="73">
+        <f>J18/I17-1</f>
         <v>0.5</v>
       </c>
-      <c r="L18" s="35"/>
-      <c r="M18" s="92"/>
-      <c r="N18" s="81">
+      <c r="L18" s="32"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="80">
         <v>69.75</v>
       </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="28" t="s">
-        <v>32</v>
+      <c r="P18" s="12" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="75" t="s">
         <v>116</v>
       </c>
       <c r="C19" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="7">
+        <v>15</v>
+      </c>
+      <c r="G19" s="7">
+        <f t="shared" si="3"/>
+        <v>630</v>
+      </c>
+      <c r="H19" s="7">
+        <v>42</v>
+      </c>
+      <c r="I19" s="7">
+        <v>3.1</v>
+      </c>
+      <c r="J19" s="9">
+        <f>N19/F18</f>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="K19" s="73">
+        <f>J18/I17-1</f>
+        <v>0.5</v>
+      </c>
+      <c r="L19" s="35"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="80">
+        <v>69.75</v>
+      </c>
+      <c r="O19" s="11"/>
+      <c r="P19" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A20" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="75" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E20" s="10">
         <v>1.4</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F20" s="10">
         <v>14</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G20" s="10">
         <f t="shared" si="3"/>
         <v>588</v>
       </c>
-      <c r="H19" s="10">
-        <v>42</v>
-      </c>
-      <c r="I19" s="7">
+      <c r="H20" s="10">
+        <v>42</v>
+      </c>
+      <c r="I20" s="7">
         <v>3.1</v>
       </c>
-      <c r="J19" s="34">
-        <f>N19/14</f>
+      <c r="J20" s="34">
+        <f>N20/14</f>
         <v>4.7</v>
       </c>
-      <c r="K19" s="74">
-        <f>J19/I16-1</f>
+      <c r="K20" s="73">
+        <f>J20/I17-1</f>
         <v>0.5161290322580645</v>
       </c>
-      <c r="L19" s="34">
-        <f>N19/10</f>
+      <c r="L20" s="34">
+        <f>N20/10</f>
         <v>6.58</v>
       </c>
-      <c r="M19" s="14"/>
-      <c r="N19" s="34">
+      <c r="M20" s="14"/>
+      <c r="N20" s="106">
         <v>65.8</v>
       </c>
-      <c r="O19" s="11"/>
-      <c r="P19" s="18" t="s">
+      <c r="O20" s="11"/>
+      <c r="P20" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="R19" s="29"/>
-    </row>
-    <row r="20" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A20" s="76" t="s">
+      <c r="R20" s="29"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A21" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="80" t="s">
+      <c r="B21" s="75" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="10">
+        <v>15</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" si="3"/>
+        <v>630</v>
+      </c>
+      <c r="H21" s="10">
+        <v>42</v>
+      </c>
+      <c r="I21" s="7">
+        <v>3.1</v>
+      </c>
+      <c r="J21" s="34">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="K21" s="73">
+        <f>J21/I18-1</f>
+        <v>0.5</v>
+      </c>
+      <c r="L21" s="34"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="106">
+        <v>69.75</v>
+      </c>
+      <c r="O21" s="11"/>
+      <c r="P21" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="R21" s="29"/>
+    </row>
+    <row r="22" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A22" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="75" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="10">
+        <v>15</v>
+      </c>
+      <c r="G22" s="10">
+        <f t="shared" ref="G22" si="4">F22*42</f>
+        <v>630</v>
+      </c>
+      <c r="H22" s="10">
+        <v>42</v>
+      </c>
+      <c r="I22" s="7">
+        <v>3.1</v>
+      </c>
+      <c r="J22" s="34">
+        <v>5.3</v>
+      </c>
+      <c r="K22" s="73">
+        <f>J22/I22-1</f>
+        <v>0.70967741935483852</v>
+      </c>
+      <c r="L22" s="34"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="106">
+        <v>79.5</v>
+      </c>
+      <c r="O22" s="11"/>
+      <c r="P22" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="R22" s="29"/>
+    </row>
+    <row r="23" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A23" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C23" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="7">
+      <c r="D23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="10">
         <v>20</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G23" s="10">
         <f t="shared" si="3"/>
         <v>840</v>
       </c>
-      <c r="H20" s="10">
-        <v>42</v>
-      </c>
-      <c r="I20" s="7">
+      <c r="H23" s="10">
+        <v>42</v>
+      </c>
+      <c r="I23" s="7">
         <v>3.92</v>
       </c>
-      <c r="J20" s="9">
-        <f>N20/F$20</f>
+      <c r="J23" s="9">
+        <f>N23/F$23</f>
         <v>5</v>
       </c>
-      <c r="K20" s="74">
+      <c r="K23" s="73">
         <f t="shared" si="1"/>
         <v>0.27551020408163263</v>
       </c>
-      <c r="L20" s="9"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="9">
+      <c r="L23" s="9"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="103">
         <v>100</v>
       </c>
-      <c r="O20" s="11"/>
-      <c r="P20" s="38" t="s">
+      <c r="O23" s="11"/>
+      <c r="P23" s="38" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A21" s="76" t="s">
+    <row r="24" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A24" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="80" t="s">
+      <c r="B24" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C24" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="7">
+      <c r="D24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="10">
         <v>20</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G24" s="10">
+        <f t="shared" ref="G24" si="5">F24*42</f>
+        <v>840</v>
+      </c>
+      <c r="H24" s="10">
+        <v>42</v>
+      </c>
+      <c r="I24" s="7">
+        <v>3.92</v>
+      </c>
+      <c r="J24" s="31">
+        <v>5.6</v>
+      </c>
+      <c r="K24" s="73">
+        <f>J24/I21-1</f>
+        <v>0.80645161290322553</v>
+      </c>
+      <c r="L24" s="9"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="80">
+        <v>112</v>
+      </c>
+      <c r="O24" s="11"/>
+      <c r="P24" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A25" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="7">
+        <v>20</v>
+      </c>
+      <c r="G25" s="7">
         <f t="shared" si="3"/>
         <v>840</v>
       </c>
-      <c r="H21" s="10">
-        <v>42</v>
-      </c>
-      <c r="I21" s="7">
+      <c r="H25" s="10">
+        <v>42</v>
+      </c>
+      <c r="I25" s="7">
         <v>3.92</v>
       </c>
-      <c r="J21" s="31">
-        <f>N21/F$20</f>
+      <c r="J25" s="31">
+        <f>N25/F$23</f>
         <v>5.6</v>
       </c>
-      <c r="K21" s="74">
-        <f>J21/I20-1</f>
+      <c r="K25" s="73">
+        <f>J25/I23-1</f>
         <v>0.4285714285714286</v>
       </c>
-      <c r="L21" s="31"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="81">
+      <c r="L25" s="9"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="80">
         <v>112</v>
       </c>
-      <c r="O21" s="11"/>
-      <c r="P21" s="39" t="s">
+      <c r="O25" s="11"/>
+      <c r="P25" s="39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A22" s="76" t="s">
+    <row r="26" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A26" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B26" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C26" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="D26" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="7">
         <v>20</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G26" s="7">
         <f t="shared" si="3"/>
         <v>840</v>
       </c>
-      <c r="H22" s="13">
-        <v>42</v>
-      </c>
-      <c r="I22" s="7">
+      <c r="H26" s="13">
+        <v>42</v>
+      </c>
+      <c r="I26" s="7">
         <v>3.92</v>
       </c>
-      <c r="J22" s="31">
-        <f>N22/F$20</f>
+      <c r="J26" s="31">
+        <f>N26/F$23</f>
         <v>5.6</v>
       </c>
-      <c r="K22" s="74">
-        <f>J21/I20-1</f>
+      <c r="K26" s="73">
+        <f>J25/I23-1</f>
         <v>0.4285714285714286</v>
       </c>
-      <c r="L22" s="34"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="81">
+      <c r="L26" s="34"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="80">
         <v>112</v>
       </c>
-      <c r="O22" s="11"/>
-      <c r="P22" s="28" t="s">
+      <c r="O26" s="11"/>
+      <c r="P26" s="28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A23" s="76" t="s">
+    <row r="27" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A27" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="80" t="s">
+      <c r="B27" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C27" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="D27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="7">
         <v>20</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G27" s="7">
         <f t="shared" si="3"/>
         <v>840</v>
       </c>
-      <c r="H23" s="13">
-        <v>42</v>
-      </c>
-      <c r="I23" s="7">
+      <c r="H27" s="13">
+        <v>42</v>
+      </c>
+      <c r="I27" s="7">
         <v>3.92</v>
       </c>
-      <c r="J23" s="9">
-        <f>N23/F$20</f>
+      <c r="J27" s="9">
+        <f>N27/F$23</f>
         <v>5.95</v>
       </c>
-      <c r="K23" s="74">
-        <f>J23/I20-1</f>
+      <c r="K27" s="73">
+        <f>J27/I23-1</f>
         <v>0.51785714285714302</v>
-      </c>
-      <c r="L23" s="9"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="9">
-        <v>119</v>
-      </c>
-      <c r="O23" s="11"/>
-      <c r="P23" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A24" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="80" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="10">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10">
-        <v>18</v>
-      </c>
-      <c r="G24" s="10">
-        <f>F24*36</f>
-        <v>648</v>
-      </c>
-      <c r="H24" s="10">
-        <v>42</v>
-      </c>
-      <c r="I24" s="7">
-        <v>7.92</v>
-      </c>
-      <c r="J24" s="9">
-        <f>N24/F24</f>
-        <v>5.83</v>
-      </c>
-      <c r="K24" s="74">
-        <f>J24/I20-1</f>
-        <v>0.48724489795918369</v>
-      </c>
-      <c r="L24" s="9">
-        <f>N24/18</f>
-        <v>5.83</v>
-      </c>
-      <c r="M24" s="10"/>
-      <c r="N24" s="9">
-        <v>104.94</v>
-      </c>
-      <c r="O24" s="9">
-        <f>5.66*F24</f>
-        <v>101.88</v>
-      </c>
-      <c r="P24" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A25" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="7">
-        <v>20</v>
-      </c>
-      <c r="G25" s="10">
-        <f>F25*36</f>
-        <v>720</v>
-      </c>
-      <c r="H25" s="10">
-        <v>42</v>
-      </c>
-      <c r="I25" s="10">
-        <v>3.25</v>
-      </c>
-      <c r="J25" s="9">
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="K25" s="74">
-        <f>J25/I25-1</f>
-        <v>0.49230769230769211</v>
-      </c>
-      <c r="L25" s="9"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="9">
-        <f>J25*20</f>
-        <v>97</v>
-      </c>
-      <c r="O25" s="9"/>
-      <c r="P25" s="28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A26" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="7">
-        <v>20</v>
-      </c>
-      <c r="G26" s="7">
-        <f t="shared" ref="G26:G39" si="4">F26*42</f>
-        <v>840</v>
-      </c>
-      <c r="H26" s="10">
-        <v>42</v>
-      </c>
-      <c r="I26" s="7">
-        <v>3.76</v>
-      </c>
-      <c r="J26" s="9">
-        <f>N26/F26</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="K26" s="74">
-        <f t="shared" si="1"/>
-        <v>0.3563829787234043</v>
-      </c>
-      <c r="L26" s="9"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="9">
-        <v>102</v>
-      </c>
-      <c r="O26" s="11"/>
-      <c r="P26" s="38" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A27" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="7">
-        <v>20</v>
-      </c>
-      <c r="G27" s="7">
-        <f t="shared" si="4"/>
-        <v>840</v>
-      </c>
-      <c r="H27" s="10">
-        <v>42</v>
-      </c>
-      <c r="I27" s="7">
-        <v>3.76</v>
-      </c>
-      <c r="J27" s="9">
-        <f>N27/F$26</f>
-        <v>5.5</v>
-      </c>
-      <c r="K27" s="74">
-        <f>J27/I26-1</f>
-        <v>0.4627659574468086</v>
       </c>
       <c r="L27" s="9"/>
       <c r="M27" s="10"/>
-      <c r="N27" s="9">
-        <v>110</v>
+      <c r="N27" s="103">
+        <v>119</v>
       </c>
       <c r="O27" s="11"/>
-      <c r="P27" s="39" t="s">
-        <v>36</v>
+      <c r="P27" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A28" s="76" t="s">
+      <c r="A28" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="B28" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="D28" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10">
+        <v>18</v>
+      </c>
+      <c r="G28" s="10">
+        <f>F28*36</f>
+        <v>648</v>
+      </c>
+      <c r="H28" s="10">
+        <v>42</v>
+      </c>
+      <c r="I28" s="7">
+        <v>7.92</v>
+      </c>
+      <c r="J28" s="9">
+        <f>N28/F28</f>
+        <v>5.83</v>
+      </c>
+      <c r="K28" s="73">
+        <f>J28/I23-1</f>
+        <v>0.48724489795918369</v>
+      </c>
+      <c r="L28" s="9">
+        <f>N28/18</f>
+        <v>5.83</v>
+      </c>
+      <c r="M28" s="10"/>
+      <c r="N28" s="103">
+        <v>104.94</v>
+      </c>
+      <c r="O28" s="9">
+        <f>5.66*F28</f>
+        <v>101.88</v>
+      </c>
+      <c r="P28" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G28" s="7">
-        <f t="shared" si="4"/>
-        <v>840</v>
-      </c>
-      <c r="H28" s="10">
-        <v>42</v>
-      </c>
-      <c r="I28" s="7">
-        <v>3.76</v>
-      </c>
-      <c r="J28" s="9">
-        <f>N28/F$26</f>
-        <v>6.45</v>
-      </c>
-      <c r="K28" s="74">
-        <f>J28/I26-1</f>
-        <v>0.71542553191489366</v>
-      </c>
-      <c r="L28" s="9"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="9">
-        <v>129</v>
-      </c>
-      <c r="O28" s="35"/>
-      <c r="P28" s="15" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A29" s="76" t="s">
+      <c r="A29" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="7" t="s">
+      <c r="B29" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="37" t="s">
         <v>39</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>34</v>
@@ -2784,46 +2810,46 @@
       <c r="F29" s="7">
         <v>20</v>
       </c>
-      <c r="G29" s="7">
-        <f t="shared" si="4"/>
-        <v>840</v>
+      <c r="G29" s="10">
+        <f>F29*36</f>
+        <v>720</v>
       </c>
       <c r="H29" s="10">
         <v>42</v>
       </c>
-      <c r="I29" s="7">
-        <v>3.76</v>
+      <c r="I29" s="10">
+        <v>3.25</v>
       </c>
       <c r="J29" s="9">
-        <f>N29/F$26</f>
-        <v>6</v>
-      </c>
-      <c r="K29" s="74">
-        <f>J29/I26-1</f>
-        <v>0.59574468085106402</v>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="K29" s="73">
+        <f>J29/I29-1</f>
+        <v>0.49230769230769211</v>
       </c>
       <c r="L29" s="9"/>
       <c r="M29" s="10"/>
-      <c r="N29" s="9">
-        <v>120</v>
-      </c>
-      <c r="O29" s="35"/>
+      <c r="N29" s="103">
+        <f>J29*20</f>
+        <v>97</v>
+      </c>
+      <c r="O29" s="9"/>
       <c r="P29" s="28" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A30" s="76" t="s">
+      <c r="A30" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="85" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="30" t="s">
+      <c r="B30" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>34</v>
@@ -2832,45 +2858,45 @@
         <v>20</v>
       </c>
       <c r="G30" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="G30:G46" si="6">F30*42</f>
         <v>840</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="10">
         <v>42</v>
       </c>
       <c r="I30" s="7">
-        <v>3.91</v>
-      </c>
-      <c r="J30" s="34">
+        <v>3.76</v>
+      </c>
+      <c r="J30" s="9">
         <f>N30/F30</f>
-        <v>5.75</v>
-      </c>
-      <c r="K30" s="74">
-        <f t="shared" si="1"/>
-        <v>0.47058823529411753</v>
-      </c>
-      <c r="L30" s="34"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="9">
-        <v>115</v>
-      </c>
-      <c r="O30" s="35"/>
-      <c r="P30" s="39" t="s">
-        <v>36</v>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="K30" s="73">
+        <f t="shared" ref="K30:K36" si="7">J30/I30-1</f>
+        <v>0.3563829787234043</v>
+      </c>
+      <c r="L30" s="9"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="103">
+        <v>102</v>
+      </c>
+      <c r="O30" s="11"/>
+      <c r="P30" s="38" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A31" s="76" t="s">
+      <c r="A31" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="85" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="30" t="s">
+      <c r="B31" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>34</v>
@@ -2879,45 +2905,44 @@
         <v>20</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="G31" si="8">F31*42</f>
         <v>840</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="10">
         <v>42</v>
       </c>
       <c r="I31" s="7">
-        <v>3.91</v>
-      </c>
-      <c r="J31" s="34">
-        <f>N31/F$30</f>
-        <v>6.75</v>
-      </c>
-      <c r="K31" s="74">
-        <f>J31/I30-1</f>
-        <v>0.7263427109974423</v>
-      </c>
-      <c r="L31" s="34"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="9">
-        <v>135</v>
-      </c>
-      <c r="O31" s="35"/>
-      <c r="P31" s="15" t="s">
-        <v>18</v>
+        <v>3.76</v>
+      </c>
+      <c r="J31" s="9">
+        <v>6.45</v>
+      </c>
+      <c r="K31" s="73">
+        <f t="shared" si="7"/>
+        <v>0.71542553191489366</v>
+      </c>
+      <c r="L31" s="9"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="103">
+        <v>129</v>
+      </c>
+      <c r="O31" s="11"/>
+      <c r="P31" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A32" s="76" t="s">
+      <c r="A32" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="85" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="30" t="s">
+      <c r="B32" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>34</v>
@@ -2926,45 +2951,45 @@
         <v>20</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>840</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="10">
         <v>42</v>
       </c>
       <c r="I32" s="7">
-        <v>3.91</v>
-      </c>
-      <c r="J32" s="34">
+        <v>3.76</v>
+      </c>
+      <c r="J32" s="9">
         <f>N32/F$30</f>
-        <v>6.25</v>
-      </c>
-      <c r="K32" s="74">
-        <f>J32/I30-1</f>
-        <v>0.59846547314577991</v>
-      </c>
-      <c r="L32" s="34"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="9">
-        <v>125</v>
-      </c>
-      <c r="O32" s="35"/>
-      <c r="P32" s="28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A33" s="76" t="s">
+        <v>5.5</v>
+      </c>
+      <c r="K32" s="73">
+        <f t="shared" si="7"/>
+        <v>0.4627659574468086</v>
+      </c>
+      <c r="L32" s="9"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="103">
+        <v>110</v>
+      </c>
+      <c r="O32" s="11"/>
+      <c r="P32" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A33" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="30" t="s">
+      <c r="B33" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>34</v>
@@ -2973,1339 +2998,1667 @@
         <v>20</v>
       </c>
       <c r="G33" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>840</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="10">
         <v>42</v>
       </c>
       <c r="I33" s="7">
+        <v>3.76</v>
+      </c>
+      <c r="J33" s="9">
+        <f>N33/F$30</f>
+        <v>6.45</v>
+      </c>
+      <c r="K33" s="73">
+        <f t="shared" si="7"/>
+        <v>0.71542553191489366</v>
+      </c>
+      <c r="L33" s="9"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="103">
+        <v>129</v>
+      </c>
+      <c r="O33" s="35"/>
+      <c r="P33" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A34" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="7">
+        <v>20</v>
+      </c>
+      <c r="G34" s="7">
+        <f t="shared" si="6"/>
+        <v>840</v>
+      </c>
+      <c r="H34" s="10">
+        <v>42</v>
+      </c>
+      <c r="I34" s="7">
+        <v>3.76</v>
+      </c>
+      <c r="J34" s="9">
+        <f>N34/F$30</f>
+        <v>6</v>
+      </c>
+      <c r="K34" s="73">
+        <f t="shared" si="7"/>
+        <v>0.59574468085106402</v>
+      </c>
+      <c r="L34" s="9"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="103">
+        <v>120</v>
+      </c>
+      <c r="O34" s="35"/>
+      <c r="P34" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A35" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="84" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="7">
+        <v>20</v>
+      </c>
+      <c r="G35" s="7">
+        <f t="shared" ref="G35" si="9">F35*42</f>
+        <v>840</v>
+      </c>
+      <c r="H35" s="14">
+        <v>42</v>
+      </c>
+      <c r="I35" s="7">
+        <v>3.91</v>
+      </c>
+      <c r="J35" s="34">
+        <v>6.75</v>
+      </c>
+      <c r="K35" s="73">
+        <f t="shared" si="7"/>
+        <v>0.7263427109974423</v>
+      </c>
+      <c r="L35" s="34"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="103">
+        <v>135</v>
+      </c>
+      <c r="O35" s="35"/>
+      <c r="P35" s="101" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A36" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="84" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="7">
+        <v>20</v>
+      </c>
+      <c r="G36" s="7">
+        <f t="shared" si="6"/>
+        <v>840</v>
+      </c>
+      <c r="H36" s="14">
+        <v>42</v>
+      </c>
+      <c r="I36" s="7">
+        <v>3.91</v>
+      </c>
+      <c r="J36" s="34">
+        <f>N36/F36</f>
+        <v>5.75</v>
+      </c>
+      <c r="K36" s="73">
+        <f t="shared" si="7"/>
+        <v>0.47058823529411753</v>
+      </c>
+      <c r="L36" s="34"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="103">
+        <v>115</v>
+      </c>
+      <c r="O36" s="35"/>
+      <c r="P36" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A37" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="84" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F37" s="7">
+        <v>20</v>
+      </c>
+      <c r="G37" s="7">
+        <f t="shared" si="6"/>
+        <v>840</v>
+      </c>
+      <c r="H37" s="14">
+        <v>42</v>
+      </c>
+      <c r="I37" s="7">
+        <v>3.91</v>
+      </c>
+      <c r="J37" s="34">
+        <f>N37/F$36</f>
+        <v>6.75</v>
+      </c>
+      <c r="K37" s="73">
+        <f>J37/I36-1</f>
+        <v>0.7263427109974423</v>
+      </c>
+      <c r="L37" s="34"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="103">
+        <v>135</v>
+      </c>
+      <c r="O37" s="35"/>
+      <c r="P37" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A38" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="84" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" s="7">
+        <v>20</v>
+      </c>
+      <c r="G38" s="7">
+        <f t="shared" si="6"/>
+        <v>840</v>
+      </c>
+      <c r="H38" s="14">
+        <v>42</v>
+      </c>
+      <c r="I38" s="7">
+        <v>3.91</v>
+      </c>
+      <c r="J38" s="34">
+        <f>N38/F$36</f>
+        <v>6.25</v>
+      </c>
+      <c r="K38" s="73">
+        <f>J38/I36-1</f>
+        <v>0.59846547314577991</v>
+      </c>
+      <c r="L38" s="34"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="103">
+        <v>125</v>
+      </c>
+      <c r="O38" s="35"/>
+      <c r="P38" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A39" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" s="7">
+        <v>20</v>
+      </c>
+      <c r="G39" s="7">
+        <f t="shared" ref="G39" si="10">F39*42</f>
+        <v>840</v>
+      </c>
+      <c r="H39" s="14">
+        <v>42</v>
+      </c>
+      <c r="I39" s="7">
         <v>4.43</v>
       </c>
-      <c r="J33" s="34">
-        <f>N33/F$33</f>
+      <c r="J39" s="34">
+        <v>6.75</v>
+      </c>
+      <c r="K39" s="73">
+        <f t="shared" si="1"/>
+        <v>0.52370203160270901</v>
+      </c>
+      <c r="L39" s="34"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="103">
+        <v>135</v>
+      </c>
+      <c r="O39" s="35"/>
+      <c r="P39" s="101" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="18.75" customHeight="1">
+      <c r="A40" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" s="7">
+        <v>20</v>
+      </c>
+      <c r="G40" s="7">
+        <f t="shared" si="6"/>
+        <v>840</v>
+      </c>
+      <c r="H40" s="14">
+        <v>42</v>
+      </c>
+      <c r="I40" s="7">
+        <v>4.43</v>
+      </c>
+      <c r="J40" s="34">
+        <f>N40/F$40</f>
         <v>5.75</v>
       </c>
-      <c r="K33" s="74">
+      <c r="K40" s="73">
         <f t="shared" si="1"/>
         <v>0.2979683972911964</v>
       </c>
-      <c r="L33" s="34"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="9">
+      <c r="L40" s="34"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="103">
         <v>115</v>
       </c>
-      <c r="O33" s="11"/>
-      <c r="P33" s="39" t="s">
+      <c r="O40" s="11"/>
+      <c r="P40" s="39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A34" s="76" t="s">
+    <row r="41" spans="1:16" ht="18.75" customHeight="1">
+      <c r="A41" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="85" t="s">
+      <c r="B41" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C41" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D41" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="E41" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F41" s="7">
         <v>20</v>
       </c>
-      <c r="G34" s="7">
-        <f t="shared" si="4"/>
+      <c r="G41" s="7">
+        <f t="shared" si="6"/>
         <v>840</v>
       </c>
-      <c r="H34" s="14">
-        <v>42</v>
-      </c>
-      <c r="I34" s="7">
+      <c r="H41" s="14">
+        <v>42</v>
+      </c>
+      <c r="I41" s="7">
         <v>4.43</v>
       </c>
-      <c r="J34" s="34">
-        <f>N34/F$33</f>
+      <c r="J41" s="34">
+        <f>N41/F$40</f>
         <v>6.75</v>
       </c>
-      <c r="K34" s="74">
-        <f>J34/I33-1</f>
+      <c r="K41" s="73">
+        <f>J41/I40-1</f>
         <v>0.52370203160270901</v>
       </c>
-      <c r="L34" s="34"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="9">
+      <c r="L41" s="34"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="103">
         <v>135</v>
       </c>
-      <c r="O34" s="11"/>
-      <c r="P34" s="15" t="s">
+      <c r="O41" s="11"/>
+      <c r="P41" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A35" s="76" t="s">
+    <row r="42" spans="1:16" ht="18.75" customHeight="1">
+      <c r="A42" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="85" t="s">
+      <c r="B42" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C42" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D42" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="E42" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F42" s="7">
         <v>20</v>
       </c>
-      <c r="G35" s="7">
-        <f t="shared" si="4"/>
+      <c r="G42" s="7">
+        <f t="shared" si="6"/>
         <v>840</v>
       </c>
-      <c r="H35" s="14">
-        <v>42</v>
-      </c>
-      <c r="I35" s="7">
+      <c r="H42" s="14">
+        <v>42</v>
+      </c>
+      <c r="I42" s="7">
         <v>4.43</v>
       </c>
-      <c r="J35" s="34">
-        <f>N35/F$33</f>
+      <c r="J42" s="34">
+        <f>N42/F$40</f>
         <v>6.25</v>
       </c>
-      <c r="K35" s="74">
-        <f>J35/I33-1</f>
+      <c r="K42" s="73">
+        <f>J42/I40-1</f>
         <v>0.4108352144469527</v>
       </c>
-      <c r="L35" s="34"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="9">
+      <c r="L42" s="34"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="103">
         <v>125</v>
       </c>
-      <c r="O35" s="11"/>
-      <c r="P35" s="28" t="s">
+      <c r="O42" s="11"/>
+      <c r="P42" s="28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A36" s="80" t="s">
+    <row r="43" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A43" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="82" t="s">
+      <c r="B43" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C43" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="40" t="s">
+      <c r="D43" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="40">
+      <c r="E43" s="40">
         <v>5</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F43" s="10">
         <v>40</v>
       </c>
-      <c r="G36" s="10">
-        <f t="shared" si="4"/>
+      <c r="G43" s="10">
+        <f t="shared" si="6"/>
         <v>1680</v>
       </c>
-      <c r="H36" s="10">
-        <v>42</v>
-      </c>
-      <c r="I36" s="10">
+      <c r="H43" s="10">
+        <v>42</v>
+      </c>
+      <c r="I43" s="10">
         <v>4.92</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J43" s="9">
         <v>6.5</v>
       </c>
-      <c r="K36" s="74">
+      <c r="K43" s="73">
         <f t="shared" si="1"/>
         <v>0.32113821138211374</v>
       </c>
-      <c r="L36" s="9">
-        <f>N36/8</f>
+      <c r="L43" s="9">
+        <f>N43/8</f>
         <v>32.5</v>
       </c>
-      <c r="M36" s="10"/>
-      <c r="N36" s="9">
-        <f>J36*F36</f>
+      <c r="M43" s="10"/>
+      <c r="N43" s="103">
+        <f>J43*F43</f>
         <v>260</v>
       </c>
-      <c r="O36" s="11"/>
-      <c r="P36" s="41" t="s">
+      <c r="O43" s="11"/>
+      <c r="P43" s="41" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A37" s="80" t="s">
+    <row r="44" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A44" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="82" t="s">
+      <c r="B44" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C44" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="D44" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="40">
+      <c r="E44" s="40">
         <v>5</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F44" s="10">
         <v>40</v>
       </c>
-      <c r="G37" s="10">
-        <f t="shared" si="4"/>
+      <c r="G44" s="10">
+        <f t="shared" si="6"/>
         <v>1680</v>
       </c>
-      <c r="H37" s="10">
-        <v>42</v>
-      </c>
-      <c r="I37" s="10">
+      <c r="H44" s="10">
+        <v>42</v>
+      </c>
+      <c r="I44" s="10">
         <v>4.7300000000000004</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J44" s="9">
         <v>6.5</v>
       </c>
-      <c r="K37" s="74">
+      <c r="K44" s="73">
         <f t="shared" si="1"/>
         <v>0.37420718816067633</v>
       </c>
-      <c r="L37" s="9">
-        <f>N37/8</f>
+      <c r="L44" s="9">
+        <f>N44/8</f>
         <v>32.5</v>
       </c>
-      <c r="M37" s="10"/>
-      <c r="N37" s="9">
-        <f>J37*F37</f>
+      <c r="M44" s="10"/>
+      <c r="N44" s="103">
+        <f>J44*F44</f>
         <v>260</v>
       </c>
-      <c r="O37" s="11"/>
-      <c r="P37" s="41" t="s">
+      <c r="O44" s="11"/>
+      <c r="P44" s="41" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A38" s="76" t="s">
+    <row r="45" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A45" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="83" t="s">
+      <c r="B45" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="42" t="s">
+      <c r="D45" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F38" s="7">
+      <c r="E45" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F45" s="7">
         <v>30</v>
       </c>
-      <c r="G38" s="7">
-        <f t="shared" si="4"/>
+      <c r="G45" s="7">
+        <f t="shared" si="6"/>
         <v>1260</v>
       </c>
-      <c r="H38" s="10">
-        <v>42</v>
-      </c>
-      <c r="I38" s="7">
+      <c r="H45" s="10">
+        <v>42</v>
+      </c>
+      <c r="I45" s="7">
         <v>4.84</v>
       </c>
-      <c r="J38" s="9">
-        <f>N38/F38</f>
+      <c r="J45" s="9">
+        <f>N45/F45</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="K38" s="74">
+      <c r="K45" s="73">
         <f t="shared" si="1"/>
         <v>0.30853994490358128</v>
       </c>
-      <c r="L38" s="9"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="9">
+      <c r="L45" s="9"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="103">
         <v>190</v>
       </c>
-      <c r="O38" s="43"/>
-      <c r="P38" s="44" t="s">
+      <c r="O45" s="43"/>
+      <c r="P45" s="44" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A39" s="76" t="s">
+    <row r="46" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A46" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="83" t="s">
+      <c r="B46" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C46" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="42" t="s">
+      <c r="D46" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="7">
+      <c r="E46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" s="7">
         <v>30</v>
       </c>
-      <c r="G39" s="7">
-        <f t="shared" si="4"/>
+      <c r="G46" s="7">
+        <f t="shared" si="6"/>
         <v>1260</v>
       </c>
-      <c r="H39" s="10">
-        <v>42</v>
-      </c>
-      <c r="I39" s="7">
+      <c r="H46" s="10">
+        <v>42</v>
+      </c>
+      <c r="I46" s="7">
         <v>4.84</v>
       </c>
-      <c r="J39" s="9">
-        <f>N39/F38</f>
+      <c r="J46" s="9">
+        <f>N46/F45</f>
         <v>5.75</v>
       </c>
-      <c r="K39" s="74">
-        <f>J39/I38-1</f>
+      <c r="K46" s="73">
+        <f>J46/I45-1</f>
         <v>0.18801652892561993</v>
       </c>
-      <c r="L39" s="31"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="31">
+      <c r="L46" s="31"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="80">
         <v>172.5</v>
       </c>
-      <c r="O39" s="46"/>
-      <c r="P39" s="39" t="s">
+      <c r="O46" s="46"/>
+      <c r="P46" s="39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A40" s="76" t="s">
+    <row r="47" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A47" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="83" t="s">
+      <c r="B47" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D40" s="42" t="s">
+      <c r="D47" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E47" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F47" s="7">
         <f>18*1.1</f>
         <v>19.8</v>
       </c>
-      <c r="G40" s="7">
-        <f t="shared" ref="G40:G47" si="5">F40*42</f>
+      <c r="G47" s="7">
+        <f t="shared" ref="G47:G54" si="11">F47*42</f>
         <v>831.6</v>
       </c>
-      <c r="H40" s="7">
-        <v>42</v>
-      </c>
-      <c r="I40" s="7">
+      <c r="H47" s="7">
+        <v>42</v>
+      </c>
+      <c r="I47" s="7">
         <v>5.34</v>
       </c>
-      <c r="J40" s="31">
-        <f>N40/F40</f>
+      <c r="J47" s="31">
+        <f>N47/F47</f>
         <v>5.954545454545455</v>
       </c>
-      <c r="K40" s="74">
+      <c r="K47" s="73">
         <f t="shared" si="1"/>
         <v>0.11508341845420511</v>
       </c>
-      <c r="L40" s="31">
-        <f>N40/18</f>
+      <c r="L47" s="31">
+        <f>N47/18</f>
         <v>6.5500000000000007</v>
       </c>
-      <c r="M40" s="7"/>
-      <c r="N40" s="31">
+      <c r="M47" s="7"/>
+      <c r="N47" s="80">
         <v>117.9</v>
       </c>
-      <c r="O40" s="31">
+      <c r="O47" s="31">
         <f>6.36*18</f>
         <v>114.48</v>
       </c>
-      <c r="P40" s="47" t="s">
+      <c r="P47" s="47" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A41" s="76" t="s">
+    <row r="48" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A48" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B41" s="83" t="s">
+      <c r="B48" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="96" t="s">
+      <c r="D48" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="97" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="98">
+      <c r="E48" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F48" s="60">
         <v>30</v>
       </c>
-      <c r="G41" s="98">
-        <f t="shared" ref="G41" si="6">F41*42</f>
+      <c r="G48" s="60">
+        <f t="shared" ref="G48" si="12">F48*42</f>
         <v>1260</v>
       </c>
-      <c r="H41" s="98">
-        <v>42</v>
-      </c>
-      <c r="I41" s="99" t="s">
-        <v>34</v>
-      </c>
-      <c r="J41" s="100">
+      <c r="H48" s="60">
+        <v>42</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" s="96">
         <v>6.35</v>
       </c>
-      <c r="K41" s="99" t="s">
-        <v>34</v>
-      </c>
-      <c r="L41" s="100"/>
-      <c r="M41" s="98"/>
-      <c r="N41" s="9">
-        <f>J41*F41</f>
+      <c r="K48" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48" s="96"/>
+      <c r="M48" s="60"/>
+      <c r="N48" s="103">
+        <f>J48*F48</f>
         <v>190.5</v>
       </c>
-      <c r="O41" s="101"/>
-      <c r="P41" s="103" t="s">
+      <c r="O48" s="97"/>
+      <c r="P48" s="98" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:16" s="45" customFormat="1" ht="15.6" customHeight="1">
-      <c r="A42" s="76" t="s">
+    <row r="49" spans="1:16" s="45" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A49" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="87" t="s">
+      <c r="B49" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="48" t="s">
+      <c r="C49" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="D42" s="49" t="s">
+      <c r="D49" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="E42" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="F42" s="50">
+      <c r="E49" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="F49" s="50">
         <v>30</v>
       </c>
-      <c r="G42" s="50">
-        <f t="shared" si="5"/>
+      <c r="G49" s="50">
+        <f t="shared" si="11"/>
         <v>1260</v>
       </c>
-      <c r="H42" s="50">
-        <v>42</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J42" s="51">
+      <c r="H49" s="50">
+        <v>42</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="51">
         <v>5.15</v>
       </c>
-      <c r="K42" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L42" s="51"/>
-      <c r="M42" s="50"/>
-      <c r="N42" s="52">
+      <c r="K49" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49" s="51"/>
+      <c r="M49" s="50"/>
+      <c r="N49" s="107">
         <v>117.9</v>
       </c>
-      <c r="O42" s="51"/>
-      <c r="P42" s="53"/>
-    </row>
-    <row r="43" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A43" s="76" t="s">
+      <c r="O49" s="51"/>
+      <c r="P49" s="52"/>
+    </row>
+    <row r="50" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A50" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="84" t="s">
+      <c r="B50" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="54" t="s">
+      <c r="C50" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D43" s="55" t="s">
+      <c r="D50" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="54">
+      <c r="E50" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F50" s="53">
         <v>30</v>
       </c>
-      <c r="G43" s="50">
-        <f t="shared" si="5"/>
+      <c r="G50" s="50">
+        <f t="shared" si="11"/>
         <v>1260</v>
       </c>
-      <c r="H43" s="54">
-        <v>42</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J43" s="57"/>
-      <c r="K43" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L43" s="57"/>
-      <c r="M43" s="54"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="57"/>
-      <c r="P43" s="58"/>
-    </row>
-    <row r="44" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A44" s="76" t="s">
+      <c r="H50" s="53">
+        <v>42</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J50" s="56"/>
+      <c r="K50" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50" s="56"/>
+      <c r="M50" s="53"/>
+      <c r="N50" s="108"/>
+      <c r="O50" s="56"/>
+      <c r="P50" s="57"/>
+    </row>
+    <row r="51" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A51" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="79" t="s">
+      <c r="B51" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C51" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D51" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E51" s="10">
         <v>5</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F51" s="10">
         <v>30</v>
       </c>
-      <c r="G44" s="7">
-        <f t="shared" si="5"/>
+      <c r="G51" s="7">
+        <f t="shared" si="11"/>
         <v>1260</v>
       </c>
-      <c r="H44" s="10">
-        <v>42</v>
-      </c>
-      <c r="I44" s="10">
+      <c r="H51" s="10">
+        <v>42</v>
+      </c>
+      <c r="I51" s="10">
         <v>0.94</v>
       </c>
-      <c r="J44" s="9">
-        <f>N44/F44</f>
+      <c r="J51" s="9">
+        <f>N51/F51</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="K44" s="74">
+      <c r="K51" s="73">
         <f t="shared" si="1"/>
         <v>0.22340425531914887</v>
       </c>
-      <c r="L44" s="9">
-        <f>N44/6</f>
+      <c r="L51" s="9">
+        <f>N51/6</f>
         <v>5.75</v>
       </c>
-      <c r="M44" s="10"/>
-      <c r="N44" s="9">
+      <c r="M51" s="10"/>
+      <c r="N51" s="103">
         <v>34.5</v>
       </c>
-      <c r="O44" s="11">
+      <c r="O51" s="11">
         <v>30</v>
       </c>
-      <c r="P44" s="59" t="s">
+      <c r="P51" s="58" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15.75">
-      <c r="A45" s="76" t="s">
+    <row r="52" spans="1:16" ht="15.75">
+      <c r="A52" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="79" t="s">
+      <c r="B52" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C52" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D52" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E45" s="102">
+      <c r="E52" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F52" s="10">
         <f>25*1.1</f>
         <v>27.500000000000004</v>
       </c>
-      <c r="G45" s="10">
-        <f t="shared" si="5"/>
+      <c r="G52" s="10">
+        <f t="shared" si="11"/>
         <v>1155.0000000000002</v>
       </c>
-      <c r="H45" s="10">
-        <v>42</v>
-      </c>
-      <c r="I45" s="10">
+      <c r="H52" s="10">
+        <v>42</v>
+      </c>
+      <c r="I52" s="10">
         <v>1.42</v>
       </c>
-      <c r="J45" s="9">
-        <f>N45/F45</f>
+      <c r="J52" s="9">
+        <f>N52/F52</f>
         <v>1.6363636363636362</v>
       </c>
-      <c r="K45" s="74">
+      <c r="K52" s="73">
         <f t="shared" si="1"/>
         <v>0.15236875800256078</v>
       </c>
-      <c r="L45" s="9">
-        <f>N45/25</f>
+      <c r="L52" s="9">
+        <f>N52/25</f>
         <v>1.8</v>
       </c>
-      <c r="M45" s="10"/>
-      <c r="N45" s="9">
+      <c r="M52" s="10"/>
+      <c r="N52" s="103">
         <v>45</v>
       </c>
-      <c r="O45" s="9">
+      <c r="O52" s="9">
         <v>45</v>
       </c>
-      <c r="P45" s="60" t="s">
+      <c r="P52" s="59" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
-      <c r="A46" s="7" t="s">
+    <row r="53" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
+      <c r="A53" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B46" s="86" t="s">
+      <c r="B53" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="30" t="s">
+      <c r="C53" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D53" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E53" s="17">
         <v>0.875</v>
       </c>
-      <c r="F46" s="61">
-        <f>E46*24</f>
+      <c r="F53" s="60">
+        <f>E53*24</f>
         <v>21</v>
       </c>
-      <c r="G46" s="10">
-        <f t="shared" si="5"/>
+      <c r="G53" s="10">
+        <f t="shared" si="11"/>
         <v>882</v>
       </c>
-      <c r="H46" s="10">
-        <v>42</v>
-      </c>
-      <c r="I46" s="10">
+      <c r="H53" s="10">
+        <v>42</v>
+      </c>
+      <c r="I53" s="10">
         <v>9.1199999999999992</v>
       </c>
-      <c r="J46" s="9">
-        <f>N46/F46</f>
+      <c r="J53" s="9">
+        <f>N53/F53</f>
         <v>10.8</v>
       </c>
-      <c r="K46" s="74">
+      <c r="K53" s="73">
         <f t="shared" si="1"/>
         <v>0.1842105263157896</v>
       </c>
-      <c r="L46" s="9">
-        <f>N46/24</f>
+      <c r="L53" s="9">
+        <f>N53/24</f>
         <v>9.4500000000000011</v>
       </c>
-      <c r="M46" s="10"/>
-      <c r="N46" s="9">
+      <c r="M53" s="10"/>
+      <c r="N53" s="103">
         <v>226.8</v>
       </c>
-      <c r="O46" s="9">
+      <c r="O53" s="9">
         <v>226.8</v>
       </c>
-      <c r="P46" s="18" t="s">
+      <c r="P53" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
-      <c r="A47" s="7" t="s">
+    <row r="54" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
+      <c r="A54" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B47" s="86" t="s">
+      <c r="B54" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C54" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D54" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E47" s="17">
+      <c r="E54" s="17">
         <v>0.75</v>
       </c>
-      <c r="F47" s="61">
+      <c r="F54" s="60">
         <v>19.5</v>
       </c>
-      <c r="G47" s="10">
-        <f t="shared" si="5"/>
+      <c r="G54" s="10">
+        <f t="shared" si="11"/>
         <v>819</v>
       </c>
-      <c r="H47" s="10">
-        <v>42</v>
-      </c>
-      <c r="I47" s="10">
+      <c r="H54" s="10">
+        <v>42</v>
+      </c>
+      <c r="I54" s="10">
         <v>5.21</v>
       </c>
-      <c r="J47" s="9">
-        <f>O47/F47</f>
+      <c r="J54" s="9">
+        <f>O54/F54</f>
         <v>7.5066666666666668</v>
       </c>
-      <c r="K47" s="74">
+      <c r="K54" s="73">
         <f t="shared" si="1"/>
         <v>0.44081893793985927</v>
       </c>
-      <c r="L47" s="9">
-        <f>N47/26</f>
+      <c r="L54" s="9">
+        <f>N54/26</f>
         <v>5.63</v>
       </c>
-      <c r="M47" s="10"/>
-      <c r="N47" s="9">
+      <c r="M54" s="10"/>
+      <c r="N54" s="103">
         <v>146.38</v>
       </c>
-      <c r="O47" s="9">
+      <c r="O54" s="9">
         <v>146.38</v>
       </c>
-      <c r="P47" s="18" t="s">
+      <c r="P54" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:16" s="63" customFormat="1" ht="18" customHeight="1">
-      <c r="A48" s="10" t="s">
+    <row r="55" spans="1:16" s="62" customFormat="1" ht="18" customHeight="1">
+      <c r="A55" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="B48" s="86" t="s">
+      <c r="B55" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="C48" s="30" t="s">
+      <c r="C55" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D55" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E48" s="65"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="66"/>
-      <c r="I48" s="66"/>
-      <c r="J48" s="67"/>
-      <c r="K48" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L48" s="67"/>
-      <c r="M48" s="68"/>
-      <c r="N48" s="67"/>
-      <c r="O48" s="64"/>
-      <c r="P48" s="62"/>
-    </row>
-    <row r="49" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A49" s="76" t="s">
+      <c r="E55" s="64"/>
+      <c r="F55" s="65"/>
+      <c r="G55" s="65"/>
+      <c r="H55" s="65"/>
+      <c r="I55" s="65"/>
+      <c r="J55" s="66"/>
+      <c r="K55" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55" s="66"/>
+      <c r="M55" s="67"/>
+      <c r="N55" s="109"/>
+      <c r="O55" s="63"/>
+      <c r="P55" s="61"/>
+    </row>
+    <row r="56" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A56" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B49" s="88" t="s">
+      <c r="B56" s="87" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="69" t="s">
+      <c r="D56" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="69">
+      <c r="E56" s="68">
         <v>5</v>
       </c>
-      <c r="F49" s="61">
+      <c r="F56" s="60">
         <v>40</v>
       </c>
-      <c r="G49" s="10">
-        <f>F49*42</f>
-        <v>1680</v>
-      </c>
-      <c r="H49" s="10">
-        <v>42</v>
-      </c>
-      <c r="I49" s="10">
+      <c r="G56" s="10">
+        <f>F56*H56</f>
+        <v>1400</v>
+      </c>
+      <c r="H56" s="10">
+        <v>35</v>
+      </c>
+      <c r="I56" s="10">
         <v>1.26</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J56" s="9">
         <v>1.95</v>
       </c>
-      <c r="K49" s="74">
+      <c r="K56" s="73">
         <f t="shared" si="1"/>
         <v>0.54761904761904767</v>
       </c>
-      <c r="L49" s="9">
-        <f>N49/8</f>
+      <c r="L56" s="9">
+        <f>N56/8</f>
         <v>9.75</v>
       </c>
-      <c r="M49" s="10"/>
-      <c r="N49" s="9">
-        <f>J49*F49</f>
+      <c r="M56" s="10"/>
+      <c r="N56" s="103">
+        <f>J56*F56</f>
         <v>78</v>
       </c>
-      <c r="O49" s="11"/>
-      <c r="P49" s="70" t="s">
+      <c r="O56" s="11"/>
+      <c r="P56" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:16" s="63" customFormat="1" ht="21" customHeight="1">
-      <c r="A50" s="76" t="s">
+    <row r="57" spans="1:16" s="62" customFormat="1" ht="21" customHeight="1">
+      <c r="A57" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B50" s="88" t="s">
+      <c r="B57" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="69" t="s">
+      <c r="D57" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="E50" s="69">
+      <c r="E57" s="68">
         <v>5</v>
       </c>
-      <c r="F50" s="61">
+      <c r="F57" s="60">
         <v>40</v>
       </c>
-      <c r="G50" s="10">
-        <f t="shared" ref="G50:G60" si="7">F50*42</f>
-        <v>1680</v>
-      </c>
-      <c r="H50" s="10">
-        <v>42</v>
-      </c>
-      <c r="I50" s="10">
+      <c r="G57" s="10">
+        <f t="shared" ref="G57:G67" si="13">F57*H57</f>
+        <v>1400</v>
+      </c>
+      <c r="H57" s="10">
+        <v>35</v>
+      </c>
+      <c r="I57" s="10">
         <v>1.53</v>
       </c>
-      <c r="J50" s="9">
+      <c r="J57" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K50" s="74">
+      <c r="K57" s="73">
         <f t="shared" si="1"/>
         <v>0.50326797385620892</v>
       </c>
-      <c r="L50" s="9">
-        <f t="shared" ref="L50:L60" si="8">N50/8</f>
+      <c r="L57" s="9">
+        <f t="shared" ref="L57:L67" si="14">N57/8</f>
         <v>11.5</v>
       </c>
-      <c r="M50" s="10"/>
-      <c r="N50" s="9">
-        <f t="shared" ref="N50:N60" si="9">J50*F50</f>
+      <c r="M57" s="10"/>
+      <c r="N57" s="103">
+        <f t="shared" ref="N57:N67" si="15">J57*F57</f>
         <v>92</v>
       </c>
-      <c r="O50" s="11"/>
-      <c r="P50" s="70" t="s">
+      <c r="O57" s="11"/>
+      <c r="P57" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="51" spans="1:16" s="63" customFormat="1" ht="21" customHeight="1">
-      <c r="A51" s="76" t="s">
+    <row r="58" spans="1:16" s="62" customFormat="1" ht="21" customHeight="1">
+      <c r="A58" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B51" s="88" t="s">
+      <c r="B58" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D51" s="69" t="s">
+      <c r="D58" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="E51" s="69">
+      <c r="E58" s="68">
         <v>5</v>
       </c>
-      <c r="F51" s="61">
+      <c r="F58" s="60">
         <v>40</v>
       </c>
-      <c r="G51" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H51" s="10">
-        <v>42</v>
-      </c>
-      <c r="I51" s="10">
+      <c r="G58" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H58" s="10">
+        <v>35</v>
+      </c>
+      <c r="I58" s="10">
         <v>1.76</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J58" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K51" s="74">
+      <c r="K58" s="73">
         <f t="shared" si="1"/>
         <v>0.30681818181818166</v>
       </c>
-      <c r="L51" s="9">
-        <f t="shared" si="8"/>
+      <c r="L58" s="9">
+        <f t="shared" si="14"/>
         <v>11.5</v>
       </c>
-      <c r="M51" s="10"/>
-      <c r="N51" s="9">
-        <f t="shared" si="9"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="103">
+        <f t="shared" si="15"/>
         <v>92</v>
       </c>
-      <c r="O51" s="11"/>
-      <c r="P51" s="70" t="s">
+      <c r="O58" s="11"/>
+      <c r="P58" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="52" spans="1:16" s="63" customFormat="1" ht="18" customHeight="1">
-      <c r="A52" s="76" t="s">
+    <row r="59" spans="1:16" s="62" customFormat="1" ht="18" customHeight="1">
+      <c r="A59" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B52" s="88" t="s">
+      <c r="B59" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C59" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="69" t="s">
+      <c r="D59" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="E52" s="69">
+      <c r="E59" s="68">
         <v>5</v>
       </c>
-      <c r="F52" s="61">
+      <c r="F59" s="60">
         <v>40</v>
       </c>
-      <c r="G52" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H52" s="10">
-        <v>42</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J52" s="9">
+      <c r="G59" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H59" s="10">
+        <v>35</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J59" s="9">
         <v>5.2</v>
       </c>
-      <c r="K52" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L52" s="9">
-        <f t="shared" si="8"/>
+      <c r="K59" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L59" s="9">
+        <f t="shared" si="14"/>
         <v>26</v>
       </c>
-      <c r="M52" s="10"/>
-      <c r="N52" s="9">
-        <f t="shared" si="9"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="103">
+        <f t="shared" si="15"/>
         <v>208</v>
       </c>
-      <c r="O52" s="11"/>
-      <c r="P52" s="70" t="s">
+      <c r="O59" s="11"/>
+      <c r="P59" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="63" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A53" s="76" t="s">
+    <row r="60" spans="1:16" s="62" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A60" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B53" s="88" t="s">
+      <c r="B60" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C60" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="69" t="s">
+      <c r="D60" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="E53" s="69">
+      <c r="E60" s="68">
         <v>5</v>
       </c>
-      <c r="F53" s="61">
+      <c r="F60" s="60">
         <v>40</v>
       </c>
-      <c r="G53" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H53" s="10">
-        <v>42</v>
-      </c>
-      <c r="I53" s="10">
+      <c r="G60" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H60" s="10">
+        <v>35</v>
+      </c>
+      <c r="I60" s="10">
         <v>2.75</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J60" s="9">
         <v>3.38</v>
       </c>
-      <c r="K53" s="74">
+      <c r="K60" s="73">
         <f t="shared" si="1"/>
         <v>0.22909090909090901</v>
       </c>
-      <c r="L53" s="9">
-        <f t="shared" si="8"/>
+      <c r="L60" s="9">
+        <f t="shared" si="14"/>
         <v>16.899999999999999</v>
       </c>
-      <c r="M53" s="10"/>
-      <c r="N53" s="9">
-        <f t="shared" si="9"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="103">
+        <f t="shared" si="15"/>
         <v>135.19999999999999</v>
       </c>
-      <c r="O53" s="11"/>
-      <c r="P53" s="70" t="s">
+      <c r="O60" s="11"/>
+      <c r="P60" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="63" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A54" s="76" t="s">
+    <row r="61" spans="1:16" s="62" customFormat="1" ht="20.25" customHeight="1">
+      <c r="A61" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B54" s="88" t="s">
+      <c r="B61" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C61" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D54" s="69" t="s">
+      <c r="D61" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="E54" s="69">
+      <c r="E61" s="68">
         <v>5</v>
       </c>
-      <c r="F54" s="61">
+      <c r="F61" s="60">
         <v>40</v>
       </c>
-      <c r="G54" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H54" s="10">
-        <v>42</v>
-      </c>
-      <c r="I54" s="10">
+      <c r="G61" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H61" s="10">
+        <v>35</v>
+      </c>
+      <c r="I61" s="10">
         <v>2.7</v>
       </c>
-      <c r="J54" s="9">
+      <c r="J61" s="9">
         <v>3.78</v>
       </c>
-      <c r="K54" s="74">
+      <c r="K61" s="73">
         <f t="shared" si="1"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="L54" s="9">
-        <f t="shared" si="8"/>
+      <c r="L61" s="9">
+        <f t="shared" si="14"/>
         <v>18.899999999999999</v>
       </c>
-      <c r="M54" s="10"/>
-      <c r="N54" s="9">
-        <f t="shared" si="9"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="103">
+        <f t="shared" si="15"/>
         <v>151.19999999999999</v>
       </c>
-      <c r="O54" s="11"/>
-      <c r="P54" s="70" t="s">
+      <c r="O61" s="11"/>
+      <c r="P61" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:16" s="63" customFormat="1" ht="18" customHeight="1">
-      <c r="A55" s="76" t="s">
+    <row r="62" spans="1:16" s="62" customFormat="1" ht="18" customHeight="1">
+      <c r="A62" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B55" s="88" t="s">
+      <c r="B62" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C62" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D55" s="69" t="s">
+      <c r="D62" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="E55" s="69">
+      <c r="E62" s="68">
         <v>5</v>
       </c>
-      <c r="F55" s="61">
+      <c r="F62" s="60">
         <v>40</v>
       </c>
-      <c r="G55" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H55" s="10">
-        <v>42</v>
-      </c>
-      <c r="I55" s="10">
+      <c r="G62" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H62" s="10">
+        <v>35</v>
+      </c>
+      <c r="I62" s="10">
         <v>2.58</v>
       </c>
-      <c r="J55" s="9">
+      <c r="J62" s="9">
         <v>3.65</v>
       </c>
-      <c r="K55" s="74">
+      <c r="K62" s="73">
         <f t="shared" si="1"/>
         <v>0.41472868217054248</v>
       </c>
-      <c r="L55" s="9">
-        <f t="shared" si="8"/>
+      <c r="L62" s="9">
+        <f t="shared" si="14"/>
         <v>18.25</v>
       </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="9">
-        <f>J55*F55</f>
+      <c r="M62" s="10"/>
+      <c r="N62" s="103">
+        <f>J62*F62</f>
         <v>146</v>
       </c>
-      <c r="O55" s="11"/>
-      <c r="P55" s="70" t="s">
+      <c r="O62" s="11"/>
+      <c r="P62" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A56" s="76" t="s">
+    <row r="63" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A63" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B56" s="88" t="s">
+      <c r="B63" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="C56" s="30" t="s">
+      <c r="C63" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="69" t="s">
+      <c r="D63" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="E56" s="69">
+      <c r="E63" s="68">
         <v>5</v>
       </c>
-      <c r="F56" s="61">
+      <c r="F63" s="60">
         <v>40</v>
       </c>
-      <c r="G56" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H56" s="10">
-        <v>42</v>
-      </c>
-      <c r="I56" s="10">
+      <c r="G63" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H63" s="10">
+        <v>35</v>
+      </c>
+      <c r="I63" s="10">
         <v>1.7</v>
       </c>
-      <c r="J56" s="9">
+      <c r="J63" s="9">
         <v>2.7</v>
       </c>
-      <c r="K56" s="74">
+      <c r="K63" s="73">
         <f t="shared" si="1"/>
         <v>0.58823529411764719</v>
       </c>
-      <c r="L56" s="9">
-        <f t="shared" si="8"/>
+      <c r="L63" s="9">
+        <f t="shared" si="14"/>
         <v>13.5</v>
       </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="9">
-        <f t="shared" si="9"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="103">
+        <f t="shared" si="15"/>
         <v>108</v>
       </c>
-      <c r="O56" s="11"/>
-      <c r="P56" s="70" t="s">
+      <c r="O63" s="11"/>
+      <c r="P63" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="57" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A57" s="76" t="s">
+    <row r="64" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A64" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B57" s="88" t="s">
+      <c r="B64" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="C57" s="30" t="s">
+      <c r="C64" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D57" s="69" t="s">
+      <c r="D64" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="69">
+      <c r="E64" s="68">
         <v>5</v>
       </c>
-      <c r="F57" s="61">
+      <c r="F64" s="60">
         <v>40</v>
       </c>
-      <c r="G57" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H57" s="10">
-        <v>42</v>
-      </c>
-      <c r="I57" s="10">
+      <c r="G64" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H64" s="10">
+        <v>35</v>
+      </c>
+      <c r="I64" s="10">
         <v>2.6</v>
       </c>
-      <c r="J57" s="9">
+      <c r="J64" s="9">
         <v>4</v>
       </c>
-      <c r="K57" s="74">
+      <c r="K64" s="73">
         <f t="shared" si="1"/>
         <v>0.53846153846153832</v>
       </c>
-      <c r="L57" s="9">
-        <f t="shared" si="8"/>
+      <c r="L64" s="9">
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="M57" s="10"/>
-      <c r="N57" s="9">
-        <f t="shared" si="9"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="103">
+        <f t="shared" si="15"/>
         <v>160</v>
       </c>
-      <c r="O57" s="11"/>
-      <c r="P57" s="70" t="s">
+      <c r="O64" s="11"/>
+      <c r="P64" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A58" s="76" t="s">
+    <row r="65" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A65" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B58" s="89" t="s">
+      <c r="B65" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="30" t="s">
+      <c r="C65" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D58" s="69" t="s">
+      <c r="D65" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="E58" s="69">
+      <c r="E65" s="68">
         <v>5</v>
       </c>
-      <c r="F58" s="61">
+      <c r="F65" s="60">
         <v>40</v>
       </c>
-      <c r="G58" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H58" s="10">
-        <v>42</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J58" s="9">
-        <f>N58/40</f>
+      <c r="G65" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H65" s="10">
+        <v>35</v>
+      </c>
+      <c r="I65" s="7">
         <v>7.5</v>
       </c>
-      <c r="K58" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L58" s="9">
-        <f t="shared" si="8"/>
+      <c r="J65" s="9">
+        <f>N65/40</f>
+        <v>7.5</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L65" s="9">
+        <f t="shared" si="14"/>
         <v>37.5</v>
       </c>
-      <c r="M58" s="10"/>
-      <c r="N58" s="9">
+      <c r="M65" s="10"/>
+      <c r="N65" s="103">
         <v>300</v>
       </c>
-      <c r="O58" s="11"/>
-      <c r="P58" s="44" t="s">
+      <c r="O65" s="11"/>
+      <c r="P65" s="44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:16" s="71" customFormat="1" ht="21">
-      <c r="A59" s="76" t="s">
+    <row r="66" spans="1:16" s="70" customFormat="1" ht="21">
+      <c r="A66" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B59" s="88" t="s">
+      <c r="B66" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="30" t="s">
+      <c r="C66" s="100" t="s">
         <v>108</v>
       </c>
-      <c r="D59" s="69" t="s">
+      <c r="D66" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="E59" s="69">
+      <c r="E66" s="68">
         <v>5</v>
       </c>
-      <c r="F59" s="61">
+      <c r="F66" s="60">
         <v>40</v>
       </c>
-      <c r="G59" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H59" s="10">
-        <v>42</v>
-      </c>
-      <c r="I59" s="10">
+      <c r="G66" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H66" s="10">
+        <v>35</v>
+      </c>
+      <c r="I66" s="10">
         <v>1.58</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J66" s="9">
         <v>3.1</v>
       </c>
-      <c r="K59" s="74">
+      <c r="K66" s="73">
         <f t="shared" si="1"/>
         <v>0.96202531645569622</v>
       </c>
-      <c r="L59" s="9">
-        <f>N59/8</f>
+      <c r="L66" s="9">
+        <f>N66/8</f>
         <v>15.5</v>
       </c>
-      <c r="M59" s="10"/>
-      <c r="N59" s="9">
-        <f t="shared" si="9"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="103">
+        <f t="shared" si="15"/>
         <v>124</v>
       </c>
-      <c r="O59" s="11"/>
-      <c r="P59" s="70" t="s">
+      <c r="O66" s="11"/>
+      <c r="P66" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="1:16" s="63" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A60" s="76" t="s">
+    <row r="67" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A67" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B60" s="88" t="s">
+      <c r="B67" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="95"/>
-      <c r="D60" s="69" t="s">
+      <c r="C67" s="94"/>
+      <c r="D67" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E60" s="69">
+      <c r="E67" s="68">
         <v>5</v>
       </c>
-      <c r="F60" s="61">
+      <c r="F67" s="60">
         <v>40</v>
       </c>
-      <c r="G60" s="10">
-        <f t="shared" si="7"/>
-        <v>1680</v>
-      </c>
-      <c r="H60" s="10">
-        <v>42</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J60" s="9">
+      <c r="G67" s="10">
+        <f t="shared" si="13"/>
+        <v>1400</v>
+      </c>
+      <c r="H67" s="10">
+        <v>35</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J67" s="9">
         <v>4</v>
       </c>
-      <c r="K60" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L60" s="9">
-        <f t="shared" si="8"/>
+      <c r="K67" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L67" s="9">
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="M60" s="10"/>
-      <c r="N60" s="9">
-        <f t="shared" si="9"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="103">
+        <f t="shared" si="15"/>
         <v>160</v>
       </c>
-      <c r="O60" s="11"/>
-      <c r="P60" s="70" t="s">
+      <c r="O67" s="11"/>
+      <c r="P67" s="69" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R67" xr:uid="{57A31AB5-A5B3-4549-84CF-985A174AC5BE}"/>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.36" right="0.36" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="47" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup scale="44" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Products Price table Web.xlsx
+++ b/Products Price table Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F81E8CD-6FDB-413A-9282-DA17A2AB6530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF44ECB8-32BF-40E1-BB15-632E2522ECE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36F92623-3410-4B5C-824E-0AA70134F832}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Item Classification 7.14.26" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item Classification 7.14.26'!$A$1:$R$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item Classification 7.14.26'!$A$1:$R$69</definedName>
     <definedName name="ITEM_DDOWN">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Item Classification 7.14.26'!$A$1:$P$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Item Classification 7.14.26'!$A$1:$P$69</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Item Classification 7.14.26'!$1:$1</definedName>
     <definedName name="TOFU">#REF!</definedName>
     <definedName name="VENDOR_DDOWN">#REF!</definedName>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="126">
   <si>
     <t>Items</t>
   </si>
@@ -1401,7 +1401,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
@@ -1491,7 +1491,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="7">
-        <f t="shared" ref="G2:G7" si="0">F2*42</f>
+        <f t="shared" ref="G2:G8" si="0">F2*42</f>
         <v>1050</v>
       </c>
       <c r="H2" s="7">
@@ -1547,10 +1547,10 @@
         <v>1050</v>
       </c>
       <c r="H3" s="7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" s="7">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="J3" s="9">
         <f>N3/F2</f>
@@ -1599,7 +1599,7 @@
         <v>1008</v>
       </c>
       <c r="H4" s="7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="10">
         <v>3.03</v>
@@ -1743,62 +1743,60 @@
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="8">
-        <v>2</v>
-      </c>
-      <c r="F7" s="10">
-        <v>24</v>
-      </c>
-      <c r="G7" s="10">
-        <f t="shared" si="0"/>
-        <v>1008</v>
-      </c>
-      <c r="H7" s="10">
-        <v>42</v>
-      </c>
-      <c r="I7" s="10">
-        <v>3.03</v>
+      <c r="D7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="7">
+        <v>5</v>
+      </c>
+      <c r="F7" s="7">
+        <v>25</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" ref="G7" si="1">F7*42</f>
+        <v>1050</v>
+      </c>
+      <c r="H7" s="7">
+        <v>42</v>
+      </c>
+      <c r="I7" s="7">
+        <v>2.86</v>
       </c>
       <c r="J7" s="9">
         <f>N7/F7</f>
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="K7" s="73">
-        <f t="shared" ref="K7:K66" si="1">J7/I7-1</f>
-        <v>0.28712871287128716</v>
+        <f>J7/I6-1</f>
+        <v>1.7972027972027975</v>
       </c>
       <c r="L7" s="9">
-        <f>N7/12</f>
-        <v>7.8</v>
+        <f>J7*5</f>
+        <v>40</v>
       </c>
       <c r="M7" s="10">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="N7" s="103">
-        <v>93.6</v>
-      </c>
-      <c r="O7" s="9">
-        <v>90</v>
-      </c>
-      <c r="P7" s="18" t="s">
-        <v>20</v>
+        <v>200</v>
+      </c>
+      <c r="O7" s="11"/>
+      <c r="P7" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
       <c r="A8" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="78" t="s">
-        <v>24</v>
+      <c r="B8" s="74" t="s">
+        <v>21</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>25</v>
+      <c r="D8" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="E8" s="8">
         <v>2</v>
@@ -1807,178 +1805,185 @@
         <v>24</v>
       </c>
       <c r="G8" s="10">
-        <f t="shared" ref="G8:G15" si="2">F8*42</f>
+        <f t="shared" si="0"/>
         <v>1008</v>
       </c>
       <c r="H8" s="10">
         <v>42</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>34</v>
+      <c r="I8" s="10">
+        <v>3.03</v>
       </c>
       <c r="J8" s="9">
         <f>N8/F8</f>
-        <v>5.2</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>34</v>
+        <v>3.9</v>
+      </c>
+      <c r="K8" s="73">
+        <f t="shared" ref="K8:K68" si="2">J8/I8-1</f>
+        <v>0.28712871287128716</v>
       </c>
       <c r="L8" s="9">
         <f>N8/12</f>
-        <v>10.4</v>
+        <v>7.8</v>
       </c>
       <c r="M8" s="10">
         <v>26</v>
       </c>
       <c r="N8" s="103">
-        <v>124.8</v>
+        <v>93.6</v>
       </c>
       <c r="O8" s="9">
-        <v>121.2</v>
+        <v>90</v>
       </c>
       <c r="P8" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10">
+        <v>24</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" ref="G9:G16" si="3">F9*42</f>
+        <v>1008</v>
+      </c>
+      <c r="H9" s="10">
+        <v>42</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="9">
+        <f>N9/F9</f>
+        <v>5.2</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="9">
+        <f>N9/12</f>
+        <v>10.4</v>
+      </c>
+      <c r="M9" s="10">
         <v>26</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="N9" s="103">
+        <v>124.8</v>
+      </c>
+      <c r="O9" s="9">
+        <v>121.2</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E10" s="8">
         <v>1</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F10" s="19">
         <v>30</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G10" s="19">
+        <f t="shared" si="3"/>
+        <v>1260</v>
+      </c>
+      <c r="H10" s="20">
+        <v>42</v>
+      </c>
+      <c r="I10" s="20">
+        <v>2.8</v>
+      </c>
+      <c r="J10" s="21">
+        <v>4.8</v>
+      </c>
+      <c r="K10" s="73">
         <f t="shared" si="2"/>
-        <v>1260</v>
-      </c>
-      <c r="H9" s="20">
-        <v>42</v>
-      </c>
-      <c r="I9" s="20">
-        <v>2.8</v>
-      </c>
-      <c r="J9" s="21">
+        <v>0.71428571428571441</v>
+      </c>
+      <c r="L10" s="21">
+        <f>N10/30</f>
         <v>4.8</v>
       </c>
-      <c r="K9" s="73">
-        <f t="shared" si="1"/>
-        <v>0.71428571428571441</v>
-      </c>
-      <c r="L9" s="21">
-        <f>N9/30</f>
-        <v>4.8</v>
-      </c>
-      <c r="M9" s="20"/>
-      <c r="N9" s="104">
-        <f>J9*30</f>
+      <c r="M10" s="20"/>
+      <c r="N10" s="104">
+        <f>J10*30</f>
         <v>144</v>
       </c>
-      <c r="O9" s="21">
+      <c r="O10" s="21">
         <f>4.65*30</f>
         <v>139.5</v>
       </c>
-      <c r="P9" s="22" t="s">
+      <c r="P10" s="22" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A10" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="75" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="25">
-        <v>18</v>
-      </c>
-      <c r="G10" s="26">
-        <f>F10*42</f>
-        <v>756</v>
-      </c>
-      <c r="H10" s="25">
-        <v>42</v>
-      </c>
-      <c r="I10" s="25"/>
-      <c r="J10" s="27">
-        <v>5.3</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="46"/>
-      <c r="M10" s="89"/>
-      <c r="N10" s="105">
-        <v>95.4</v>
-      </c>
-      <c r="O10" s="27"/>
-      <c r="P10" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="R10" s="29"/>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1">
       <c r="A11" s="75" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="75" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="20">
-        <v>20</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="D11" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="25">
+        <v>18</v>
+      </c>
+      <c r="G11" s="26">
         <f>F11*42</f>
-        <v>840</v>
-      </c>
-      <c r="H11" s="20">
-        <v>42</v>
-      </c>
-      <c r="I11" s="20">
-        <v>3.18</v>
-      </c>
-      <c r="J11" s="93">
-        <v>4.875</v>
-      </c>
-      <c r="K11" s="73">
-        <f t="shared" si="1"/>
-        <v>0.53301886792452824</v>
+        <v>756</v>
+      </c>
+      <c r="H11" s="25">
+        <v>42</v>
+      </c>
+      <c r="I11" s="25"/>
+      <c r="J11" s="27">
+        <v>5.3</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="L11" s="46"/>
       <c r="M11" s="89"/>
-      <c r="N11" s="104">
-        <v>97.5</v>
-      </c>
-      <c r="O11" s="21"/>
+      <c r="N11" s="105">
+        <v>95.4</v>
+      </c>
+      <c r="O11" s="27"/>
       <c r="P11" s="28" t="s">
         <v>32</v>
       </c>
@@ -1989,47 +1994,47 @@
         <v>30</v>
       </c>
       <c r="B12" s="75" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="D12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="20">
         <v>20</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="19">
+        <f>F12*42</f>
+        <v>840</v>
+      </c>
+      <c r="H12" s="20">
+        <v>42</v>
+      </c>
+      <c r="I12" s="20">
+        <v>3.18</v>
+      </c>
+      <c r="J12" s="93">
+        <v>4.875</v>
+      </c>
+      <c r="K12" s="73">
         <f t="shared" si="2"/>
-        <v>840</v>
-      </c>
-      <c r="H12" s="10">
-        <v>42</v>
-      </c>
-      <c r="I12" s="7">
-        <v>2.87</v>
-      </c>
-      <c r="J12" s="31">
-        <f>N12/F12</f>
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="K12" s="73">
-        <f t="shared" si="1"/>
-        <v>0.60278745644599274</v>
-      </c>
-      <c r="L12" s="32"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="80">
-        <v>92</v>
-      </c>
-      <c r="O12" s="32"/>
-      <c r="P12" s="33" t="s">
-        <v>36</v>
-      </c>
+        <v>0.53301886792452824</v>
+      </c>
+      <c r="L12" s="46"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="104">
+        <v>97.5</v>
+      </c>
+      <c r="O12" s="21"/>
+      <c r="P12" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" s="29"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1">
       <c r="A13" s="75" t="s">
@@ -2051,10 +2056,10 @@
         <v>20</v>
       </c>
       <c r="G13" s="7">
-        <f>F13*42</f>
+        <f t="shared" si="3"/>
         <v>840</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="10">
         <v>42</v>
       </c>
       <c r="I13" s="7">
@@ -2065,17 +2070,17 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="K13" s="73">
-        <f>J12/I12-1</f>
+        <f t="shared" si="2"/>
         <v>0.60278745644599274</v>
       </c>
-      <c r="L13" s="35"/>
-      <c r="M13" s="91"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="90"/>
       <c r="N13" s="80">
         <v>92</v>
       </c>
-      <c r="O13" s="35"/>
-      <c r="P13" s="28" t="s">
-        <v>32</v>
+      <c r="O13" s="32"/>
+      <c r="P13" s="33" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1">
@@ -2108,6 +2113,7 @@
         <v>2.87</v>
       </c>
       <c r="J14" s="31">
+        <f>N14/F14</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="K14" s="73">
@@ -2120,8 +2126,8 @@
         <v>92</v>
       </c>
       <c r="O14" s="35"/>
-      <c r="P14" s="101" t="s">
-        <v>123</v>
+      <c r="P14" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1">
@@ -2129,13 +2135,13 @@
         <v>30</v>
       </c>
       <c r="B15" s="75" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>34</v>
@@ -2144,31 +2150,30 @@
         <v>20</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="2"/>
+        <f>F15*42</f>
         <v>840</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="13">
         <v>42</v>
       </c>
       <c r="I15" s="7">
         <v>2.87</v>
       </c>
-      <c r="J15" s="9">
-        <f>N15/F15</f>
-        <v>4.5</v>
+      <c r="J15" s="31">
+        <v>4.5999999999999996</v>
       </c>
       <c r="K15" s="73">
-        <f t="shared" si="1"/>
-        <v>0.56794425087108014</v>
-      </c>
-      <c r="L15" s="11"/>
-      <c r="M15" s="92"/>
-      <c r="N15" s="103">
-        <v>90</v>
-      </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="36" t="s">
-        <v>38</v>
+        <f>J14/I14-1</f>
+        <v>0.60278745644599274</v>
+      </c>
+      <c r="L15" s="35"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="80">
+        <v>92</v>
+      </c>
+      <c r="O15" s="35"/>
+      <c r="P15" s="101" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1">
@@ -2191,7 +2196,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="7">
-        <f t="shared" ref="G16:G27" si="3">F16*42</f>
+        <f t="shared" si="3"/>
         <v>840</v>
       </c>
       <c r="H16" s="7">
@@ -2201,21 +2206,21 @@
         <v>2.87</v>
       </c>
       <c r="J16" s="9">
-        <f>N16/F15</f>
-        <v>5.4</v>
+        <f>N16/F16</f>
+        <v>4.5</v>
       </c>
       <c r="K16" s="73">
-        <f>J16/I15-1</f>
-        <v>0.88153310104529625</v>
+        <f t="shared" si="2"/>
+        <v>0.56794425087108014</v>
       </c>
       <c r="L16" s="11"/>
       <c r="M16" s="92"/>
       <c r="N16" s="103">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="O16" s="11"/>
-      <c r="P16" s="15" t="s">
-        <v>18</v>
+      <c r="P16" s="36" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1">
@@ -2223,46 +2228,46 @@
         <v>30</v>
       </c>
       <c r="B17" s="75" t="s">
-        <v>116</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>39</v>
+        <v>115</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F17" s="7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G17" s="7">
-        <f t="shared" si="3"/>
-        <v>630</v>
-      </c>
-      <c r="H17" s="10">
+        <f t="shared" ref="G17:G28" si="4">F17*42</f>
+        <v>840</v>
+      </c>
+      <c r="H17" s="7">
         <v>42</v>
       </c>
       <c r="I17" s="7">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="J17" s="9">
-        <f>N17/F17</f>
-        <v>5.3</v>
+        <f>N17/F16</f>
+        <v>5.4</v>
       </c>
       <c r="K17" s="73">
-        <f t="shared" si="1"/>
-        <v>0.70967741935483852</v>
+        <f>J17/I16-1</f>
+        <v>0.88153310104529625</v>
       </c>
       <c r="L17" s="11"/>
       <c r="M17" s="92"/>
       <c r="N17" s="103">
-        <v>79.5</v>
+        <v>108</v>
       </c>
       <c r="O17" s="11"/>
-      <c r="P17" s="33" t="s">
-        <v>36</v>
+      <c r="P17" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1">
@@ -2285,7 +2290,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>630</v>
       </c>
       <c r="H18" s="10">
@@ -2294,22 +2299,22 @@
       <c r="I18" s="7">
         <v>3.1</v>
       </c>
-      <c r="J18" s="31">
-        <f>N18/F17</f>
-        <v>4.6500000000000004</v>
+      <c r="J18" s="9">
+        <f>N18/F18</f>
+        <v>5.3</v>
       </c>
       <c r="K18" s="73">
-        <f>J18/I17-1</f>
-        <v>0.5</v>
-      </c>
-      <c r="L18" s="32"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="80">
-        <v>69.75</v>
+        <f t="shared" si="2"/>
+        <v>0.70967741935483852</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="103">
+        <v>79.5</v>
       </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="12" t="s">
-        <v>17</v>
+      <c r="P18" s="33" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1">
@@ -2332,31 +2337,31 @@
         <v>15</v>
       </c>
       <c r="G19" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>630</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="10">
         <v>42</v>
       </c>
       <c r="I19" s="7">
         <v>3.1</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="31">
         <f>N19/F18</f>
         <v>4.6500000000000004</v>
       </c>
       <c r="K19" s="73">
-        <f>J18/I17-1</f>
+        <f>J19/I18-1</f>
         <v>0.5</v>
       </c>
-      <c r="L19" s="35"/>
-      <c r="M19" s="91"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="90"/>
       <c r="N19" s="80">
         <v>69.75</v>
       </c>
       <c r="O19" s="11"/>
-      <c r="P19" s="28" t="s">
-        <v>32</v>
+      <c r="P19" s="12" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15.75" customHeight="1">
@@ -2369,69 +2374,65 @@
       <c r="C20" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="F20" s="10">
-        <v>14</v>
-      </c>
-      <c r="G20" s="10">
-        <f t="shared" si="3"/>
-        <v>588</v>
-      </c>
-      <c r="H20" s="10">
+      <c r="D20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="7">
+        <v>15</v>
+      </c>
+      <c r="G20" s="7">
+        <f t="shared" si="4"/>
+        <v>630</v>
+      </c>
+      <c r="H20" s="7">
         <v>42</v>
       </c>
       <c r="I20" s="7">
         <v>3.1</v>
       </c>
-      <c r="J20" s="34">
-        <f>N20/14</f>
-        <v>4.7</v>
+      <c r="J20" s="9">
+        <f>N20/F19</f>
+        <v>4.6500000000000004</v>
       </c>
       <c r="K20" s="73">
-        <f>J20/I17-1</f>
-        <v>0.5161290322580645</v>
-      </c>
-      <c r="L20" s="34">
-        <f>N20/10</f>
-        <v>6.58</v>
-      </c>
-      <c r="M20" s="14"/>
-      <c r="N20" s="106">
-        <v>65.8</v>
+        <f>J19/I18-1</f>
+        <v>0.5</v>
+      </c>
+      <c r="L20" s="35"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="80">
+        <v>69.75</v>
       </c>
       <c r="O20" s="11"/>
-      <c r="P20" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="R20" s="29"/>
+      <c r="P20" s="28" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1">
       <c r="A21" s="75" t="s">
         <v>30</v>
       </c>
       <c r="B21" s="75" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C21" s="30" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1.4</v>
       </c>
       <c r="F21" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21" s="10">
-        <f t="shared" si="3"/>
-        <v>630</v>
+        <f t="shared" si="4"/>
+        <v>588</v>
       </c>
       <c r="H21" s="10">
         <v>42</v>
@@ -2440,20 +2441,24 @@
         <v>3.1</v>
       </c>
       <c r="J21" s="34">
-        <v>4.6500000000000004</v>
+        <f>N21/14</f>
+        <v>4.7</v>
       </c>
       <c r="K21" s="73">
         <f>J21/I18-1</f>
-        <v>0.5</v>
-      </c>
-      <c r="L21" s="34"/>
+        <v>0.5161290322580645</v>
+      </c>
+      <c r="L21" s="34">
+        <f>N21/10</f>
+        <v>6.58</v>
+      </c>
       <c r="M21" s="14"/>
       <c r="N21" s="106">
-        <v>69.75</v>
+        <v>65.8</v>
       </c>
       <c r="O21" s="11"/>
-      <c r="P21" s="12" t="s">
-        <v>123</v>
+      <c r="P21" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="R21" s="29"/>
     </row>
@@ -2477,7 +2482,7 @@
         <v>15</v>
       </c>
       <c r="G22" s="10">
-        <f t="shared" ref="G22" si="4">F22*42</f>
+        <f t="shared" si="4"/>
         <v>630</v>
       </c>
       <c r="H22" s="10">
@@ -2487,20 +2492,20 @@
         <v>3.1</v>
       </c>
       <c r="J22" s="34">
-        <v>5.3</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="K22" s="73">
-        <f>J22/I22-1</f>
-        <v>0.70967741935483852</v>
+        <f>J22/I19-1</f>
+        <v>0.5</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="14"/>
       <c r="N22" s="106">
-        <v>79.5</v>
+        <v>69.75</v>
       </c>
       <c r="O22" s="11"/>
-      <c r="P22" s="15" t="s">
-        <v>18</v>
+      <c r="P22" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="R22" s="29"/>
     </row>
@@ -2508,48 +2513,48 @@
       <c r="A23" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="79" t="s">
-        <v>117</v>
+      <c r="B23" s="75" t="s">
+        <v>124</v>
       </c>
       <c r="C23" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>42</v>
+      <c r="D23" s="13" t="s">
+        <v>125</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>34</v>
       </c>
       <c r="F23" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G23" s="10">
-        <f t="shared" si="3"/>
-        <v>840</v>
+        <f t="shared" ref="G23" si="5">F23*42</f>
+        <v>630</v>
       </c>
       <c r="H23" s="10">
         <v>42</v>
       </c>
       <c r="I23" s="7">
-        <v>3.92</v>
-      </c>
-      <c r="J23" s="9">
-        <f>N23/F$23</f>
-        <v>5</v>
+        <v>3.1</v>
+      </c>
+      <c r="J23" s="34">
+        <v>5.3</v>
       </c>
       <c r="K23" s="73">
-        <f t="shared" si="1"/>
-        <v>0.27551020408163263</v>
-      </c>
-      <c r="L23" s="9"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="103">
-        <v>100</v>
+        <f>J23/I23-1</f>
+        <v>0.70967741935483852</v>
+      </c>
+      <c r="L23" s="34"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="106">
+        <v>79.5</v>
       </c>
       <c r="O23" s="11"/>
-      <c r="P23" s="38" t="s">
-        <v>43</v>
-      </c>
+      <c r="P23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="R23" s="29"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1">
       <c r="A24" s="75" t="s">
@@ -2571,7 +2576,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="10">
-        <f t="shared" ref="G24" si="5">F24*42</f>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H24" s="10">
@@ -2580,21 +2585,22 @@
       <c r="I24" s="7">
         <v>3.92</v>
       </c>
-      <c r="J24" s="31">
-        <v>5.6</v>
+      <c r="J24" s="9">
+        <f>N24/F$24</f>
+        <v>5</v>
       </c>
       <c r="K24" s="73">
-        <f>J24/I21-1</f>
-        <v>0.80645161290322553</v>
+        <f t="shared" si="2"/>
+        <v>0.27551020408163263</v>
       </c>
       <c r="L24" s="9"/>
       <c r="M24" s="10"/>
-      <c r="N24" s="80">
-        <v>112</v>
+      <c r="N24" s="103">
+        <v>100</v>
       </c>
       <c r="O24" s="11"/>
-      <c r="P24" s="12" t="s">
-        <v>123</v>
+      <c r="P24" s="38" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1">
@@ -2610,14 +2616,14 @@
       <c r="D25" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E25" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="10">
         <v>20</v>
       </c>
-      <c r="G25" s="7">
-        <f t="shared" si="3"/>
+      <c r="G25" s="10">
+        <f t="shared" ref="G25" si="6">F25*42</f>
         <v>840</v>
       </c>
       <c r="H25" s="10">
@@ -2627,12 +2633,11 @@
         <v>3.92</v>
       </c>
       <c r="J25" s="31">
-        <f>N25/F$23</f>
         <v>5.6</v>
       </c>
       <c r="K25" s="73">
-        <f>J25/I23-1</f>
-        <v>0.4285714285714286</v>
+        <f>J25/I22-1</f>
+        <v>0.80645161290322553</v>
       </c>
       <c r="L25" s="9"/>
       <c r="M25" s="10"/>
@@ -2640,8 +2645,8 @@
         <v>112</v>
       </c>
       <c r="O25" s="11"/>
-      <c r="P25" s="39" t="s">
-        <v>36</v>
+      <c r="P25" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1">
@@ -2664,31 +2669,31 @@
         <v>20</v>
       </c>
       <c r="G26" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="10">
         <v>42</v>
       </c>
       <c r="I26" s="7">
         <v>3.92</v>
       </c>
       <c r="J26" s="31">
-        <f>N26/F$23</f>
+        <f>N26/F$24</f>
         <v>5.6</v>
       </c>
       <c r="K26" s="73">
-        <f>J25/I23-1</f>
+        <f>J26/I24-1</f>
         <v>0.4285714285714286</v>
       </c>
-      <c r="L26" s="34"/>
-      <c r="M26" s="14"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="10"/>
       <c r="N26" s="80">
         <v>112</v>
       </c>
       <c r="O26" s="11"/>
-      <c r="P26" s="28" t="s">
-        <v>32</v>
+      <c r="P26" s="39" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15.75" customHeight="1">
@@ -2711,7 +2716,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>840</v>
       </c>
       <c r="H27" s="13">
@@ -2720,22 +2725,22 @@
       <c r="I27" s="7">
         <v>3.92</v>
       </c>
-      <c r="J27" s="9">
-        <f>N27/F$23</f>
-        <v>5.95</v>
+      <c r="J27" s="31">
+        <f>N27/F$24</f>
+        <v>5.6</v>
       </c>
       <c r="K27" s="73">
-        <f>J27/I23-1</f>
-        <v>0.51785714285714302</v>
-      </c>
-      <c r="L27" s="9"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="103">
-        <v>119</v>
+        <f>J26/I24-1</f>
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="L27" s="34"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="80">
+        <v>112</v>
       </c>
       <c r="O27" s="11"/>
-      <c r="P27" s="15" t="s">
-        <v>18</v>
+      <c r="P27" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" customHeight="1">
@@ -2748,108 +2753,108 @@
       <c r="C28" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="10">
-        <v>1</v>
-      </c>
-      <c r="F28" s="10">
-        <v>18</v>
-      </c>
-      <c r="G28" s="10">
-        <f>F28*36</f>
-        <v>648</v>
-      </c>
-      <c r="H28" s="10">
+      <c r="D28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="7">
+        <v>20</v>
+      </c>
+      <c r="G28" s="7">
+        <f t="shared" si="4"/>
+        <v>840</v>
+      </c>
+      <c r="H28" s="13">
         <v>42</v>
       </c>
       <c r="I28" s="7">
-        <v>7.92</v>
+        <v>3.92</v>
       </c>
       <c r="J28" s="9">
-        <f>N28/F28</f>
-        <v>5.83</v>
+        <f>N28/F$24</f>
+        <v>5.95</v>
       </c>
       <c r="K28" s="73">
-        <f>J28/I23-1</f>
-        <v>0.48724489795918369</v>
-      </c>
-      <c r="L28" s="9">
-        <f>N28/18</f>
-        <v>5.83</v>
-      </c>
+        <f>J28/I24-1</f>
+        <v>0.51785714285714302</v>
+      </c>
+      <c r="L28" s="9"/>
       <c r="M28" s="10"/>
       <c r="N28" s="103">
-        <v>104.94</v>
-      </c>
-      <c r="O28" s="9">
-        <f>5.66*F28</f>
-        <v>101.88</v>
-      </c>
-      <c r="P28" s="18" t="s">
-        <v>20</v>
+        <v>119</v>
+      </c>
+      <c r="O28" s="11"/>
+      <c r="P28" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1">
       <c r="A29" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="78" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="37" t="s">
+      <c r="B29" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="7">
-        <v>20</v>
+      <c r="D29" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="10">
+        <v>1</v>
+      </c>
+      <c r="F29" s="10">
+        <v>18</v>
       </c>
       <c r="G29" s="10">
         <f>F29*36</f>
-        <v>720</v>
+        <v>648</v>
       </c>
       <c r="H29" s="10">
         <v>42</v>
       </c>
-      <c r="I29" s="10">
-        <v>3.25</v>
+      <c r="I29" s="7">
+        <v>7.92</v>
       </c>
       <c r="J29" s="9">
-        <v>4.8499999999999996</v>
+        <f>N29/F29</f>
+        <v>5.83</v>
       </c>
       <c r="K29" s="73">
-        <f>J29/I29-1</f>
-        <v>0.49230769230769211</v>
-      </c>
-      <c r="L29" s="9"/>
+        <f>J29/I24-1</f>
+        <v>0.48724489795918369</v>
+      </c>
+      <c r="L29" s="9">
+        <f>N29/18</f>
+        <v>5.83</v>
+      </c>
       <c r="M29" s="10"/>
       <c r="N29" s="103">
-        <f>J29*20</f>
-        <v>97</v>
-      </c>
-      <c r="O29" s="9"/>
-      <c r="P29" s="28" t="s">
-        <v>32</v>
+        <v>104.94</v>
+      </c>
+      <c r="O29" s="9">
+        <f>5.66*F29</f>
+        <v>101.88</v>
+      </c>
+      <c r="P29" s="18" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1">
       <c r="A30" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="74" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="7" t="s">
+      <c r="B30" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="37" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>34</v>
@@ -2857,32 +2862,32 @@
       <c r="F30" s="7">
         <v>20</v>
       </c>
-      <c r="G30" s="7">
-        <f t="shared" ref="G30:G46" si="6">F30*42</f>
-        <v>840</v>
+      <c r="G30" s="10">
+        <f>F30*36</f>
+        <v>720</v>
       </c>
       <c r="H30" s="10">
         <v>42</v>
       </c>
-      <c r="I30" s="7">
-        <v>3.76</v>
+      <c r="I30" s="10">
+        <v>3.25</v>
       </c>
       <c r="J30" s="9">
-        <f>N30/F30</f>
-        <v>5.0999999999999996</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="K30" s="73">
-        <f t="shared" ref="K30:K36" si="7">J30/I30-1</f>
-        <v>0.3563829787234043</v>
+        <f>J30/I30-1</f>
+        <v>0.49230769230769211</v>
       </c>
       <c r="L30" s="9"/>
       <c r="M30" s="10"/>
       <c r="N30" s="103">
-        <v>102</v>
-      </c>
-      <c r="O30" s="11"/>
-      <c r="P30" s="38" t="s">
-        <v>43</v>
+        <f>J30*20</f>
+        <v>97</v>
+      </c>
+      <c r="O30" s="9"/>
+      <c r="P30" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1">
@@ -2905,7 +2910,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" ref="G31" si="8">F31*42</f>
+        <f t="shared" ref="G31:G47" si="7">F31*42</f>
         <v>840</v>
       </c>
       <c r="H31" s="10">
@@ -2915,20 +2920,21 @@
         <v>3.76</v>
       </c>
       <c r="J31" s="9">
-        <v>6.45</v>
+        <f>N31/F31</f>
+        <v>5.0999999999999996</v>
       </c>
       <c r="K31" s="73">
-        <f t="shared" si="7"/>
-        <v>0.71542553191489366</v>
+        <f t="shared" ref="K31:K37" si="8">J31/I31-1</f>
+        <v>0.3563829787234043</v>
       </c>
       <c r="L31" s="9"/>
       <c r="M31" s="10"/>
       <c r="N31" s="103">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="O31" s="11"/>
-      <c r="P31" s="12" t="s">
-        <v>123</v>
+      <c r="P31" s="38" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75" customHeight="1">
@@ -2951,7 +2957,7 @@
         <v>20</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G32" si="9">F32*42</f>
         <v>840</v>
       </c>
       <c r="H32" s="10">
@@ -2961,21 +2967,20 @@
         <v>3.76</v>
       </c>
       <c r="J32" s="9">
-        <f>N32/F$30</f>
-        <v>5.5</v>
+        <v>6.45</v>
       </c>
       <c r="K32" s="73">
-        <f t="shared" si="7"/>
-        <v>0.4627659574468086</v>
+        <f t="shared" si="8"/>
+        <v>0.71542553191489366</v>
       </c>
       <c r="L32" s="9"/>
       <c r="M32" s="10"/>
       <c r="N32" s="103">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="O32" s="11"/>
-      <c r="P32" s="39" t="s">
-        <v>36</v>
+      <c r="P32" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="15.75" customHeight="1">
@@ -2998,7 +3003,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="H33" s="10">
@@ -3008,21 +3013,21 @@
         <v>3.76</v>
       </c>
       <c r="J33" s="9">
-        <f>N33/F$30</f>
-        <v>6.45</v>
+        <f>N33/F$31</f>
+        <v>5.5</v>
       </c>
       <c r="K33" s="73">
-        <f t="shared" si="7"/>
-        <v>0.71542553191489366</v>
+        <f t="shared" si="8"/>
+        <v>0.4627659574468086</v>
       </c>
       <c r="L33" s="9"/>
       <c r="M33" s="10"/>
       <c r="N33" s="103">
-        <v>129</v>
-      </c>
-      <c r="O33" s="35"/>
-      <c r="P33" s="15" t="s">
-        <v>18</v>
+        <v>110</v>
+      </c>
+      <c r="O33" s="11"/>
+      <c r="P33" s="39" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="15.75" customHeight="1">
@@ -3045,7 +3050,7 @@
         <v>20</v>
       </c>
       <c r="G34" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="H34" s="10">
@@ -3055,35 +3060,35 @@
         <v>3.76</v>
       </c>
       <c r="J34" s="9">
-        <f>N34/F$30</f>
-        <v>6</v>
+        <f>N34/F$31</f>
+        <v>6.45</v>
       </c>
       <c r="K34" s="73">
-        <f t="shared" si="7"/>
-        <v>0.59574468085106402</v>
+        <f t="shared" si="8"/>
+        <v>0.71542553191489366</v>
       </c>
       <c r="L34" s="9"/>
       <c r="M34" s="10"/>
       <c r="N34" s="103">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="O34" s="35"/>
-      <c r="P34" s="28" t="s">
-        <v>32</v>
+      <c r="P34" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="15.75" customHeight="1">
       <c r="A35" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="84" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="30" t="s">
+      <c r="B35" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>34</v>
@@ -3092,30 +3097,31 @@
         <v>20</v>
       </c>
       <c r="G35" s="7">
-        <f t="shared" ref="G35" si="9">F35*42</f>
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="10">
         <v>42</v>
       </c>
       <c r="I35" s="7">
-        <v>3.91</v>
-      </c>
-      <c r="J35" s="34">
-        <v>6.75</v>
+        <v>3.76</v>
+      </c>
+      <c r="J35" s="9">
+        <f>N35/F$31</f>
+        <v>6</v>
       </c>
       <c r="K35" s="73">
-        <f t="shared" si="7"/>
-        <v>0.7263427109974423</v>
-      </c>
-      <c r="L35" s="34"/>
-      <c r="M35" s="14"/>
+        <f t="shared" si="8"/>
+        <v>0.59574468085106402</v>
+      </c>
+      <c r="L35" s="9"/>
+      <c r="M35" s="10"/>
       <c r="N35" s="103">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="O35" s="35"/>
-      <c r="P35" s="101" t="s">
-        <v>123</v>
+      <c r="P35" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1">
@@ -3138,7 +3144,7 @@
         <v>20</v>
       </c>
       <c r="G36" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G36" si="10">F36*42</f>
         <v>840</v>
       </c>
       <c r="H36" s="14">
@@ -3148,21 +3154,20 @@
         <v>3.91</v>
       </c>
       <c r="J36" s="34">
-        <f>N36/F36</f>
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="K36" s="73">
-        <f t="shared" si="7"/>
-        <v>0.47058823529411753</v>
+        <f t="shared" si="8"/>
+        <v>0.7263427109974423</v>
       </c>
       <c r="L36" s="34"/>
       <c r="M36" s="14"/>
       <c r="N36" s="103">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="O36" s="35"/>
-      <c r="P36" s="39" t="s">
-        <v>36</v>
+      <c r="P36" s="101" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="15.75" customHeight="1">
@@ -3185,7 +3190,7 @@
         <v>20</v>
       </c>
       <c r="G37" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="H37" s="14">
@@ -3195,21 +3200,21 @@
         <v>3.91</v>
       </c>
       <c r="J37" s="34">
-        <f>N37/F$36</f>
-        <v>6.75</v>
+        <f>N37/F37</f>
+        <v>5.75</v>
       </c>
       <c r="K37" s="73">
-        <f>J37/I36-1</f>
-        <v>0.7263427109974423</v>
+        <f t="shared" si="8"/>
+        <v>0.47058823529411753</v>
       </c>
       <c r="L37" s="34"/>
       <c r="M37" s="14"/>
       <c r="N37" s="103">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="O37" s="35"/>
-      <c r="P37" s="15" t="s">
-        <v>18</v>
+      <c r="P37" s="39" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="15.75" customHeight="1">
@@ -3232,7 +3237,7 @@
         <v>20</v>
       </c>
       <c r="G38" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="H38" s="14">
@@ -3242,21 +3247,21 @@
         <v>3.91</v>
       </c>
       <c r="J38" s="34">
-        <f>N38/F$36</f>
-        <v>6.25</v>
+        <f>N38/F$37</f>
+        <v>6.75</v>
       </c>
       <c r="K38" s="73">
-        <f>J38/I36-1</f>
-        <v>0.59846547314577991</v>
+        <f>J38/I37-1</f>
+        <v>0.7263427109974423</v>
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="14"/>
       <c r="N38" s="103">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="O38" s="35"/>
-      <c r="P38" s="28" t="s">
-        <v>32</v>
+      <c r="P38" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="15.75" customHeight="1">
@@ -3264,13 +3269,13 @@
         <v>30</v>
       </c>
       <c r="B39" s="84" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C39" s="30" t="s">
         <v>39</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>34</v>
@@ -3279,33 +3284,34 @@
         <v>20</v>
       </c>
       <c r="G39" s="7">
-        <f t="shared" ref="G39" si="10">F39*42</f>
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="H39" s="14">
         <v>42</v>
       </c>
       <c r="I39" s="7">
-        <v>4.43</v>
+        <v>3.91</v>
       </c>
       <c r="J39" s="34">
-        <v>6.75</v>
+        <f>N39/F$37</f>
+        <v>6.25</v>
       </c>
       <c r="K39" s="73">
-        <f t="shared" si="1"/>
-        <v>0.52370203160270901</v>
+        <f>J39/I37-1</f>
+        <v>0.59846547314577991</v>
       </c>
       <c r="L39" s="34"/>
       <c r="M39" s="14"/>
       <c r="N39" s="103">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="O39" s="35"/>
-      <c r="P39" s="101" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="18.75" customHeight="1">
+      <c r="P39" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15.75" customHeight="1">
       <c r="A40" s="75" t="s">
         <v>30</v>
       </c>
@@ -3325,7 +3331,7 @@
         <v>20</v>
       </c>
       <c r="G40" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G40" si="11">F40*42</f>
         <v>840</v>
       </c>
       <c r="H40" s="14">
@@ -3335,21 +3341,20 @@
         <v>4.43</v>
       </c>
       <c r="J40" s="34">
-        <f>N40/F$40</f>
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="K40" s="73">
-        <f t="shared" si="1"/>
-        <v>0.2979683972911964</v>
+        <f t="shared" si="2"/>
+        <v>0.52370203160270901</v>
       </c>
       <c r="L40" s="34"/>
       <c r="M40" s="14"/>
       <c r="N40" s="103">
-        <v>115</v>
-      </c>
-      <c r="O40" s="11"/>
-      <c r="P40" s="39" t="s">
-        <v>36</v>
+        <v>135</v>
+      </c>
+      <c r="O40" s="35"/>
+      <c r="P40" s="101" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="18.75" customHeight="1">
@@ -3372,7 +3377,7 @@
         <v>20</v>
       </c>
       <c r="G41" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="H41" s="14">
@@ -3382,21 +3387,21 @@
         <v>4.43</v>
       </c>
       <c r="J41" s="34">
-        <f>N41/F$40</f>
-        <v>6.75</v>
+        <f>N41/F$41</f>
+        <v>5.75</v>
       </c>
       <c r="K41" s="73">
-        <f>J41/I40-1</f>
-        <v>0.52370203160270901</v>
+        <f t="shared" si="2"/>
+        <v>0.2979683972911964</v>
       </c>
       <c r="L41" s="34"/>
       <c r="M41" s="14"/>
       <c r="N41" s="103">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="O41" s="11"/>
-      <c r="P41" s="15" t="s">
-        <v>18</v>
+      <c r="P41" s="39" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18.75" customHeight="1">
@@ -3419,7 +3424,7 @@
         <v>20</v>
       </c>
       <c r="G42" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
       <c r="H42" s="14">
@@ -3429,71 +3434,68 @@
         <v>4.43</v>
       </c>
       <c r="J42" s="34">
-        <f>N42/F$40</f>
-        <v>6.25</v>
+        <f>N42/F$41</f>
+        <v>6.75</v>
       </c>
       <c r="K42" s="73">
-        <f>J42/I40-1</f>
-        <v>0.4108352144469527</v>
+        <f>J42/I41-1</f>
+        <v>0.52370203160270901</v>
       </c>
       <c r="L42" s="34"/>
       <c r="M42" s="14"/>
       <c r="N42" s="103">
+        <v>135</v>
+      </c>
+      <c r="O42" s="11"/>
+      <c r="P42" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="18.75" customHeight="1">
+      <c r="A43" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="7">
+        <v>20</v>
+      </c>
+      <c r="G43" s="7">
+        <f t="shared" si="7"/>
+        <v>840</v>
+      </c>
+      <c r="H43" s="14">
+        <v>42</v>
+      </c>
+      <c r="I43" s="7">
+        <v>4.43</v>
+      </c>
+      <c r="J43" s="34">
+        <f>N43/F$41</f>
+        <v>6.25</v>
+      </c>
+      <c r="K43" s="73">
+        <f>J43/I41-1</f>
+        <v>0.4108352144469527</v>
+      </c>
+      <c r="L43" s="34"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="103">
         <v>125</v>
       </c>
-      <c r="O42" s="11"/>
-      <c r="P42" s="28" t="s">
+      <c r="O43" s="11"/>
+      <c r="P43" s="28" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A43" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="81" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="40">
-        <v>5</v>
-      </c>
-      <c r="F43" s="10">
-        <v>40</v>
-      </c>
-      <c r="G43" s="10">
-        <f t="shared" si="6"/>
-        <v>1680</v>
-      </c>
-      <c r="H43" s="10">
-        <v>42</v>
-      </c>
-      <c r="I43" s="10">
-        <v>4.92</v>
-      </c>
-      <c r="J43" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="K43" s="73">
-        <f t="shared" si="1"/>
-        <v>0.32113821138211374</v>
-      </c>
-      <c r="L43" s="9">
-        <f>N43/8</f>
-        <v>32.5</v>
-      </c>
-      <c r="M43" s="10"/>
-      <c r="N43" s="103">
-        <f>J43*F43</f>
-        <v>260</v>
-      </c>
-      <c r="O43" s="11"/>
-      <c r="P43" s="41" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="15.75" customHeight="1">
@@ -3501,13 +3503,13 @@
         <v>53</v>
       </c>
       <c r="B44" s="81" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E44" s="40">
         <v>5</v>
@@ -3516,21 +3518,21 @@
         <v>40</v>
       </c>
       <c r="G44" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1680</v>
       </c>
       <c r="H44" s="10">
         <v>42</v>
       </c>
       <c r="I44" s="10">
-        <v>4.7300000000000004</v>
+        <v>4.92</v>
       </c>
       <c r="J44" s="9">
         <v>6.5</v>
       </c>
       <c r="K44" s="73">
-        <f t="shared" si="1"/>
-        <v>0.37420718816067633</v>
+        <f t="shared" si="2"/>
+        <v>0.32113821138211374</v>
       </c>
       <c r="L44" s="9">
         <f>N44/8</f>
@@ -3546,51 +3548,54 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A45" s="75" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45" s="7" t="s">
+    <row r="45" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A45" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="81" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D45" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F45" s="7">
-        <v>30</v>
-      </c>
-      <c r="G45" s="7">
-        <f t="shared" si="6"/>
-        <v>1260</v>
+      <c r="D45" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="40">
+        <v>5</v>
+      </c>
+      <c r="F45" s="10">
+        <v>40</v>
+      </c>
+      <c r="G45" s="10">
+        <f t="shared" si="7"/>
+        <v>1680</v>
       </c>
       <c r="H45" s="10">
         <v>42</v>
       </c>
-      <c r="I45" s="7">
-        <v>4.84</v>
+      <c r="I45" s="10">
+        <v>4.7300000000000004</v>
       </c>
       <c r="J45" s="9">
-        <f>N45/F45</f>
-        <v>6.333333333333333</v>
+        <v>6.5</v>
       </c>
       <c r="K45" s="73">
-        <f t="shared" si="1"/>
-        <v>0.30853994490358128</v>
-      </c>
-      <c r="L45" s="9"/>
+        <f t="shared" si="2"/>
+        <v>0.37420718816067633</v>
+      </c>
+      <c r="L45" s="9">
+        <f>N45/8</f>
+        <v>32.5</v>
+      </c>
       <c r="M45" s="10"/>
       <c r="N45" s="103">
-        <v>190</v>
-      </c>
-      <c r="O45" s="43"/>
-      <c r="P45" s="44" t="s">
-        <v>62</v>
+        <f>J45*F45</f>
+        <v>260</v>
+      </c>
+      <c r="O45" s="11"/>
+      <c r="P45" s="41" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
@@ -3613,7 +3618,7 @@
         <v>30</v>
       </c>
       <c r="G46" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1260</v>
       </c>
       <c r="H46" s="10">
@@ -3623,21 +3628,21 @@
         <v>4.84</v>
       </c>
       <c r="J46" s="9">
-        <f>N46/F45</f>
-        <v>5.75</v>
+        <f>N46/F46</f>
+        <v>6.333333333333333</v>
       </c>
       <c r="K46" s="73">
-        <f>J46/I45-1</f>
-        <v>0.18801652892561993</v>
-      </c>
-      <c r="L46" s="31"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="80">
-        <v>172.5</v>
-      </c>
-      <c r="O46" s="46"/>
-      <c r="P46" s="39" t="s">
-        <v>36</v>
+        <f t="shared" si="2"/>
+        <v>0.30853994490358128</v>
+      </c>
+      <c r="L46" s="9"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="103">
+        <v>190</v>
+      </c>
+      <c r="O46" s="43"/>
+      <c r="P46" s="44" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
@@ -3645,53 +3650,46 @@
         <v>59</v>
       </c>
       <c r="B47" s="82" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.1000000000000001</v>
+        <v>61</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="F47" s="7">
-        <f>18*1.1</f>
-        <v>19.8</v>
+        <v>30</v>
       </c>
       <c r="G47" s="7">
-        <f t="shared" ref="G47:G54" si="11">F47*42</f>
-        <v>831.6</v>
-      </c>
-      <c r="H47" s="7">
+        <f t="shared" si="7"/>
+        <v>1260</v>
+      </c>
+      <c r="H47" s="10">
         <v>42</v>
       </c>
       <c r="I47" s="7">
-        <v>5.34</v>
-      </c>
-      <c r="J47" s="31">
-        <f>N47/F47</f>
-        <v>5.954545454545455</v>
+        <v>4.84</v>
+      </c>
+      <c r="J47" s="9">
+        <f>N47/F46</f>
+        <v>5.75</v>
       </c>
       <c r="K47" s="73">
-        <f t="shared" si="1"/>
-        <v>0.11508341845420511</v>
-      </c>
-      <c r="L47" s="31">
-        <f>N47/18</f>
-        <v>6.5500000000000007</v>
-      </c>
+        <f>J47/I46-1</f>
+        <v>0.18801652892561993</v>
+      </c>
+      <c r="L47" s="31"/>
       <c r="M47" s="7"/>
       <c r="N47" s="80">
-        <v>117.9</v>
-      </c>
-      <c r="O47" s="31">
-        <f>6.36*18</f>
-        <v>114.48</v>
-      </c>
-      <c r="P47" s="47" t="s">
-        <v>65</v>
+        <v>172.5</v>
+      </c>
+      <c r="O47" s="46"/>
+      <c r="P47" s="39" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
@@ -3699,479 +3697,480 @@
         <v>59</v>
       </c>
       <c r="B48" s="82" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D48" s="95" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F48" s="60">
+      <c r="D48" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F48" s="7">
         <v>30</v>
       </c>
-      <c r="G48" s="60">
+      <c r="G48" s="7">
         <f t="shared" ref="G48" si="12">F48*42</f>
         <v>1260</v>
       </c>
-      <c r="H48" s="60">
-        <v>42</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J48" s="96">
+      <c r="H48" s="10">
+        <v>42</v>
+      </c>
+      <c r="I48" s="7">
+        <v>4.84</v>
+      </c>
+      <c r="J48" s="31">
+        <f>N48/F48</f>
         <v>6.35</v>
       </c>
-      <c r="K48" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L48" s="96"/>
-      <c r="M48" s="60"/>
-      <c r="N48" s="103">
-        <f>J48*F48</f>
+      <c r="K48" s="73">
+        <f>J48/I47-1</f>
+        <v>0.31198347107438007</v>
+      </c>
+      <c r="L48" s="31"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="80">
         <v>190.5</v>
       </c>
-      <c r="O48" s="97"/>
-      <c r="P48" s="98" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" s="45" customFormat="1" ht="15.6" customHeight="1">
+      <c r="O48" s="46"/>
+      <c r="P48" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
       <c r="A49" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="86" t="s">
-        <v>66</v>
-      </c>
-      <c r="C49" s="48" t="s">
+      <c r="B49" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="F49" s="50">
-        <v>30</v>
-      </c>
-      <c r="G49" s="50">
-        <f t="shared" si="11"/>
-        <v>1260</v>
-      </c>
-      <c r="H49" s="50">
-        <v>42</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49" s="51">
-        <v>5.15</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L49" s="51"/>
-      <c r="M49" s="50"/>
-      <c r="N49" s="107">
+      <c r="D49" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F49" s="7">
+        <f>18*1.1</f>
+        <v>19.8</v>
+      </c>
+      <c r="G49" s="7">
+        <f t="shared" ref="G49:G56" si="13">F49*42</f>
+        <v>831.6</v>
+      </c>
+      <c r="H49" s="7">
+        <v>42</v>
+      </c>
+      <c r="I49" s="7">
+        <v>5.34</v>
+      </c>
+      <c r="J49" s="31">
+        <f>N49/F49</f>
+        <v>5.954545454545455</v>
+      </c>
+      <c r="K49" s="73">
+        <f t="shared" si="2"/>
+        <v>0.11508341845420511</v>
+      </c>
+      <c r="L49" s="31">
+        <f>N49/18</f>
+        <v>6.5500000000000007</v>
+      </c>
+      <c r="M49" s="7"/>
+      <c r="N49" s="80">
         <v>117.9</v>
       </c>
-      <c r="O49" s="51"/>
-      <c r="P49" s="52"/>
+      <c r="O49" s="31">
+        <f>6.36*18</f>
+        <v>114.48</v>
+      </c>
+      <c r="P49" s="47" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="50" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
       <c r="A50" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="83" t="s">
+      <c r="B50" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="95" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F50" s="60">
+        <v>30</v>
+      </c>
+      <c r="G50" s="60">
+        <f t="shared" ref="G50" si="14">F50*42</f>
+        <v>1260</v>
+      </c>
+      <c r="H50" s="60">
+        <v>42</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J50" s="96">
+        <v>6.35</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50" s="96"/>
+      <c r="M50" s="60"/>
+      <c r="N50" s="103">
+        <f>J50*F50</f>
+        <v>190.5</v>
+      </c>
+      <c r="O50" s="97"/>
+      <c r="P50" s="98" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" s="45" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A51" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="86" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="F51" s="50">
+        <v>30</v>
+      </c>
+      <c r="G51" s="50">
+        <f t="shared" si="13"/>
+        <v>1260</v>
+      </c>
+      <c r="H51" s="50">
+        <v>42</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J51" s="51">
+        <v>5.15</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51" s="51"/>
+      <c r="M51" s="50"/>
+      <c r="N51" s="107">
+        <v>117.9</v>
+      </c>
+      <c r="O51" s="51"/>
+      <c r="P51" s="52"/>
+    </row>
+    <row r="52" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A52" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="53" t="s">
+      <c r="C52" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D50" s="54" t="s">
+      <c r="D52" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="E50" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="F50" s="53">
+      <c r="E52" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F52" s="53">
         <v>30</v>
       </c>
-      <c r="G50" s="50">
-        <f t="shared" si="11"/>
+      <c r="G52" s="50">
+        <f t="shared" si="13"/>
         <v>1260</v>
       </c>
-      <c r="H50" s="53">
-        <v>42</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J50" s="56"/>
-      <c r="K50" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L50" s="56"/>
-      <c r="M50" s="53"/>
-      <c r="N50" s="108"/>
-      <c r="O50" s="56"/>
-      <c r="P50" s="57"/>
-    </row>
-    <row r="51" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A51" s="75" t="s">
+      <c r="H52" s="53">
+        <v>42</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J52" s="56"/>
+      <c r="K52" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52" s="56"/>
+      <c r="M52" s="53"/>
+      <c r="N52" s="108"/>
+      <c r="O52" s="56"/>
+      <c r="P52" s="57"/>
+    </row>
+    <row r="53" spans="1:16" s="45" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A53" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="78" t="s">
+      <c r="B53" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="C51" s="30" t="s">
+      <c r="C53" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D53" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E51" s="10">
+      <c r="E53" s="10">
         <v>5</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F53" s="10">
         <v>30</v>
       </c>
-      <c r="G51" s="7">
-        <f t="shared" si="11"/>
+      <c r="G53" s="7">
+        <f t="shared" si="13"/>
         <v>1260</v>
       </c>
-      <c r="H51" s="10">
-        <v>42</v>
-      </c>
-      <c r="I51" s="10">
+      <c r="H53" s="10">
+        <v>42</v>
+      </c>
+      <c r="I53" s="10">
         <v>0.94</v>
       </c>
-      <c r="J51" s="9">
-        <f>N51/F51</f>
+      <c r="J53" s="9">
+        <f>N53/F53</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="K51" s="73">
-        <f t="shared" si="1"/>
+      <c r="K53" s="73">
+        <f t="shared" si="2"/>
         <v>0.22340425531914887</v>
       </c>
-      <c r="L51" s="9">
-        <f>N51/6</f>
+      <c r="L53" s="9">
+        <f>N53/6</f>
         <v>5.75</v>
       </c>
-      <c r="M51" s="10"/>
-      <c r="N51" s="103">
+      <c r="M53" s="10"/>
+      <c r="N53" s="103">
         <v>34.5</v>
       </c>
-      <c r="O51" s="11">
+      <c r="O53" s="11">
         <v>30</v>
       </c>
-      <c r="P51" s="58" t="s">
+      <c r="P53" s="58" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="15.75">
-      <c r="A52" s="75" t="s">
+    <row r="54" spans="1:16" ht="15.75">
+      <c r="A54" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B52" s="78" t="s">
+      <c r="B54" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="30" t="s">
+      <c r="C54" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D54" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E54" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F54" s="10">
         <f>25*1.1</f>
         <v>27.500000000000004</v>
       </c>
-      <c r="G52" s="10">
-        <f t="shared" si="11"/>
+      <c r="G54" s="10">
+        <f t="shared" si="13"/>
         <v>1155.0000000000002</v>
       </c>
-      <c r="H52" s="10">
-        <v>42</v>
-      </c>
-      <c r="I52" s="10">
+      <c r="H54" s="10">
+        <v>42</v>
+      </c>
+      <c r="I54" s="10">
         <v>1.42</v>
       </c>
-      <c r="J52" s="9">
-        <f>N52/F52</f>
+      <c r="J54" s="9">
+        <f>N54/F54</f>
         <v>1.6363636363636362</v>
       </c>
-      <c r="K52" s="73">
-        <f t="shared" si="1"/>
+      <c r="K54" s="73">
+        <f t="shared" si="2"/>
         <v>0.15236875800256078</v>
       </c>
-      <c r="L52" s="9">
-        <f>N52/25</f>
+      <c r="L54" s="9">
+        <f>N54/25</f>
         <v>1.8</v>
-      </c>
-      <c r="M52" s="10"/>
-      <c r="N52" s="103">
-        <v>45</v>
-      </c>
-      <c r="O52" s="9">
-        <v>45</v>
-      </c>
-      <c r="P52" s="59" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
-      <c r="A53" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" s="85" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E53" s="17">
-        <v>0.875</v>
-      </c>
-      <c r="F53" s="60">
-        <f>E53*24</f>
-        <v>21</v>
-      </c>
-      <c r="G53" s="10">
-        <f t="shared" si="11"/>
-        <v>882</v>
-      </c>
-      <c r="H53" s="10">
-        <v>42</v>
-      </c>
-      <c r="I53" s="10">
-        <v>9.1199999999999992</v>
-      </c>
-      <c r="J53" s="9">
-        <f>N53/F53</f>
-        <v>10.8</v>
-      </c>
-      <c r="K53" s="73">
-        <f t="shared" si="1"/>
-        <v>0.1842105263157896</v>
-      </c>
-      <c r="L53" s="9">
-        <f>N53/24</f>
-        <v>9.4500000000000011</v>
-      </c>
-      <c r="M53" s="10"/>
-      <c r="N53" s="103">
-        <v>226.8</v>
-      </c>
-      <c r="O53" s="9">
-        <v>226.8</v>
-      </c>
-      <c r="P53" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
-      <c r="A54" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B54" s="85" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E54" s="17">
-        <v>0.75</v>
-      </c>
-      <c r="F54" s="60">
-        <v>19.5</v>
-      </c>
-      <c r="G54" s="10">
-        <f t="shared" si="11"/>
-        <v>819</v>
-      </c>
-      <c r="H54" s="10">
-        <v>42</v>
-      </c>
-      <c r="I54" s="10">
-        <v>5.21</v>
-      </c>
-      <c r="J54" s="9">
-        <f>O54/F54</f>
-        <v>7.5066666666666668</v>
-      </c>
-      <c r="K54" s="73">
-        <f t="shared" si="1"/>
-        <v>0.44081893793985927</v>
-      </c>
-      <c r="L54" s="9">
-        <f>N54/26</f>
-        <v>5.63</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="103">
-        <v>146.38</v>
+        <v>45</v>
       </c>
       <c r="O54" s="9">
-        <v>146.38</v>
-      </c>
-      <c r="P54" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="P54" s="59" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:16" s="62" customFormat="1" ht="18" customHeight="1">
-      <c r="A55" s="99" t="s">
-        <v>81</v>
+    <row r="55" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
+      <c r="A55" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="B55" s="85" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C55" s="30" t="s">
         <v>15</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E55" s="64"/>
-      <c r="F55" s="65"/>
-      <c r="G55" s="65"/>
-      <c r="H55" s="65"/>
-      <c r="I55" s="65"/>
-      <c r="J55" s="66"/>
-      <c r="K55" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L55" s="66"/>
-      <c r="M55" s="67"/>
-      <c r="N55" s="109"/>
-      <c r="O55" s="63"/>
-      <c r="P55" s="61"/>
-    </row>
-    <row r="56" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A56" s="75" t="s">
-        <v>84</v>
-      </c>
-      <c r="B56" s="87" t="s">
-        <v>85</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D56" s="68" t="s">
-        <v>87</v>
-      </c>
-      <c r="E56" s="68">
-        <v>5</v>
+        <v>78</v>
+      </c>
+      <c r="E55" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="F55" s="60">
+        <f>E55*24</f>
+        <v>21</v>
+      </c>
+      <c r="G55" s="10">
+        <f t="shared" si="13"/>
+        <v>882</v>
+      </c>
+      <c r="H55" s="10">
+        <v>42</v>
+      </c>
+      <c r="I55" s="10">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="J55" s="9">
+        <f>N55/F55</f>
+        <v>10.8</v>
+      </c>
+      <c r="K55" s="73">
+        <f t="shared" si="2"/>
+        <v>0.1842105263157896</v>
+      </c>
+      <c r="L55" s="9">
+        <f>N55/24</f>
+        <v>9.4500000000000011</v>
+      </c>
+      <c r="M55" s="10"/>
+      <c r="N55" s="103">
+        <v>226.8</v>
+      </c>
+      <c r="O55" s="9">
+        <v>226.8</v>
+      </c>
+      <c r="P55" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" s="45" customFormat="1" ht="18" customHeight="1">
+      <c r="A56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" s="17">
+        <v>0.75</v>
       </c>
       <c r="F56" s="60">
-        <v>40</v>
+        <v>19.5</v>
       </c>
       <c r="G56" s="10">
-        <f>F56*H56</f>
-        <v>1400</v>
+        <f t="shared" si="13"/>
+        <v>819</v>
       </c>
       <c r="H56" s="10">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I56" s="10">
-        <v>1.26</v>
+        <v>5.21</v>
       </c>
       <c r="J56" s="9">
-        <v>1.95</v>
+        <f>O56/F56</f>
+        <v>7.5066666666666668</v>
       </c>
       <c r="K56" s="73">
-        <f t="shared" si="1"/>
-        <v>0.54761904761904767</v>
+        <f t="shared" si="2"/>
+        <v>0.44081893793985927</v>
       </c>
       <c r="L56" s="9">
-        <f>N56/8</f>
-        <v>9.75</v>
+        <f>N56/26</f>
+        <v>5.63</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="103">
-        <f>J56*F56</f>
-        <v>78</v>
-      </c>
-      <c r="O56" s="11"/>
-      <c r="P56" s="69" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" s="62" customFormat="1" ht="21" customHeight="1">
-      <c r="A57" s="75" t="s">
-        <v>84</v>
-      </c>
-      <c r="B57" s="87" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D57" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="E57" s="68">
-        <v>5</v>
-      </c>
-      <c r="F57" s="60">
-        <v>40</v>
-      </c>
-      <c r="G57" s="10">
-        <f t="shared" ref="G57:G67" si="13">F57*H57</f>
-        <v>1400</v>
-      </c>
-      <c r="H57" s="10">
-        <v>35</v>
-      </c>
-      <c r="I57" s="10">
-        <v>1.53</v>
-      </c>
-      <c r="J57" s="9">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="K57" s="73">
-        <f t="shared" si="1"/>
-        <v>0.50326797385620892</v>
-      </c>
-      <c r="L57" s="9">
-        <f t="shared" ref="L57:L67" si="14">N57/8</f>
-        <v>11.5</v>
-      </c>
-      <c r="M57" s="10"/>
-      <c r="N57" s="103">
-        <f t="shared" ref="N57:N67" si="15">J57*F57</f>
-        <v>92</v>
-      </c>
-      <c r="O57" s="11"/>
-      <c r="P57" s="69" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" s="62" customFormat="1" ht="21" customHeight="1">
+        <v>146.38</v>
+      </c>
+      <c r="O56" s="9">
+        <v>146.38</v>
+      </c>
+      <c r="P56" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" s="62" customFormat="1" ht="18" customHeight="1">
+      <c r="A57" s="99" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="65"/>
+      <c r="J57" s="66"/>
+      <c r="K57" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L57" s="66"/>
+      <c r="M57" s="67"/>
+      <c r="N57" s="109"/>
+      <c r="O57" s="63"/>
+      <c r="P57" s="61"/>
+    </row>
+    <row r="58" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
       <c r="A58" s="75" t="s">
         <v>84</v>
       </c>
       <c r="B58" s="87" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>86</v>
       </c>
       <c r="D58" s="68" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E58" s="68">
         <v>5</v>
@@ -4180,48 +4179,48 @@
         <v>40</v>
       </c>
       <c r="G58" s="10">
-        <f t="shared" si="13"/>
+        <f>F58*H58</f>
         <v>1400</v>
       </c>
       <c r="H58" s="10">
         <v>35</v>
       </c>
       <c r="I58" s="10">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="J58" s="9">
-        <v>2.2999999999999998</v>
+        <v>1.95</v>
       </c>
       <c r="K58" s="73">
-        <f t="shared" si="1"/>
-        <v>0.30681818181818166</v>
+        <f t="shared" si="2"/>
+        <v>0.54761904761904767</v>
       </c>
       <c r="L58" s="9">
-        <f t="shared" si="14"/>
-        <v>11.5</v>
+        <f>N58/8</f>
+        <v>9.75</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="103">
-        <f t="shared" si="15"/>
-        <v>92</v>
+        <f>J58*F58</f>
+        <v>78</v>
       </c>
       <c r="O58" s="11"/>
       <c r="P58" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="59" spans="1:16" s="62" customFormat="1" ht="18" customHeight="1">
+    <row r="59" spans="1:16" s="62" customFormat="1" ht="21" customHeight="1">
       <c r="A59" s="75" t="s">
         <v>84</v>
       </c>
       <c r="B59" s="87" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>86</v>
       </c>
       <c r="D59" s="68" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E59" s="68">
         <v>5</v>
@@ -4230,47 +4229,48 @@
         <v>40</v>
       </c>
       <c r="G59" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="G59:G69" si="15">F59*H59</f>
         <v>1400</v>
       </c>
       <c r="H59" s="10">
         <v>35</v>
       </c>
-      <c r="I59" s="7" t="s">
-        <v>34</v>
+      <c r="I59" s="10">
+        <v>1.53</v>
       </c>
       <c r="J59" s="9">
-        <v>5.2</v>
-      </c>
-      <c r="K59" s="7" t="s">
-        <v>34</v>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K59" s="73">
+        <f t="shared" si="2"/>
+        <v>0.50326797385620892</v>
       </c>
       <c r="L59" s="9">
-        <f t="shared" si="14"/>
-        <v>26</v>
+        <f t="shared" ref="L59:L69" si="16">N59/8</f>
+        <v>11.5</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="103">
-        <f t="shared" si="15"/>
-        <v>208</v>
+        <f t="shared" ref="N59:N69" si="17">J59*F59</f>
+        <v>92</v>
       </c>
       <c r="O59" s="11"/>
       <c r="P59" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="1:16" s="62" customFormat="1" ht="22.5" customHeight="1">
+    <row r="60" spans="1:16" s="62" customFormat="1" ht="21" customHeight="1">
       <c r="A60" s="75" t="s">
         <v>84</v>
       </c>
       <c r="B60" s="87" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>86</v>
       </c>
       <c r="D60" s="68" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E60" s="68">
         <v>5</v>
@@ -4279,48 +4279,48 @@
         <v>40</v>
       </c>
       <c r="G60" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1400</v>
       </c>
       <c r="H60" s="10">
         <v>35</v>
       </c>
       <c r="I60" s="10">
-        <v>2.75</v>
+        <v>1.76</v>
       </c>
       <c r="J60" s="9">
-        <v>3.38</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="K60" s="73">
-        <f t="shared" si="1"/>
-        <v>0.22909090909090901</v>
+        <f t="shared" si="2"/>
+        <v>0.30681818181818166</v>
       </c>
       <c r="L60" s="9">
-        <f t="shared" si="14"/>
-        <v>16.899999999999999</v>
+        <f t="shared" si="16"/>
+        <v>11.5</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="103">
-        <f t="shared" si="15"/>
-        <v>135.19999999999999</v>
+        <f t="shared" si="17"/>
+        <v>92</v>
       </c>
       <c r="O60" s="11"/>
       <c r="P60" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="1:16" s="62" customFormat="1" ht="20.25" customHeight="1">
+    <row r="61" spans="1:16" s="62" customFormat="1" ht="18" customHeight="1">
       <c r="A61" s="75" t="s">
         <v>84</v>
       </c>
       <c r="B61" s="87" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>86</v>
       </c>
       <c r="D61" s="68" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E61" s="68">
         <v>5</v>
@@ -4329,48 +4329,47 @@
         <v>40</v>
       </c>
       <c r="G61" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1400</v>
       </c>
       <c r="H61" s="10">
         <v>35</v>
       </c>
-      <c r="I61" s="10">
-        <v>2.7</v>
+      <c r="I61" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="J61" s="9">
-        <v>3.78</v>
-      </c>
-      <c r="K61" s="73">
-        <f t="shared" si="1"/>
-        <v>0.39999999999999991</v>
+        <v>5.2</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="L61" s="9">
-        <f t="shared" si="14"/>
-        <v>18.899999999999999</v>
+        <f t="shared" si="16"/>
+        <v>26</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="103">
-        <f t="shared" si="15"/>
-        <v>151.19999999999999</v>
+        <f t="shared" si="17"/>
+        <v>208</v>
       </c>
       <c r="O61" s="11"/>
       <c r="P61" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="62" spans="1:16" s="62" customFormat="1" ht="18" customHeight="1">
+    <row r="62" spans="1:16" s="62" customFormat="1" ht="22.5" customHeight="1">
       <c r="A62" s="75" t="s">
         <v>84</v>
       </c>
       <c r="B62" s="87" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>86</v>
       </c>
       <c r="D62" s="68" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E62" s="68">
         <v>5</v>
@@ -4379,48 +4378,48 @@
         <v>40</v>
       </c>
       <c r="G62" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1400</v>
       </c>
       <c r="H62" s="10">
         <v>35</v>
       </c>
       <c r="I62" s="10">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="J62" s="9">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="K62" s="73">
-        <f t="shared" si="1"/>
-        <v>0.41472868217054248</v>
+        <f t="shared" si="2"/>
+        <v>0.22909090909090901</v>
       </c>
       <c r="L62" s="9">
-        <f t="shared" si="14"/>
-        <v>18.25</v>
+        <f t="shared" si="16"/>
+        <v>16.899999999999999</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="103">
-        <f>J62*F62</f>
-        <v>146</v>
+        <f t="shared" si="17"/>
+        <v>135.19999999999999</v>
       </c>
       <c r="O62" s="11"/>
       <c r="P62" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="63" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
+    <row r="63" spans="1:16" s="62" customFormat="1" ht="20.25" customHeight="1">
       <c r="A63" s="75" t="s">
         <v>84</v>
       </c>
       <c r="B63" s="87" t="s">
-        <v>101</v>
-      </c>
-      <c r="C63" s="30" t="s">
-        <v>118</v>
+        <v>97</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="D63" s="68" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E63" s="68">
         <v>5</v>
@@ -4429,48 +4428,48 @@
         <v>40</v>
       </c>
       <c r="G63" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1400</v>
       </c>
       <c r="H63" s="10">
         <v>35</v>
       </c>
       <c r="I63" s="10">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J63" s="9">
-        <v>2.7</v>
+        <v>3.78</v>
       </c>
       <c r="K63" s="73">
-        <f t="shared" si="1"/>
-        <v>0.58823529411764719</v>
+        <f t="shared" si="2"/>
+        <v>0.39999999999999991</v>
       </c>
       <c r="L63" s="9">
-        <f t="shared" si="14"/>
-        <v>13.5</v>
+        <f t="shared" si="16"/>
+        <v>18.899999999999999</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="103">
-        <f t="shared" si="15"/>
-        <v>108</v>
+        <f t="shared" si="17"/>
+        <v>151.19999999999999</v>
       </c>
       <c r="O63" s="11"/>
       <c r="P63" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
+    <row r="64" spans="1:16" s="62" customFormat="1" ht="18" customHeight="1">
       <c r="A64" s="75" t="s">
         <v>84</v>
       </c>
       <c r="B64" s="87" t="s">
-        <v>103</v>
-      </c>
-      <c r="C64" s="30" t="s">
-        <v>118</v>
+        <v>99</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="D64" s="68" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E64" s="68">
         <v>5</v>
@@ -4479,30 +4478,30 @@
         <v>40</v>
       </c>
       <c r="G64" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1400</v>
       </c>
       <c r="H64" s="10">
         <v>35</v>
       </c>
       <c r="I64" s="10">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J64" s="9">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K64" s="73">
-        <f t="shared" si="1"/>
-        <v>0.53846153846153832</v>
+        <f t="shared" si="2"/>
+        <v>0.41472868217054248</v>
       </c>
       <c r="L64" s="9">
-        <f t="shared" si="14"/>
-        <v>20</v>
+        <f t="shared" si="16"/>
+        <v>18.25</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="103">
-        <f t="shared" si="15"/>
-        <v>160</v>
+        <f>J64*F64</f>
+        <v>146</v>
       </c>
       <c r="O64" s="11"/>
       <c r="P64" s="69" t="s">
@@ -4513,14 +4512,14 @@
       <c r="A65" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B65" s="88" t="s">
-        <v>105</v>
+      <c r="B65" s="87" t="s">
+        <v>101</v>
       </c>
       <c r="C65" s="30" t="s">
         <v>118</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E65" s="68">
         <v>5</v>
@@ -4529,47 +4528,48 @@
         <v>40</v>
       </c>
       <c r="G65" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1400</v>
       </c>
       <c r="H65" s="10">
         <v>35</v>
       </c>
-      <c r="I65" s="7">
-        <v>7.5</v>
+      <c r="I65" s="10">
+        <v>1.7</v>
       </c>
       <c r="J65" s="9">
-        <f>N65/40</f>
-        <v>7.5</v>
-      </c>
-      <c r="K65" s="7" t="s">
-        <v>34</v>
+        <v>2.7</v>
+      </c>
+      <c r="K65" s="73">
+        <f t="shared" si="2"/>
+        <v>0.58823529411764719</v>
       </c>
       <c r="L65" s="9">
-        <f t="shared" si="14"/>
-        <v>37.5</v>
+        <f t="shared" si="16"/>
+        <v>13.5</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="103">
-        <v>300</v>
+        <f t="shared" si="17"/>
+        <v>108</v>
       </c>
       <c r="O65" s="11"/>
-      <c r="P65" s="44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" s="70" customFormat="1" ht="21">
+      <c r="P65" s="69" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
       <c r="A66" s="75" t="s">
         <v>84</v>
       </c>
       <c r="B66" s="87" t="s">
-        <v>107</v>
-      </c>
-      <c r="C66" s="100" t="s">
-        <v>108</v>
+        <v>103</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>118</v>
       </c>
       <c r="D66" s="68" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E66" s="68">
         <v>5</v>
@@ -4578,30 +4578,30 @@
         <v>40</v>
       </c>
       <c r="G66" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1400</v>
       </c>
       <c r="H66" s="10">
         <v>35</v>
       </c>
       <c r="I66" s="10">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="J66" s="9">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="K66" s="73">
-        <f t="shared" si="1"/>
-        <v>0.96202531645569622</v>
+        <f t="shared" si="2"/>
+        <v>0.53846153846153832</v>
       </c>
       <c r="L66" s="9">
-        <f>N66/8</f>
-        <v>15.5</v>
+        <f t="shared" si="16"/>
+        <v>20</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="103">
-        <f t="shared" si="15"/>
-        <v>124</v>
+        <f t="shared" si="17"/>
+        <v>160</v>
       </c>
       <c r="O66" s="11"/>
       <c r="P66" s="69" t="s">
@@ -4612,12 +4612,14 @@
       <c r="A67" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B67" s="87" t="s">
-        <v>110</v>
-      </c>
-      <c r="C67" s="94"/>
+      <c r="B67" s="88" t="s">
+        <v>105</v>
+      </c>
+      <c r="C67" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="D67" s="68" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E67" s="68">
         <v>5</v>
@@ -4626,37 +4628,134 @@
         <v>40</v>
       </c>
       <c r="G67" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1400</v>
       </c>
       <c r="H67" s="10">
         <v>35</v>
       </c>
-      <c r="I67" s="7" t="s">
-        <v>34</v>
+      <c r="I67" s="7">
+        <v>7.5</v>
       </c>
       <c r="J67" s="9">
-        <v>4</v>
+        <f>N67/40</f>
+        <v>7.5</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>34</v>
       </c>
       <c r="L67" s="9">
-        <f t="shared" si="14"/>
-        <v>20</v>
+        <f t="shared" si="16"/>
+        <v>37.5</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="103">
+        <v>300</v>
+      </c>
+      <c r="O67" s="11"/>
+      <c r="P67" s="44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" s="70" customFormat="1" ht="21">
+      <c r="A68" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" s="87" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" s="100" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="E68" s="68">
+        <v>5</v>
+      </c>
+      <c r="F68" s="60">
+        <v>40</v>
+      </c>
+      <c r="G68" s="10">
         <f t="shared" si="15"/>
+        <v>1400</v>
+      </c>
+      <c r="H68" s="10">
+        <v>35</v>
+      </c>
+      <c r="I68" s="10">
+        <v>1.58</v>
+      </c>
+      <c r="J68" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="K68" s="73">
+        <f t="shared" si="2"/>
+        <v>0.96202531645569622</v>
+      </c>
+      <c r="L68" s="9">
+        <f>N68/8</f>
+        <v>15.5</v>
+      </c>
+      <c r="M68" s="10"/>
+      <c r="N68" s="103">
+        <f t="shared" si="17"/>
+        <v>124</v>
+      </c>
+      <c r="O68" s="11"/>
+      <c r="P68" s="69" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" s="62" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A69" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="C69" s="94"/>
+      <c r="D69" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="E69" s="68">
+        <v>5</v>
+      </c>
+      <c r="F69" s="60">
+        <v>40</v>
+      </c>
+      <c r="G69" s="10">
+        <f t="shared" si="15"/>
+        <v>1400</v>
+      </c>
+      <c r="H69" s="10">
+        <v>35</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J69" s="9">
+        <v>4</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L69" s="9">
+        <f t="shared" si="16"/>
+        <v>20</v>
+      </c>
+      <c r="M69" s="10"/>
+      <c r="N69" s="103">
+        <f t="shared" si="17"/>
         <v>160</v>
       </c>
-      <c r="O67" s="11"/>
-      <c r="P67" s="69" t="s">
+      <c r="O69" s="11"/>
+      <c r="P69" s="69" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R67" xr:uid="{57A31AB5-A5B3-4549-84CF-985A174AC5BE}"/>
+  <autoFilter ref="A1:R69" xr:uid="{57A31AB5-A5B3-4549-84CF-985A174AC5BE}"/>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.36" right="0.36" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="44" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
